--- a/laptop_tgdd_all.xlsx
+++ b/laptop_tgdd_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H474"/>
+  <dimension ref="A1:H479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15338,7 +15338,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:01</t>
+          <t>2026-07-04 11:48:25</t>
         </is>
       </c>
     </row>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>-29%</t>
+          <t>-33%</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -15380,7 +15380,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:17</t>
+          <t>2026-07-04 11:48:38</t>
         </is>
       </c>
     </row>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:31</t>
+          <t>2026-07-04 11:48:52</t>
         </is>
       </c>
     </row>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:45</t>
+          <t>2026-07-04 11:49:06</t>
         </is>
       </c>
     </row>
@@ -15486,7 +15486,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>2026-07-04 09:21:59</t>
+          <t>2026-07-04 11:49:20</t>
         </is>
       </c>
     </row>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>-26%</t>
+          <t>-31%</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -15548,7 +15548,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:12</t>
+          <t>2026-07-04 11:49:34</t>
         </is>
       </c>
     </row>
@@ -15570,7 +15570,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-28%</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -15590,7 +15590,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:26</t>
+          <t>2026-07-04 11:49:48</t>
         </is>
       </c>
     </row>
@@ -15632,7 +15632,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:40</t>
+          <t>2026-07-04 11:50:02</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>2026-07-04 09:22:54</t>
+          <t>2026-07-04 11:50:16</t>
         </is>
       </c>
     </row>
@@ -15696,7 +15696,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:07</t>
+          <t>2026-07-04 11:50:32</t>
         </is>
       </c>
     </row>
@@ -15738,7 +15738,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:21</t>
+          <t>2026-07-04 11:50:46</t>
         </is>
       </c>
     </row>
@@ -15800,7 +15800,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:35</t>
+          <t>2026-07-04 11:51:00</t>
         </is>
       </c>
     </row>
@@ -15842,7 +15842,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>2026-07-04 09:23:49</t>
+          <t>2026-07-04 11:51:14</t>
         </is>
       </c>
     </row>
@@ -15864,7 +15864,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:03</t>
+          <t>2026-07-04 11:51:28</t>
         </is>
       </c>
     </row>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:16</t>
+          <t>2026-07-04 11:51:43</t>
         </is>
       </c>
     </row>
@@ -15948,7 +15948,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>-23%</t>
+          <t>-28%</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -15968,7 +15968,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:30</t>
+          <t>2026-07-04 11:51:57</t>
         </is>
       </c>
     </row>
@@ -15990,7 +15990,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>-19%</t>
+          <t>-24%</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -16010,7 +16010,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:44</t>
+          <t>2026-07-04 11:52:10</t>
         </is>
       </c>
     </row>
@@ -16032,7 +16032,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>2026-07-04 09:24:58</t>
+          <t>2026-07-04 11:52:24</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -16094,7 +16094,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:11</t>
+          <t>2026-07-04 11:52:38</t>
         </is>
       </c>
     </row>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:26</t>
+          <t>2026-07-04 11:52:52</t>
         </is>
       </c>
     </row>
@@ -16158,7 +16158,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -16178,7 +16178,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:39</t>
+          <t>2026-07-04 11:53:05</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>-32%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -16220,7 +16220,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>2026-07-04 09:25:53</t>
+          <t>2026-07-04 11:53:20</t>
         </is>
       </c>
     </row>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -16262,7 +16262,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>2026-07-04 09:26:07</t>
+          <t>2026-07-04 11:53:34</t>
         </is>
       </c>
     </row>
@@ -16284,7 +16284,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>-32%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>2026-07-04 09:26:21</t>
+          <t>2026-07-04 11:53:48</t>
         </is>
       </c>
     </row>
@@ -16326,7 +16326,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>2026-07-04 09:26:35</t>
+          <t>2026-07-04 11:54:02</t>
         </is>
       </c>
     </row>
@@ -16368,7 +16368,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -16388,7 +16388,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>2026-07-04 09:26:49</t>
+          <t>2026-07-04 11:54:16</t>
         </is>
       </c>
     </row>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>2026-07-04 09:27:02</t>
+          <t>2026-07-04 11:54:30</t>
         </is>
       </c>
     </row>
@@ -16472,7 +16472,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>2026-07-04 09:27:16</t>
+          <t>2026-07-04 11:54:44</t>
         </is>
       </c>
     </row>
@@ -16494,7 +16494,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -16514,7 +16514,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>2026-07-04 09:27:30</t>
+          <t>2026-07-04 11:54:59</t>
         </is>
       </c>
     </row>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -16556,7 +16556,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>2026-07-04 09:27:43</t>
+          <t>2026-07-04 11:55:13</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>2026-07-04 09:27:57</t>
+          <t>2026-07-04 11:55:27</t>
         </is>
       </c>
     </row>
@@ -16620,7 +16620,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>-32%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>2026-07-04 09:28:11</t>
+          <t>2026-07-04 11:55:41</t>
         </is>
       </c>
     </row>
@@ -16662,7 +16662,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -16682,7 +16682,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>2026-07-04 09:28:25</t>
+          <t>2026-07-04 11:55:57</t>
         </is>
       </c>
     </row>
@@ -16724,7 +16724,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>2026-07-04 09:28:39</t>
+          <t>2026-07-04 11:56:10</t>
         </is>
       </c>
     </row>
@@ -16746,7 +16746,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -16766,7 +16766,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>2026-07-04 09:28:52</t>
+          <t>2026-07-04 11:56:24</t>
         </is>
       </c>
     </row>
@@ -16788,7 +16788,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>2026-07-04 09:29:06</t>
+          <t>2026-07-04 11:56:38</t>
         </is>
       </c>
     </row>
@@ -16830,7 +16830,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -16850,7 +16850,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>2026-07-04 09:29:20</t>
+          <t>2026-07-04 11:56:53</t>
         </is>
       </c>
     </row>
@@ -16872,7 +16872,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>2026-07-04 09:29:35</t>
+          <t>2026-07-04 11:57:09</t>
         </is>
       </c>
     </row>
@@ -16914,7 +16914,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -16934,7 +16934,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>2026-07-04 09:29:49</t>
+          <t>2026-07-04 11:57:23</t>
         </is>
       </c>
     </row>
@@ -16956,7 +16956,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>2026-07-04 09:30:02</t>
+          <t>2026-07-04 11:57:36</t>
         </is>
       </c>
     </row>
@@ -17018,7 +17018,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>2026-07-04 09:30:16</t>
+          <t>2026-07-04 11:57:50</t>
         </is>
       </c>
     </row>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>2026-07-04 09:30:30</t>
+          <t>2026-07-04 11:58:04</t>
         </is>
       </c>
     </row>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>-24%</t>
+          <t>-28%</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -17102,7 +17102,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>2026-07-04 09:30:45</t>
+          <t>2026-07-04 11:58:18</t>
         </is>
       </c>
     </row>
@@ -17124,7 +17124,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -17144,7 +17144,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>2026-07-04 09:30:59</t>
+          <t>2026-07-04 11:58:32</t>
         </is>
       </c>
     </row>
@@ -17166,7 +17166,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-29%</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -17186,7 +17186,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>2026-07-04 09:31:13</t>
+          <t>2026-07-04 11:58:46</t>
         </is>
       </c>
     </row>
@@ -17208,7 +17208,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>-32%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -17228,7 +17228,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>2026-07-04 09:31:27</t>
+          <t>2026-07-04 11:58:59</t>
         </is>
       </c>
     </row>
@@ -17250,7 +17250,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>-32%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>2026-07-04 09:31:41</t>
+          <t>2026-07-04 11:59:13</t>
         </is>
       </c>
     </row>
@@ -17292,7 +17292,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>2026-07-04 09:31:55</t>
+          <t>2026-07-04 11:59:28</t>
         </is>
       </c>
     </row>
@@ -17354,7 +17354,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>2026-07-04 09:32:09</t>
+          <t>2026-07-04 11:59:41</t>
         </is>
       </c>
     </row>
@@ -17376,7 +17376,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -17396,7 +17396,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>2026-07-04 09:32:22</t>
+          <t>2026-07-04 11:59:56</t>
         </is>
       </c>
     </row>
@@ -17438,7 +17438,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>2026-07-04 09:32:36</t>
+          <t>2026-07-04 12:00:11</t>
         </is>
       </c>
     </row>
@@ -17460,7 +17460,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>2026-07-04 09:32:50</t>
+          <t>2026-07-04 12:00:25</t>
         </is>
       </c>
     </row>
@@ -17522,7 +17522,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>2026-07-04 09:33:04</t>
+          <t>2026-07-04 12:00:39</t>
         </is>
       </c>
     </row>
@@ -17564,7 +17564,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>2026-07-04 09:33:18</t>
+          <t>2026-07-04 12:00:52</t>
         </is>
       </c>
     </row>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>2026-07-04 09:33:32</t>
+          <t>2026-07-04 12:01:07</t>
         </is>
       </c>
     </row>
@@ -17648,7 +17648,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>2026-07-04 09:33:45</t>
+          <t>2026-07-04 12:01:21</t>
         </is>
       </c>
     </row>
@@ -17690,7 +17690,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>2026-07-04 09:33:59</t>
+          <t>2026-07-04 12:01:34</t>
         </is>
       </c>
     </row>
@@ -17732,7 +17732,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>2026-07-04 09:34:13</t>
+          <t>2026-07-04 12:01:49</t>
         </is>
       </c>
     </row>
@@ -17774,7 +17774,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>2026-07-04 09:34:28</t>
+          <t>2026-07-04 12:02:10</t>
         </is>
       </c>
     </row>
@@ -17816,7 +17816,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>2026-07-04 09:34:42</t>
+          <t>2026-07-04 12:02:24</t>
         </is>
       </c>
     </row>
@@ -17858,7 +17858,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>2026-07-04 09:34:56</t>
+          <t>2026-07-04 12:02:40</t>
         </is>
       </c>
     </row>
@@ -17880,7 +17880,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>2026-07-04 09:35:10</t>
+          <t>2026-07-04 12:02:55</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>-32%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -17942,7 +17942,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>2026-07-04 09:35:25</t>
+          <t>2026-07-04 12:03:08</t>
         </is>
       </c>
     </row>
@@ -17984,7 +17984,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>2026-07-04 09:35:39</t>
+          <t>2026-07-04 12:03:22</t>
         </is>
       </c>
     </row>
@@ -18006,7 +18006,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>-32%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>2026-07-04 09:35:53</t>
+          <t>2026-07-04 12:03:35</t>
         </is>
       </c>
     </row>
@@ -18048,7 +18048,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -18068,7 +18068,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>2026-07-04 09:36:07</t>
+          <t>2026-07-04 12:03:49</t>
         </is>
       </c>
     </row>
@@ -18090,7 +18090,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -18110,7 +18110,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>2026-07-04 09:36:21</t>
+          <t>2026-07-04 12:04:04</t>
         </is>
       </c>
     </row>
@@ -18132,7 +18132,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -18152,7 +18152,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>2026-07-04 09:36:36</t>
+          <t>2026-07-04 12:04:19</t>
         </is>
       </c>
     </row>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>2026-07-04 09:36:49</t>
+          <t>2026-07-04 12:04:33</t>
         </is>
       </c>
     </row>
@@ -18216,7 +18216,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -18236,7 +18236,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>2026-07-04 09:37:03</t>
+          <t>2026-07-04 12:04:47</t>
         </is>
       </c>
     </row>
@@ -18258,7 +18258,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>2026-07-04 09:37:17</t>
+          <t>2026-07-04 12:05:01</t>
         </is>
       </c>
     </row>
@@ -18300,7 +18300,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>2026-07-04 09:37:30</t>
+          <t>2026-07-04 12:05:15</t>
         </is>
       </c>
     </row>
@@ -18362,7 +18362,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>2026-07-04 09:37:45</t>
+          <t>2026-07-04 12:05:29</t>
         </is>
       </c>
     </row>
@@ -18404,7 +18404,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>2026-07-04 09:38:00</t>
+          <t>2026-07-04 12:05:43</t>
         </is>
       </c>
     </row>
@@ -18446,7 +18446,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>2026-07-04 09:38:15</t>
+          <t>2026-07-04 12:05:57</t>
         </is>
       </c>
     </row>
@@ -18468,7 +18468,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -18488,7 +18488,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>2026-07-04 09:38:30</t>
+          <t>2026-07-04 12:06:11</t>
         </is>
       </c>
     </row>
@@ -18510,7 +18510,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -18530,7 +18530,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>2026-07-04 09:38:44</t>
+          <t>2026-07-04 12:06:24</t>
         </is>
       </c>
     </row>
@@ -18572,7 +18572,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>2026-07-04 09:38:59</t>
+          <t>2026-07-04 12:06:38</t>
         </is>
       </c>
     </row>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>2026-07-04 09:39:13</t>
+          <t>2026-07-04 12:07:03</t>
         </is>
       </c>
     </row>
@@ -18636,7 +18636,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -18656,7 +18656,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>2026-07-04 09:39:27</t>
+          <t>2026-07-04 12:07:16</t>
         </is>
       </c>
     </row>
@@ -18678,7 +18678,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>2026-07-04 09:39:41</t>
+          <t>2026-07-04 12:07:30</t>
         </is>
       </c>
     </row>
@@ -18720,7 +18720,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -18740,7 +18740,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>2026-07-04 09:39:55</t>
+          <t>2026-07-04 12:07:44</t>
         </is>
       </c>
     </row>
@@ -18762,7 +18762,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -18782,7 +18782,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>2026-07-04 09:40:10</t>
+          <t>2026-07-04 12:07:58</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-19%</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>2026-07-04 09:40:23</t>
+          <t>2026-07-04 12:08:11</t>
         </is>
       </c>
     </row>
@@ -18846,7 +18846,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>-35%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>2026-07-04 09:40:38</t>
+          <t>2026-07-04 12:08:25</t>
         </is>
       </c>
     </row>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>-35%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -18908,7 +18908,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>2026-07-04 09:40:52</t>
+          <t>2026-07-04 12:08:39</t>
         </is>
       </c>
     </row>
@@ -18950,7 +18950,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>2026-07-04 09:41:08</t>
+          <t>2026-07-04 12:08:53</t>
         </is>
       </c>
     </row>
@@ -18992,7 +18992,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>2026-07-04 09:41:22</t>
+          <t>2026-07-04 12:09:08</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>2026-07-04 09:41:36</t>
+          <t>2026-07-04 12:09:22</t>
         </is>
       </c>
     </row>
@@ -19056,7 +19056,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>-35%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -19076,7 +19076,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>2026-07-04 09:41:50</t>
+          <t>2026-07-04 12:09:36</t>
         </is>
       </c>
     </row>
@@ -19098,7 +19098,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>2026-07-04 09:42:03</t>
+          <t>2026-07-04 12:09:51</t>
         </is>
       </c>
     </row>
@@ -19140,7 +19140,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -19160,7 +19160,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>2026-07-04 09:42:17</t>
+          <t>2026-07-04 12:10:04</t>
         </is>
       </c>
     </row>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -19202,7 +19202,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>2026-07-04 09:42:31</t>
+          <t>2026-07-04 12:10:18</t>
         </is>
       </c>
     </row>
@@ -19224,7 +19224,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -19244,7 +19244,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>2026-07-04 09:42:45</t>
+          <t>2026-07-04 12:10:32</t>
         </is>
       </c>
     </row>
@@ -19266,7 +19266,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -19286,7 +19286,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>2026-07-04 09:42:59</t>
+          <t>2026-07-04 12:10:46</t>
         </is>
       </c>
     </row>
@@ -19308,7 +19308,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -19328,7 +19328,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>2026-07-04 09:43:13</t>
+          <t>2026-07-04 12:11:00</t>
         </is>
       </c>
     </row>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -19370,7 +19370,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>2026-07-04 09:43:27</t>
+          <t>2026-07-04 12:11:13</t>
         </is>
       </c>
     </row>
@@ -19392,7 +19392,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -19412,7 +19412,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>2026-07-04 09:43:41</t>
+          <t>2026-07-04 12:11:27</t>
         </is>
       </c>
     </row>
@@ -19434,7 +19434,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>-35%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -19454,7 +19454,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>2026-07-04 09:43:55</t>
+          <t>2026-07-04 12:11:41</t>
         </is>
       </c>
     </row>
@@ -19476,7 +19476,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -19496,7 +19496,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>2026-07-04 09:44:10</t>
+          <t>2026-07-04 12:11:55</t>
         </is>
       </c>
     </row>
@@ -19518,7 +19518,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -19538,7 +19538,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>2026-07-04 09:44:25</t>
+          <t>2026-07-04 12:12:12</t>
         </is>
       </c>
     </row>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>2026-07-04 09:44:39</t>
+          <t>2026-07-04 12:12:26</t>
         </is>
       </c>
     </row>
@@ -19602,7 +19602,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -19622,7 +19622,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>2026-07-04 09:44:53</t>
+          <t>2026-07-04 12:12:40</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>2026-07-04 09:45:07</t>
+          <t>2026-07-04 12:12:54</t>
         </is>
       </c>
     </row>
@@ -19686,7 +19686,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>-32%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
@@ -19706,7 +19706,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>2026-07-04 09:45:21</t>
+          <t>2026-07-04 12:13:08</t>
         </is>
       </c>
     </row>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>2026-07-04 09:45:35</t>
+          <t>2026-07-04 12:13:22</t>
         </is>
       </c>
     </row>
@@ -19770,7 +19770,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -19790,7 +19790,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>2026-07-04 09:45:50</t>
+          <t>2026-07-04 12:13:37</t>
         </is>
       </c>
     </row>
@@ -19820,7 +19820,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>2026-07-04 09:46:04</t>
+          <t>2026-07-04 12:13:51</t>
         </is>
       </c>
     </row>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>2026-07-04 09:46:18</t>
+          <t>2026-07-04 12:14:05</t>
         </is>
       </c>
     </row>
@@ -19904,7 +19904,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>2026-07-04 09:46:33</t>
+          <t>2026-07-04 12:14:20</t>
         </is>
       </c>
     </row>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>-32%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -19946,7 +19946,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>2026-07-04 09:46:47</t>
+          <t>2026-07-04 12:14:34</t>
         </is>
       </c>
     </row>
@@ -19968,7 +19968,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -19988,7 +19988,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>2026-07-04 09:47:02</t>
+          <t>2026-07-04 12:14:49</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>2026-07-04 09:47:16</t>
+          <t>2026-07-04 12:15:03</t>
         </is>
       </c>
     </row>
@@ -20052,7 +20052,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -20072,7 +20072,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>2026-07-04 09:47:31</t>
+          <t>2026-07-04 12:15:17</t>
         </is>
       </c>
     </row>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -20114,7 +20114,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>2026-07-04 09:47:45</t>
+          <t>2026-07-04 12:15:33</t>
         </is>
       </c>
     </row>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -20156,7 +20156,217 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>2026-07-04 09:48:00</t>
+          <t>2026-07-04 12:15:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Laptop Acer Aspire 3 A314 42P R3B3 - NX.KSFSV.001 (R7 5700U, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>14.290.000₫</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>15.990.000₫</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ  Xem chi tiết | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 5700U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 1.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: LPDDR4X (Onboard) | Tốc độ Bus RAM:: 4266 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED Backlit Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 HDMI 1 x USB Type-C (hỗ trợ USB 3.2, DisplayPort) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Acer Purified Voice | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2024 | Kích thước:: Dài 318.2 mm - Rộng 225.5 mm - Dày 17.8 mm - 1.4 kg | Chất liệu:: Vỏ nhựa</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-3-a314-42p-r3b3-r7-nxksfsv001</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>2026-07-04 11:48:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Laptop Acer Aspire Lite 14 AL14 71M 52GQ - NX.J4ASV.001 (i5 12500H, 16GB, 512GB, Full HD+, Win11)</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>15.290.000₫</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>18.990.000₫</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>-19%</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ  Xem chi tiết | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Công nghệ CPU:: Intel Core i5 Alder Lake - 12500H | Số nhân:: 12 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Iris Xe Graphics eligible | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 8 GB) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 40 GB | Ổ cứng:: 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Wide viewing angle LCD TFT LED Backlit Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3x Type-A USB 3.2 Gen 1 1x USB-C 3.2 Gen 2 (hỗ trợ DisplayPort) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Built-in microphone Stereo speakers | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314.4 mm - Rộng 221.9 mm - Dày 19.5 mm - 1.55 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng hợp kim nhôm</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-14-al14-71m-52gq-i5-12500h-nx-j4asv-001</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>2026-07-04 11:50:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC - NX.DG3SV.002.16G (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>22.990.000₫</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>24.990.000₫</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 357.6 mm - Rộng 228.5 mm - Dày 18.7 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-53p-56ec-core-5-120u-nx-dg3sv-002-16g</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>2026-07-04 11:53:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV16 41 R6ZY - NH.QP2SV.002 (R5 8645HS, 16GB, 512GB, RTX 3050 6GB, WUXGA 165Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>28.990.000₫</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>30.990.000₫</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Balo Acer Predator Gaming | Phiếu mua hàng 500.000đ mua Chuột Gaming Logitech dòng Pro X | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ  Xem chi tiết | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 8645HS | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 4.30 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 6 GB | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tần số quét:: 165 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: TFT LED Backlit Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 HDMI 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2024 | Kích thước:: Dài 361.8 mm - Rộng 278.4 mm - Dày 25.46 mm - 2.5 kg | Chất liệu:: Vỏ nhựa</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/laptop/acer-nitro-v-16-propanel-anv16-41-r6zy-r5-nhqp2sv002</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>2026-07-04 12:00:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Laptop Asus Vivobook 14 Flip TP3407SA - SG349W (Ultra 5 226V, 16GB, 512GB, WUXGA OLED, Cảm ứng, Win11)</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>26.490.000₫</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>30.590.000₫</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Lunar Lake - 226V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 40 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 95% DCI-P3 | Công nghệ màn hình:: Glossy Display 70% Less harmful blue light 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x USB 3.2. Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Thunderbolt 4 (hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD card reader | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Tản nhiệt ASUS IceCool | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.6 mm - Rộng 220.9 mm - Dày 17.1 mm - 1.57 kg | Chất liệu:: Vỏ kim loại</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-flip-tp3407sa-ultra-5-226v-sg349w</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>2026-07-04 12:10:36</t>
         </is>
       </c>
     </row>

--- a/laptop_tgdd_all.xlsx
+++ b/laptop_tgdd_all.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0&quot;đ&quot;"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,12 +57,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -492,14 +497,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US002WVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>30090000</v>
+          <t>Laptop Acer Aspire Go 15 AG15-52P-52WT - NX.JWKSV.001 (Ultra 5 115U, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>22790000</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>32990000</v>
+        <v>24990000</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -508,1227 +513,1203 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 115U | Số nhân:: 8 | Số luồng:: 10 | Tốc độ CPU:: 1.5 GHz (Lên đến 4.2 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB onboard + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 2 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357.5 mm - Rộng 229 mm - Dày 17.95 mm - 1.59 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-7-355-83us002wvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-go-15-ag15-52p-52wt-ultra-5-115u-nx-jwksv-001</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:43:11</t>
+          <t>2026-07-30 10:48:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US003YVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>29490000</v>
+          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP - NX.DMCSV.003 (R7 7730U, 8GB, 512GB, Full HD+, Win11)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>20990000</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>32990000</v>
+        <v>22990000</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 680M Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14.5" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB Type - C 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 324 mm - Rộng 227.6 mm - Dày 17.9 mm - 1.3 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-7-355-83us003yvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-14-al14-44p-r0sp-r7-7730u-nx-dmcsv-003</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:43:25</t>
+          <t>2026-07-30 10:48:16</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 - 83S1006RVN (R7 AI 445, 16GB, 512GB, WUXGA OLED, Win11)</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>30590000</v>
+          <t>Laptop Acer Aspire Lite 14 AL14-45P-R7Z3 - NX.DPESV.002 (R3 5400U, 8GB, 512GB, Full HD+, Win11)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>14990000</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>32990000</v>
+        <v>17990000</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.0 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 2 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 2-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 3 - 5400U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.60 GHz (Lên đến 4.0 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.8 mm - Rộng 219.7 mm - Dày 19.1 mm - 1.3 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-14agp11-r7-ai-445-83s1006rvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-14-al14-45p-r7z3-r3-5400u-nx-dpesv-002</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:43:39</t>
+          <t>2026-07-30 10:48:30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14IPH11 - 83S5004FVN (Ultra 7 355, 16GB, 512GB, WUXGA OLED, Win11)</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>34490000</v>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W - NX.DNRSV.002 (R5 40, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>19590000</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>37990000</v>
+        <v>22990000</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 53 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360.66 mm - Rộng 234.8 mm - Dày 16.95 mm - 1.45 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-14iph11-ultra-7-355-83s5004fvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-21p-r91w-r5-40-nx-dnrsv-002</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:43:53</t>
+          <t>2026-07-30 10:48:44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 OLED 14IPH11 - 83S5000DVN (Ultra 5 322, 16GB, 512GB, WUXGA OLED, Win11)</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>29490000</v>
+          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN - NX.DDASV.001 (Core 3 N350, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>17890000</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>32990000</v>
+        <v>18990000</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD NVMe M.2 PCIe Gen 4.0 mở rộng (2280) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 2 x USB Type-C 3.2 (hỗ trợ truyền dữ liệu, Power Delivery 3.0, and DisplayPort 1.2) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Nắp lưng và mặt đáy bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 3 Twin Lake - N350 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 3.90 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB 3.2 HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.0 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357.8 mm - Rộng 235.6 mm - Dày 19.7 mm - 1.53 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-oled-14iph11-ultra-5-322-83s5000dvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-36p-30tn-core-3-n350-nx-ddasv-001</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:44:07</t>
+          <t>2026-07-30 10:48:57</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkBook 14 G9 - 21V0005PVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>28290000</v>
+          <t>Laptop Acer Aspire Lite 15 AL15-44P-R4UH - NX.DJVSV.002 (R7 7730U, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>21990000</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>31190000</v>
+        <v>23990000</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB Type - C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 230.2 mm - Dày 18.6 mm - 1.49 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-g9-r7-250-21v0005pvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-44p-r4uh-r7-7730u-nx-djvsv-002</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:44:20</t>
+          <t>2026-07-30 10:49:10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkBook 14 Gen 9 IRL - 21UY008TVN (i5 13420H, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>27290000</v>
+          <t>Laptop Acer Aspire Lite 15 AL15-46P-R73C - NX.JXMSV.001 (R3 5400U, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>14490000</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>28890000</v>
+        <v>17990000</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-19%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 3 - 5400U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.60 GHz (Lên đến 4.0 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 3.2. 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) 1 x USB 3.2 Gen 2 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 53 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360.66 mm - Rộng 234.8 mm - Dày 16.95 mm - 1.45 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-gen-9-irl-i5-13420h-21uy008tvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-46p-r73c-r3-5400u-nx-jxmsv-001</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:44:34</t>
+          <t>2026-07-30 10:49:24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkBook 16 G9 - 21UT005MVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>29690000</v>
+          <t>Laptop Acer Aspire Lite 15 AL15-48P-R86Q - NX.DS1SV.002 (R7 5825U, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>18990000</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>31590000</v>
+        <v>21990000</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356 mm - Rộng 253.5 mm - Dày 17.5 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 5825U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) 1 x USB 3.2 Gen 2 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360.66 mm - Rộng 234.8 mm - Dày 16.95 mm - 1.45 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-16-g9-r7-250-21ut005mvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-48p-r86q-r7-5825u-nx-ds1sv-002</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:44:47</t>
+          <t>2026-07-30 10:50:01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad E14 Gen 7 - 21SX00BNVN (Ultra 5 135H, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>29690000</v>
+          <t>Laptop Acer Aspire Lite 15 AL15-49P-R6XX - NX.DRZSV.002 (R5 7430U, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>20990000</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>31590000</v>
+        <v>1590000</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 135H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.60 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x USB-A (USB 10Gbps/USB 3.2 Gen 2), Always On 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Audio by HARMAN Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 19.7 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 7430U | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) 1 x USB 3.2 Gen 2 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360.66 mm - Rộng 234.8 mm - Dày 16.95 mm - 1.45 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-5-135h-21sx00bnvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-49p-r6xx-r5-7430u-nx-drzsv-002</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:45:00</t>
+          <t>2026-07-30 10:50:15</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad E14 Gen 7 - 21SX005NVN (Ultra 5 225U, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>31490000</v>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC - NX.DG3SV.002.16G (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>24990000</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>33890000</v>
+        <v>1590000</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4 với USB Power Delivery và DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Audio by HARMAN Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 19.7 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 357.6 mm - Rộng 228.5 mm - Dày 18.7 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-5-225u-21sx005nvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-53p-56ec-core-5-120u-nx-dg3sv-002-16g</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:45:14</t>
+          <t>2026-07-30 10:50:28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad X9 14 Gen 1 - 21QA006JVN (Ultra 7 258V, 32GB, 512GB, WUXGA OLED, Win11Pro)</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>53290000</v>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH - NX.DG3SV.001 (Core 5 120U, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>24990000</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>55190000</v>
+        <v>1590000</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.80 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Chống chói Anti Glare Dolby Vision 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm HDMI 2.1 2 x USB-C (hỗ trợ Thunderbolt 4/USB 4, USB Power Delivery và DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.8 mm - Rộng 212.3 mm - Dày 17.18 mm - 1.21 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD WVA | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3x Type-A USB 3.2 Gen 1 1 x USB Type-C 3.2 gen 1 (hỗ trợ truyền dữ liệu và Power Delivery) HDMI 1.4 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) Wi-Fi Dual Band | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357.6 mm - Rộng 228.5 mm - Dày 18.7 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-x9-14-gen-1-ultra-7-258v-21qa006jvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-53p-56qh-core-5-120u-nx-dg3sv-001</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:45:28</t>
+          <t>2026-07-30 10:50:42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo V14 G5 - 83HD0035VN (Core7 240H, 16G, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
+          <t>Laptop Acer Aspire Lite 16 AL16-71P-582Q - NX.DRSSV.001 (Ultra 5 125H, 16GB, 512GB, Full HD+ 120Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
         <v>26990000</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>28590000</v>
+        <v>1590000</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) LAN (RJ45) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Ion, 47 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324.2 mm - Rộng 215.2 mm - Dày 17.9 mm - 1.37 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 125H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357 mm - Rộng 245.5 mm - Dày 18.9 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-v14-g5-core7-240h-83hd0035vn</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-16-al16-71p-582q-ultra-5-125h-nx-drssv-001</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:45:41</t>
+          <t>2026-07-30 10:50:56</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002LVN (Ultra 5 322, 16GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>37490000</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+          <t>Laptop Acer Gaming Aspire 7 A715-59G-59RD - NH.DXUSV.001 (Core 5 210H, 16GB, 512GB, RTX 3050 4GB, Fulll HD 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>31990000</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.45 mm - 1.38 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 4 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35W - 80W | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 4 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle 350 nits Acer ComfyView | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C (hỗ trợ DisplayPort 1.4) LAN (RJ45) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn LED - 15 chế độ màu | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 359.5 mm - Rộng 238 mm - Dày 22.7 mm - 1.99 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-5-322-83tc002lvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-aspire-7-a715-59g-59rd-core-5-210h-nh-dxusv-001</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:45:54</t>
+          <t>2026-07-30 10:51:11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002MVN (Ultra 7 355, 32GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>54490000</v>
+          <t>Laptop Acer Gaming Nitro ProPanel AN16S-61-R9CN - NH.QXGSV.001 (Ryzen AI 7 350, 16GB, 512GB, RTX 5070 8GB, 2K+ 180Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>59990000</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>57990000</v>
+        <v>1590000</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.95 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.0 GHz (Lên đến 5.2 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe mở rộng (nâng cấp tối đa 2 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits 3ms | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: NVIDIA Optimus | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 19.9 mm - 2.18 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-7-355-83tc002mvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-an16s-61-r9cn-ryzen-ai-7-350-nh-qxgsv-001</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:46:07</t>
+          <t>2026-07-30 10:51:25</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga 7 2in1 OLED 14IPH11 - 83TC002JVN (Ultra 7 355, 32GB, 1TB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>53490000</v>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-73Z8 - NH.QUASV.001 (Core 7 240H, 16GB, 512GB, RTX 4050 6GB, Full HD  180Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>37290000</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>57990000</v>
+        <v>37990000</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Tiêu chuẩn Nền Intel Evo | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.45 mm - 1.38 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số luồng:: 16 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: IPS | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1x Ethernet 3 x USB 3.2 Gen 1 Type-A 1 x USB Type-C (65W) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: 720p at 30 fps HD camera Camera with Dual Microphone | Đèn bàn phím:: Đơn sắc - Màu cam | Công nghệ âm thanh:: Windows Spatial Sound High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-oled-14iph11-ultra-7-355-83tc002jvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-73z8-core-7-240h-nh-quasv-001</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:46:22</t>
+          <t>2026-07-30 10:51:39</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 OLED 14AGP11 - 83QS001DVN (R7 AI 445, 16GB, 512GB, WUXGA OLED, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>37490000</v>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV16-72-71T9 - NH.QUNSV.001 (Core 7 240H, 16GB, 512GB, RTX 5060 8GB, WUXGA 180Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>43990000</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>39990000</v>
+        <v>45990000</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 8000 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Glossy Display Chuẩn DisplayHDR True Black 500 Eyesafe Dolby Vision 400 nits X-Rite Flicker Free | Cổng giao tiếp:: 1 x USB Type-C (hỗ trợ DisplayPort 1.4) 2 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 221 mm - Dày 13.9 mm - 1.15 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 95 W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD WVA NVIDIA Advanced Optimus | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 2 x USB 3.2 gen 2 Type-A LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (2 x 2) Wi-Fi Dual Band | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu cam | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio High SNR DAC with 2.1 Vrms out capability Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 360 mm - Rộng 274.5 mm - Dày 24.5 mm - 2.4 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-oled-14agp11-r7-ai-445-83qs001dvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16-72-71t9-core-7-240h-nh-qunsv-001</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:46:35</t>
+          <t>2026-07-30 10:51:53</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 OLED 14IPH11 - 83QM002FVN (Ultra 7 355, 32GB, 1TB, WUXGA OLED, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>52490000</v>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-61-R0B8 - NH.QXQSV.001 (Ryzen AI 5 340, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>45390000</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>55990000</v>
+        <v>47990000</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe 600nits (peak) Dolby Vision 400 nits X-Rite Flicker Free | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 2-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 221 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.40 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-oled-14iph11-ultra-7-355</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-61-r0b8-ryzen-ai-5-340-nh-qxqsv-001</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:46:50</t>
+          <t>2026-07-30 10:52:06</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Laptop MacBook Pro 14 inch M5 Pro 48GB/1TB</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>84990000</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>85490000</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-1%</t>
-        </is>
-      </c>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-71-58WQ - NH.QXBSV.001 (Core 5 210H, 16GB, 512GB, RTX 5050 8GB, 2K+ 180Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>46990000</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm giá 500,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Phiếu mua hàng Chuột, Bàn phím (Apple) trị giá 500,000đ | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng 50.000đ mua Chuột Logitech M240 | Tặng Phiếu mua hàng Balo, Túi chống sốc (giá trị trên 1,000,000đ) trị giá 300,000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Apple M5 Pro | Số nhân:: 15 | Số luồng:: Hãng không công bố | Tốc độ CPU:: 307 GB/s memory bandwidth | Card màn hình:: Card tích hợp - 16 nhân GPU | RAM:: 48 GB | Loại RAM:: Hãng không công bố | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 1 TB SSD | Kích thước màn hình:: 14.2" | Độ phân giải:: Liquid Retina XDR display (3024 x 1964) | Tần số quét:: up to 120 Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: ProMotion Độ sáng XDR: toàn màn hình 1000 nits, cao nhất 1600 nits (chỉ nội dung HDR) Độ sáng SDR: lên đến 1000 nits Wide color (P3) True Tone Technology 1 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm MagSafe 3 3 x Thunderbolt 5 (hỗ trợ DisplayPort, Thunderbolt 5 (up to 120Gb/s), USB 4 (up to 120Gb/s)) HDMI | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Khe đọc thẻ nhớ:: SDXC | Webcam:: Camera 12MP Center Stage | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Hệ thống âm thanh 6 loa Spatial Audio 3 microphones Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-Po, 72.4 Wh | Hệ điều hành:: macOS Tahoe | Thời điểm ra mắt:: 03/2026 | Kích thước:: Dài 312.6 mm - Rộng 221.2 mm - Dày 15.5 mm - 1.6 kg | Chất liệu:: Vỏ nhôm tái chế 100% | Hãng:: MacBook. Xem thông tin hãng</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/macbook-pro-14-inch-m5-pro-48gb-1tb</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-71-58wq-core-5-210h-nh-qxbsv-001</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:47:03</t>
+          <t>2026-07-30 10:52:21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Laptop MacBook Pro 14 inch M5 Pro 48GB/2TB</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>98690000</v>
+          <t>Laptop Acer Gaming Predator Helios Neo 16 PHN16-I31-50H7 - NH.U4SSV.001 (i5 14450HX, 32GB, 512GB, RTX 5050 8GB, Full HD+ 180Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>51390000</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>99190000</v>
+        <v>61990000</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm giá 500,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Phiếu mua hàng Chuột, Bàn phím (Apple) trị giá 500,000đ | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng 50.000đ mua Chuột Logitech M240 | Tặng Phiếu mua hàng Balo, Túi chống sốc (giá trị trên 1,000,000đ) trị giá 300,000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Apple M5 Pro | Số nhân:: 15 | Số luồng:: Hãng không công bố | Tốc độ CPU:: 307 GB/s memory bandwidth | Card màn hình:: Card tích hợp - 16 nhân GPU | RAM:: 48 GB | Loại RAM:: Hãng không công bố | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 2 TB SSD | Kích thước màn hình:: 14.2" | Độ phân giải:: Liquid Retina XDR display (3024 x 1964) | Tần số quét:: up to 120 Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: ProMotion Độ sáng XDR: toàn màn hình 1000 nits, cao nhất 1600 nits (chỉ nội dung HDR) Độ sáng SDR: lên đến 1000 nits Wide color (P3) True Tone Technology 1 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm MagSafe 3 3 x Thunderbolt 5 (hỗ trợ DisplayPort, Thunderbolt 5 (up to 120Gb/s), USB 4 (up to 120Gb/s)) HDMI | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Khe đọc thẻ nhớ:: SDXC | Webcam:: Camera 12MP Center Stage | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Hệ thống âm thanh 6 loa Spatial Audio 3 microphones Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-Po, 72.4 Wh | Hệ điều hành:: macOS Tahoe | Thời điểm ra mắt:: 03/2026 | Kích thước:: Dài 312.6 mm - Rộng 221.2 mm - Dày 15.5 mm - 1.6 kg | Chất liệu:: Vỏ nhôm tái chế 100% | Hãng:: MacBook. Xem thông tin hãng</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe mở rộng (nâng cấp tối đa 2 TB) 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 2 x Thunderbolt 4 with USB Type - C (hỗ trợ DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Hi-Res Audio Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Quạt kim loại 3D AeroBlade 2 quạt | Tính năng khác:: NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 26.75 mm - 2.5 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/macbook-pro-14-inch-m5-pro-48gb-2tb</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16-phn16-i31-50h7-i5-14450hx-nh-u4ssv-001</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:47:16</t>
+          <t>2026-07-30 10:52:35</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Laptop MacBook Pro 16 inch M5 Pro 64GB/1TB</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>109490000</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="inlineStr"/>
+          <t>Laptop Acer Gaming Predator Helios Neo 16 PHN16-I31-72XE - NH.U4RSV.001 (i7 14650HX, 32GB, 512GB, RTX5060 8GB, 2K+ 180Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>61390000</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>71990000</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm giá 500,000đ - Tặng Microsoft 365 Personal | Phiếu mua hàng Chuột, Bàn phím (Apple) trị giá 500,000đ | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng 50.000đ mua Chuột Logitech M240 | Tặng Phiếu mua hàng Balo, Túi chống sốc (giá trị trên 1,000,000đ) trị giá 300,000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Apple M5 Pro | Số nhân:: 18 | Số luồng:: Hãng không công bố | Tốc độ CPU:: 307 GB/s memory bandwidth | Card màn hình:: Card tích hợp - 20 nhân GPU | RAM:: 64 GB | Loại RAM:: Hãng không công bố | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 1 TB SSD | Kích thước màn hình:: 16.2" | Độ phân giải:: Liquid Retina XDR display (3456 x 2234) | Tần số quét:: up to 120 Hz | Công nghệ màn hình:: ProMotion Độ sáng XDR: toàn màn hình 1000 nits, cao nhất 1600 nits (chỉ nội dung HDR) Độ sáng SDR: lên đến 1000 nits Wide color (P3) True Tone Technology 1 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm MagSafe 3 3 x Thunderbolt 5 (hỗ trợ DisplayPort, Thunderbolt 5 (up to 120Gb/s), USB 4 (up to 120Gb/s)) HDMI | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Khe đọc thẻ nhớ:: SDXC | Webcam:: Camera 12MP Center Stage | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Hệ thống âm thanh 6 loa Spatial Audio 3 microphones Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-Po, 100 Wh | Hệ điều hành:: macOS Tahoe | Thời điểm ra mắt:: 03/2026 | Kích thước:: Dài 355.7 mm - Rộng 248.1 mm - Dày 16.8 mm - 2.14 kg | Chất liệu:: Vỏ nhôm tái chế 100% | Hãng:: MacBook. Xem thông tin hãng</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 14650HX | Số nhân:: 16 | Số luồng:: 24 | Tốc độ CPU:: 2.20 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe mở rộng (nâng cấp tối đa 2 TB) 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 2 x Thunderbolt 4 with USB Type - C (hỗ trợ DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Hi-Res Audio Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Quạt kim loại 3D AeroBlade 2 quạt | Tính năng khác:: NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 26.75 mm - 2.5 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/macbook-pro-16-inch-m5-pro-64gb-1tb</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16-phn16-i31-72xe-i7-14650hx-nh-u4rsv-001</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:47:33</t>
+          <t>2026-07-30 10:52:49</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Gaming Cyborg 15 Black Edition A13VE - A13VE-2410VN (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>27990000</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>31990000</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-13%</t>
-        </is>
-      </c>
+          <t>Laptop Acer Gaming Predator Helios Neo 16 PHN16-I31-74MN - NH.U4SSV.002 (i7 14650HX, 32GB, 512GB, RTX 5050 8GB, Full HD+ 180Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>66990000</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.60 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Công nghệ âm thanh:: Hi-Res Audio DTS Audio | Tản nhiệt:: Cooler Boost 1 x Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 53.5 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.36 mm - Rộng 250.34 mm - Dày 22.9 mm - 1.98 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 14650HX | Số nhân:: 16 | Số luồng:: 24 | Tốc độ CPU:: 2.20 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView NVIDIA Advanced Optimus | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1x Ethernet 2 x Thunderbolt 4 with USB Type - C (hỗ trợ DisplayPort 2.1) 2 x USB 3.2 gen 2 Type-A HDMI 2.1 | Kết nối không dây:: Bluetooth 5.4 + LE Wi-Fi 6E (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Hi-Res certification Windows Spatial Sound High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Quạt kim loại 3D AeroBlade 2 quạt | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 26.75 mm - 2.5 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-black-edition-a13ve-i5-13420h-a13ve-2410vn</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16-phn16-i31-74mn-i7-14650hx-nh-u4ssv-002</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:47:49</t>
+          <t>2026-07-30 10:53:02</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Gaming Cyborg 15 C13WEO-417VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>35590000</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>36990000</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+          <t>Laptop Acer Gaming Predator Helios Neo 16S PHN16S-I51-97T9 - NH.U3SSV.006 (Ultra 9 386H, 16GB, 512GB, RTX 5070 8GB, 2K+ 165Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>77990000</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card rời - Intel UHD Graphics (tích hợp) + NVIDIA GeForce RTX 5050 GPU, 8GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB Type-A 1 x Headphone/ Microphone combo audio jack 1 x USB Type C (chỉ hỗ trợ Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: DTS Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.98 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 9 Panther Lake - 386H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 50 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: LED-backlit TFT LCD 500 nits Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 18.9 mm - 2.2 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-c13weo-417vn-i7-13620h</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16s-phn16s-i51-97t9-ultra-9-386h</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:48:03</t>
+          <t>2026-07-30 10:53:15</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Gaming Raider 16 MAX HX B2WI - 095VN (Ultra 9 290HX Plus, 64GB, 2TB, RTX 5080 16GB, QHD+ OLED 240Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>1350000</v>
+          <t>Laptop Acer Nitro ProPanel ANV15-52-50RB - NH.QUASV.002 (Core 5 210H, 16GB, 512GB, RTX 4050 6GB, Full HD 180Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>35990000</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>1590000</v>
+        <v>37990000</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 9 Arrow Lake - 290HX Plus | Số nhân:: 24 | Số luồng:: 24 | Tốc độ CPU:: 2.70 GHz (Lên đến 5.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 1334 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5080, 16 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 175 W | RAM:: 64 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe 32 GB) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: 128 GB | Ổ cứng:: 2 TB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 4 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: QHD+ (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 240Hz | Độ phủ màu:: 100% DCI-P3 | Cổng giao tiếp:: 2 x Thunderbolt 4 (hỗ trợ Power Delivery 3.1 và DisplayPort) 3 x USB Type-A 3.2 Gen 2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Cooler Boost 3 Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-Po, 91.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 363 mm - Rộng 269.7 mm - Dày 28.85 mm - 2.6 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 60W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 300 nits Acer ComfyView 3ms | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2 microphones Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Tính năng khác:: Copilot Key | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-gaming-raider-16-max-hx-b2wi-ultra-9-290hx-plus-095vn</t>
+          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv15-52-50rb-core-5-210h-nh-quasv-002</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:48:16</t>
+          <t>2026-07-30 10:53:29</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 F1MG-1264VN (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>19990000</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>22390000</v>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>-11%</t>
-        </is>
-      </c>
+          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP - NX.JZHSV.003 (Ultra 7 358H, 32GB, 1TB, 2.8K 120Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>50990000</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core thế hệ 12 - 120U | Số nhân:: Hãng không công bố | Số luồng:: 12 | Tốc độ CPU:: 1.45 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (2280) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: Hãng không công bố | Cổng giao tiếp:: 3 x USB 3.2 Gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell, 46.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.7 kg | Chất liệu:: Plastic (nhựa dẻo)</t>
+          <t>Công nghệ CPU:: Intel Core Ultra X7 - 358H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 9600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: 2.8K (2880 x 1800) - OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 ACER CineCrystal WVA | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A HDMI 2.1 2 x USB-C (hỗ trợ Thunderbolt 4/USB 4, USB Power Delivery và DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res certification High SNR DAC with 2.1 Vrms out capability Công nghệ Smart AMP Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-ion, 71 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.5 mm - Rộng 218.9 mm - Dày 15.6 mm - 1.12 kg | Chất liệu:: Vỏ hợp kim Nhôm</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-modern-15-f1mg-1264vn-core-5-120u</t>
+          <t>https://www.thegioididong.com/laptop/acer-swift-go-14-ai-sfg14-i71-70rp-ultra-7-358h-nx-jzhsv-003</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:48:30</t>
+          <t>2026-07-30 10:53:44</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Laptop SingPC M16-i382 (i3 1215U, 8GB, 256GB, WUXGA, Win11 Pro)</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>13890000</v>
+          <t>Laptop Asus Gaming ROG Strix G16 G614PM - TS147W (R9 8940HX, 16GB, 512GB, RTX 5060 8GB, WQXGA 300Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>52990000</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>15190000</v>
+        <v>1590000</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i3 Alder Lake - 1215U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.2GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 256 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115W - 140W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.288 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/singpc-m16-i382-i3-1215u</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pm-r9-8940hx-ts147w</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:48:43</t>
+          <t>2026-07-30 10:53:58</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Laptop SingPC M16-i595 (i5 1235U, 16GB, 512GB, WUXGA, Win11 Pro)</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>18390000</v>
+          <t>Laptop Asus Gaming ROG Strix G16 G614PR - TS103W (R9 8940HX, 16GB, 512GB, RTX 5070Ti 12GB, WQXGA 300Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>70590000</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>19990000</v>
+        <v>71990000</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Alder Lake - 1235U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.30 GHz (Lên đến 4.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 72% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070Ti, 12 GB | Số nhân GPU:: 5888 CUDA Cores | Công suất đồ hoạ - TGP:: 140 W | Hiệu năng xử lý AI (TOPS):: Lên đến 992 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.34 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/singpc-m16-i595-i5-1235u</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pr-r9-8940hx-ts103w</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 15:48:56</t>
+          <t>2026-07-30 10:54:12</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - DC5C3851W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr"/>
+          <t>Laptop Asus Gaming ROG Zephyrus GA403GM - SY004W (R9 AI 465, 32GB, 1TB, RTX 5060 8GB, 3K OLED 120Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>65990000</v>
+      </c>
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x Headphone/ Microphone combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 2 x USB 2.0 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 235 mm - Rộng 358.5 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 9 - 465 | Số nhân:: 10 | Số luồng:: 20 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 623 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Anti-Reflective G-Sync ROG Nebula HDR Display 1000 nits Dolby Vision | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, G-SYNC) 1 x USB4 Type-C (hỗ trợ DisplayPort, Power Delivery) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 73 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311 mm - Rộng 220 mm - Dày 16.3 mm - 1.5 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3851w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-zephyrus-ga403gm-r9-ai-465-sy004w</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:12:32</t>
+          <t>2026-07-30 10:54:26</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - CPH992 (i5 1334U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365B, Win11)</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>21990000</v>
+          <t>Laptop Asus TUF Gaming F16 FX608JHI - TU210W (i5 14450HX, 16GB, 512GB,RTX 5050 8GB, WUXGA 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>40990000</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>23490000</v>
+        <v>47990000</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 1334U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 2666 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Bluetooth 5.0 Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235.6 mm - Dày 19 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 2TB) 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 72% NTSC | Công nghệ màn hình:: G-Sync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 3 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: FHD 1080p | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Dolby Atmos | Tản nhiệt:: 2 quạt | Tính năng khác:: MUX Switch NVIDIA Optimus Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 269 mm - Dày 27.3 mm - 2.2 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-i5-1334u-cph992</t>
+          <t>https://www.thegioididong.com/laptop/asus-tuf-gaming-f16-fx608jhi-i5-14450hx-tu210w</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:12:46</t>
+          <t>2026-07-30 10:54:40</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - DC15250-i5U165W11SLU-27 (i5 1334U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>21990000</v>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>23490000</v>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+          <t>Laptop Asus TUF Gaming FA401EA - RG034W (RYZEN AI MAX+ 392, 64GB, 1TB, WQXGA 165Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>64990000</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 1334U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.30 GHz (Lên đến 4.60 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm HDD SATA (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 18.99 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI Max+ - 392 | Số nhân:: 12 | Số luồng:: 24 | Tốc độ CPU:: 3.2 GHz (Lên đến 5.0 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 8060S Graphics | RAM:: 64 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8000 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 2 x USB 3.2 gen 2 Type-A 1 x USB Type-C USB 4 (hỗ trợ DisplayPort và Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hi-Res certification AI noise-canceling technology Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 73 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311 mm - Rộng 227 mm - Dày 19.9 mm - 1.48 kg | Chất liệu:: Nắp lưng và chiếu nghỉ tay bằng kim loại</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-i5-1334u-dc15250-i5u165w11slu-27</t>
+          <t>https://www.thegioididong.com/laptop/asus-tuf-gaming-fa401ea-ryzen-ai-max-392-rg034w</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:13:00</t>
+          <t>2026-07-30 10:55:09</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - DC15250-i7U161W11SLU-27 (i7 1355U, 16GB, 1TB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>26990000</v>
+          <t>Laptop HP OmniBook X Flip 14 fk0082AU - BZ7N8PA (R7 AI 350, 32GB, 1TB, 2K, Cảm ứng, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>39890000</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>27490000</v>
+        <v>40890000</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
@@ -1737,721 +1718,733 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 1355U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.70 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-Po, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 18.99 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: 2K (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Corning Gorilla Glass 3 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB Type-C (hỗ trợ truyền dữ liệu, DisplayPort 2.1, Power delivery 3.1, HP Sleep and Charge) Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E MT7922 Bluetooth 5.3 | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ | Thông tin Pin:: 3-cell Li-Po, 59 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 218.5 mm - Dày 14.6 mm - 1.39 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-i7-1355u-dc15250-i7u161w11slu-27</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-x-flip-14-fk0082au-r7-ai-350-bz7n8pa</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:13:14</t>
+          <t>2026-07-30 11:53:41</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15255 - DC5R5973W1-2Y (R5 7530U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>24990000</v>
+          <t>Laptop HP Probook 4 G1ah 16 - C40JPAT (R5 220, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>25490000</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>25690000</v>
+        <v>29890000</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 7530U | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/microphone combo 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 220 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 48 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x USB Type-C 3.2 Gen 2 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: FHD 1080p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 359.4 mm - Rộng 251 mm - Dày 17 mm - 1.785 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r5-7530u-dc5r5973w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/hp-probook-4-g1ah-16-r5-220-c40jpat</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:13:28</t>
+          <t>2026-07-30 11:53:56</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 16 DC16250 - 71092481 (Core 5 120U, 16GB, 1TB, Full HD+, OfficeHS24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>27990000</v>
+          <t>Laptop HP ProBook 4 G1iR 14 - C40JKAT (Core 5 120U, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>26990000</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>28490000</v>
+        <v>34590000</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Display with ComfortView Wide viewing angle Chống chói Anti Glare | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1x Global headset jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD RGB | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Bảo mật vân tay | Công nghệ âm thanh:: Realtek ALC32xx | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 249.52 mm - Dày 17.37 mm - 1.98 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB Type-A 2 x USB Type-C (hỗ trợ DisplayPort 1.4, Power delivery 3.0, HP Sleep and Charge) 1 x Headphone/microphone combo LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 56 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-5-120u-71092481</t>
+          <t>https://www.thegioididong.com/laptop/hp-probook-4-g1ir-14-core-5-120u-c40jkat</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:13:42</t>
+          <t>2026-07-30 11:54:11</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 16 DC16250 - DC16250-C7U161W11BLU-27 (Core 7 150U, 16GB, 1TB, Full HD+, OfficeHS24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>35290000</v>
+          <t>Laptop Lenovo Gaming Legion 5 15AHP11 - 83Q7001HVN (R7 250, 16GB, 512GB, RTX 5050 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>55290000</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>35990000</v>
+        <v>55990000</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits ComfortView Plus | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.3 mm - Rộng 250.6 mm - Dày 18.23 mm - 2 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: Boost Clock 2662MHz, TGP 115W, 440 AI TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: 2.5K | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: DisplayHDR True Black 1000 | Cổng giao tiếp:: 1x Ethernet 2 x USB Type-C (USB4 40Gbps) hỗ trợ USB PD 65 - 100W và DisplayPort 1.4 1 x Headphone/ Microphone combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) 2×2 Bluetooth 6.0 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 244.5 mm - Rộng 344 mm - Dày 19~20 - 1.87 kg | Chất liệu:: Mặt trên: nhôm + Mặt dưới: nhựa PC-ABS</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-7-150u-dc16250-c7u161w11blu-27</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15ahp11-r7-250-83q7001hvn</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:13:56</t>
+          <t>2026-07-30 11:54:26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell Pro 14 PC14250 - PC14250-235U-16512WP-2Y (Ultra 5 235U, 16GB, 512GB, Full HD+, Win11Pro)</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>38290000</v>
+          <t>Laptop Lenovo Gaming Legion 5 15AHP11 - 83Q7001JVN (R7 250, 16GB, 512GB, RTX 5060 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>55490000</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>39990000</v>
+        <v>58990000</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 235U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 2.0 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1x Global headset jack 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4, USB Power Delivery 3.1 and DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 2TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WQXGA (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light 1000 nits (peak) G-Sync 500 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB4 Type-C (DisplayPort 1.4, Power Delivery) LAN (RJ45) HDMI 2.1 3 x USB A | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio Audio by HARMAN Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Legion ColdFont Hyper | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344 mm - Rộng 244.5 mm - Dày 19.95 mm - 1.87 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-pro-14-pc14250-ultra-5-235u-pc14250-235u-16512wp-2y</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15ahp11-r7-250-83q7001jvn</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:14:11</t>
+          <t>2026-07-30 11:54:41</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell Pro 14 PC14250 - PC14250-255U-32512WH-2Y (Ultra 7 255U, 32GB, 512GB, Full HD+, Win11)</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>55290000</v>
+          <t>Laptop Lenovo Gaming Legion 5 15IPH11 - 83RW0023VN (Ultra 7 356H, 16GB, 512GB, RTX 5060 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>59490000</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>56690000</v>
+        <v>64990000</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 2.0 GHz (Lên đến 5.2 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe trống) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1x Global headset jack 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4, USB Power Delivery 3.1 and DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 365H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 15.3" | Độ phân giải:: WQXGA (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light 1000 nits (peak) 500 nits typical G-Sync DisplayHDR True Black 1000 High Gaming Performance Flicker Free | Cổng giao tiếp:: 3 x USB Jack tai nghe 3.5 mm 1 x USB Type-C (USB Power Delivery, DisplayPort 2.1) LAN (RJ45) HDMI 2.1 1 x Thunderbolt 4 (hỗ trợ DisplayPort 2.1, Power Delivery) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đèn chuyển màu RGB - 24 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Realtek Audio Audio by HARMAN Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Legion ColdFont Hyper | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344 mm - Rộng 244.5 mm - Dày 19.95 mm - 1.87 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-pro-14-pc14250-ultra-7-255u-pc14250-255u-32512wh-2y</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15iph11-ultra-7-356h-83rw0023vn</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:14:25</t>
+          <t>2026-07-30 11:54:56</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell Pro 15 Essential PV15250 - PV15250-100U-8512W-2Y (Core 3 100U, 8GB, 512GB, Full HD, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr"/>
-      <c r="C37" s="2" t="inlineStr"/>
-      <c r="D37" s="2" t="inlineStr"/>
-      <c r="E37" s="2" t="inlineStr"/>
+          <t>Laptop Lenovo Gaming LOQ 15AHP11 - 83TN0040VN (R7 250, 16GB, 512GB, RTX 5050 8GB, WUXGA 165Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>43490000</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>46990000</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Rộng 358.5 mm - Dày 17.5 mm | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 2TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Low Blue Light G-Sync AMD Freesync 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm LAN (RJ45) HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) 3 x USB A | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344.9 mm - Rộng 254.83 mm - Dày 23.25 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-pro-15-essential-pv15250-core-3-100u-pv15250-100u-8512w-2y</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15ahp11-r7-250-83tn0040vn</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:14:39</t>
+          <t>2026-07-30 11:55:11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 15 fd1487TU - D0BH4PA (Ultra 5 125H, 24GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>22490000</v>
+          <t>Laptop Lenovo Gaming LOQ 15ARP10E - 83S0004FVN (R7 7735HS, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>34490000</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>24390000</v>
+        <v>40990000</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 125H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 24 GB | Loại RAM:: DDR5 (1 khe RAM) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB Type-A HDMI 1.4b 1 x USB Type - C (hỗ trợ Power Delivery, DisplayPort 1.4b, HP Sleep and Charge) 1 x Headphone/microphone combo | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.8 mm - Rộng 236 mm - Dày 18.6 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 7735HS | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 65 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: AMD Freesync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A 1x Ethernet 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery 3.0) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3 - cell Li-ion, 57.5 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 359.2 mm - Rộng 236 mm - Dày 22.95 mm - 1.8 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-15-fd1487tu-ultra-5-125h-d0bh4pa</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15arp10e-r7-7735hs-83s0004fvn</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:14:51</t>
+          <t>2026-07-30 11:55:25</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 15 fd2126TU - D72CBPA (Ultra 5 225U, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>22990000</v>
+          <t>Laptop Lenovo Gaming LOQ 15IPH11 - 83SL000LVN (Ultra 7 356H, 16GB, 512GB, RTX 5060 8GB, WUXGA 165Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>51490000</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>26990000</v>
+        <v>55990000</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: Hãng không công bố | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB Type-A 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack HDMI | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.8 mm - Rộng 236 mm - Dày 18.6 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 365H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 1TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Low Blue Light G-Sync AMD Freesync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 3 x USB Jack tai nghe 3.5 mm LAN (RJ45) HDMI 2.1 1 x Thunderbolt 4 (hỗ trợ DisplayPort 2.1, Power Delivery) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344.9 mm - Rộng 254.83 mm - Dày 23.25 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-15-fd2126tu-ultra-5-225u-d72cbpa</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15iph11-ultra-7-356h-83sl000lvn</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:15:04</t>
+          <t>2026-07-30 11:55:40</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 15 fd2127TU - D72CCPA (Ultra 5 225U, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>22990000</v>
+          <t>Laptop Lenovo Gaming LOQ 15IRX9 - 83DV01H2VN (i7 13645HX, 16GB, 1TB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>34590000</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>26990000</v>
+        <v>36990000</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.40 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 2800 MHz | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB Type-A HDMI 1.4b 1 x USB Type - C (hỗ trợ Power Delivery 3.1, DisplayPort 1.4b, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.8 mm - Rộng 236 mm - Dày 18.6 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13645HX | Số nhân:: 14 | Số luồng:: 20 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 150 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD NVMe M.2 PCIe Gen 4.0x4 (2242) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1x Ethernet 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.86 mm - Rộng 258.7 mm - Dày 23.9 mm - 2.38 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-15-fd2127tu-ultra-5-225u-d72ccpa</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15irx9-i7-13645hx-83dv01h2vn</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:15:19</t>
+          <t>2026-07-30 11:55:55</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 240R G10 - C3SG9AT (Core 5 120U, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>20490000</v>
+          <t>Laptop Lenovo Gaming LOQ 15IRX9 - 83DV01H3VN (i7 13645HX, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>34590000</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>23590000</v>
+        <v>36490000</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack HDMI | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HP TrueVision Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 323.7 mm - Rộng 215 mm - Dày 13.2 mm - 1.404 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13645HX | Số nhân:: 14 | Số luồng:: 20 | Tốc độ CPU:: 2.60 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 105 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1x Ethernet 3 x USB 3.2 Gen 1 HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.86 mm - Rộng 258.7 mm - Dày 23.9 mm - 2.38 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-240r-g10-core-5-120u-c3sg9at</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15irx9-i7-13645hx-83dv01h3vn</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:15:33</t>
+          <t>2026-07-30 11:56:12</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 240R G10 - CC9B9PT (Core 7 150U, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>23990000</v>
+          <t>Laptop Lenovo Gaming LOQ Essential 15ARP10E - 83S0000DVN (R5 7535HS, 16GB, 512GB, RTX 3050 6GB, Full HD 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>24190000</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>29590000</v>
+        <v>35990000</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>-19%</t>
+          <t>-33%</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x USB Type-C (Power Delivery, DisplayPort 1.4, HP Sleep and Charge) 2 x USB Type-A HDMI 1.4b 1 x Headphone/ Microphone combo audio jack | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 323.7 mm - Rộng 215 mm - Dày 13.2 mm - 1.406 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 7535HS | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.30 GHz (Lên đến 4.55 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 6 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 65 W | Hiệu năng xử lý AI (TOPS):: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB onboard + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: AMD Freesync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery 3.0) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hyper Champer Cooling | Thông tin Pin:: 4-cell Li-ion, 57.5 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 359.2 mm - Rộng 236 mm - Dày 22.95 mm - 1.8 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-240r-g10-core-7-150u-cc9b9pt</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-essential-15arp10e-r5-7535hs-83s0000dvn</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:15:48</t>
+          <t>2026-07-30 11:56:25</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 240R G9 - C40LGAT (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>24490000</v>
+          <t>Laptop Lenovo IdeaPad 5 2in1 14IPH11 - 83UG0026VN (Ultra 5 322, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>30590000</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>26590000</v>
+        <v>32990000</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HP TrueVision Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324 mm - Rộng 225.9 mm - Dày 9.4 mm - 1.406 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.6 mm - Rộng 224.9 mm - Dày 17.4 mm - 1.54 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-240r-g9-core-5-120u-c40lgat</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-5-2in1-14iph11-ultra-5-322-83ug0026vn</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:16:03</t>
+          <t>2026-07-30 11:56:40</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 240R G9 - C40M2AT (Core 5 120U, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>18990000</v>
+          <t>Laptop Lenovo IdeaPad 5 2in1 14IPH11 - 83UG0027VN (Ultra 7 355, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>35590000</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>23590000</v>
+        <v>37990000</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>-19%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HP TrueVision Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324 mm - Rộng 225.9 mm - Dày 9.4 mm - 1.406 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.6 mm - Rộng 224.9 mm - Dày 17.4 mm - 1.54 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-240r-g9-core-5-120u-c40m2at</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-5-2in1-14iph11-ultra-7-355-83ug0027vn</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:16:16</t>
+          <t>2026-07-30 11:56:54</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 240R G9 - AX3C6AT (i3 1315U, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>14490000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 14ARP10 - 83K600E6VN (R5 7535HS, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>19690000</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>16390000</v>
+        <v>24990000</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i3 Raptor Lake - 1315U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.50 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324 mm - Rộng 225.9 mm - Dày 9.4 mm - 1.397 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 7533HS | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.30 GHz (Lên đến 4.55 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 660M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 1TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.39 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-240r-g9-i3-1315u-ax3c6at</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14arp10-r5-7535hs-83k600e6vn</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:16:31</t>
+          <t>2026-07-30 11:57:09</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP EliteBook 6 G1a 14 - C0CE1PT (R5 AI 340, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>30190000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 14ARP10 - 83K6005WVN (R7 7735HS, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>19690000</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>31590000</v>
+        <v>26990000</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-27%</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.528 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 7735HS | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 680M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.39 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r5-ai-340-c0ce1pt</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14arp10-r7-7735hs-83k6005wvn</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:16:46</t>
+          <t>2026-07-30 11:57:23</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP EliteBook 6 G1a 14 - C0CF2PT (R5 AI 340, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>31190000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IPH11 - 83UQ003NVN (Ultra 5 322, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>25390000</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>32590000</v>
+        <v>27990000</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.528 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.43 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r5-ai-340-c0cf2pt</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iph11-ultra-5-322-83uq003nvn</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:17:01</t>
+          <t>2026-07-30 11:57:37</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP EliteBook 6 G1a 14 - C0CE2PT (R7 AI 350, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>34290000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IPH11 - 83UQ003PVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>30090000</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>35690000</v>
+        <v>32990000</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2461,939 +2454,939 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.549 kg | Chất liệu:: Nắp lưng và chiếu nghỉ tay bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.43 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r7-ai-350-c0ce2pt</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iph11-ultra-7-355-83uq003pvn</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:17:16</t>
+          <t>2026-07-30 11:57:52</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP EliteBook 6 G1a 14 - C0CG2PT (R7 AI 350, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>33290000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002NVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>24190000</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>34690000</v>
+        <v>26490000</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.531 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r7-ai-350-c0cg2pt</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002nvn</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:17:30</t>
+          <t>2026-07-30 11:58:07</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP EliteBook 8 G1a 14 - C0CE5PT (R7 AI PRO 350, 32GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>37790000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002PVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>20790000</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>39190000</v>
+        <v>22990000</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x USB 3.2. 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1 x Headphone/microphone combo 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 62 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 315.6 mm - Rộng 222 mm - Dày 15.5 mm - 1.564 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-8-g1a-14-ai-350-c0ce5pt</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002pvn</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:17:44</t>
+          <t>2026-07-30 11:58:22</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP EliteBook 8 G1a 14 - C0CE3PT (R5 AI PRO 340, 32GB, 512GB, WUXGA, Cảm ứng, Win11 Pro)</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>40790000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 15ARP10 - 83K700YUVN (R5 7535HS, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>18690000</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>42190000</v>
+        <v>24990000</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 Pro - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x USB A 2 x Thunderbolt 4 (Hỗ trợ Power Delivery, DisplayPort 2.1, HP Sleep and Charge) 1 x Headphone/microphone combo HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 62 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 315.6 mm - Rộng 222 mm - Dày 15.5 mm - 1.39 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 7535HS | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.30 GHz (Lên đến 4.55 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 660M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe RAM) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB Type-C 3.2 Gen 1 (hỗ trợ DisplayPort 1.2 và Power delivery 3.0) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Nắp lưng và chiếu nghỉ tay bằng nhôm</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-8-g1a-14-r5-ai-pro-340-c0ce3pt</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15arp10-r5-7535hs-83k700yuvn</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:17:58</t>
+          <t>2026-07-30 11:58:37</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP EliteBook 8 G1a 14 - C0CE6PT (R7 AI PRO 350, 32GB, 512GB, WUXGA, Cảm ứng, Win11 Pro)</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n">
-        <v>44790000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 15ARP10 - 83K700YVVN (R7 7735HS, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>19890000</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>46190000</v>
+        <v>26990000</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 Pro - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x USB 3.2. 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1 x Headphone/microphone combo 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 62 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 315.6 mm - Rộng 222 mm - Dày 15.5 mm - 1.558 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 7735HS | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 660M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-8-g1a-14-r7-ai-pro-350-c0ce6pt</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15arp10-r7-7735hs-83k700yvvn</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:18:13</t>
+          <t>2026-07-30 11:58:51</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP Gaming HyperX Omen 15 ga0092TX - D72D8PA (i5 14450HX, 16GB, 512GB, RTX 5050 8GB, WUXGA 165Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="n">
-        <v>45590000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IPH11 - 83UR00A4VN (Ultra 5 322, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>24990000</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>46990000</v>
+        <v>27990000</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 421 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.37 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 2.50 GHz (Lên đến 4.40 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.63 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-gaming-hyperx-omen-15-ga0092tx-i5-14450hx-d72d8pa</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iph11-ultra-5-322-83ur00a4vn</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:18:28</t>
+          <t>2026-07-30 11:59:06</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP Gaming VICTUS 15 fa2451TX - D17WPPA (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n">
-        <v>27490000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IPH11 - 83UR0075VN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>28990000</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>31990000</v>
+        <v>32990000</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35W - 115W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x USB 3.2 1 x USB 3.2 (hỗ trợ HP Sleep and Charge) 1 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358 mm - Rộng 255 mm - Dày 23.5 mm - 2.29 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4 1 x USB Type-C (hỗ trợ USB, Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.63 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-gaming-victus-15-fa2451tx-i5-13420h-d17wppa</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iph11-ultra-7-355-83ur0075vn</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:18:41</t>
+          <t>2026-07-30 11:59:22</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP HyperX Omen 15 ga0091TX - D72D7PA (i5 14450HX, 16GB, 512GB, RTX 5060 8GB, WUXGA 165Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n">
-        <v>48590000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IPH11 - 83UR00A5VN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>29490000</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>49990000</v>
+        <v>32990000</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3840 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 614 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.363 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.63 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-hyperx-omen-15-ga0091tx-i5-14450h-d72d7pa</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iph11-ultra-7-355-83ur00a5vn</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:18:55</t>
+          <t>2026-07-30 11:59:37</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP OmniBook 7 Aero 13 bg1087AU - BZ7S1PA (R5 AI 340, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n">
-        <v>27990000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00A8VN (Core 3 304, 8GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>18990000</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>29790000</v>
+        <v>20890000</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCie Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4TB) | Kích thước màn hình:: 13.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 400 nits | Cổng giao tiếp:: 2 x USB Type-A 2 x USB Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/microphone combo HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E MT7922 Bluetooth 5.3 | Webcam:: HP 5MP Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Poly Studio HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 43 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 297.3 mm - Rộng 211.2 mm - Dày 17.4 mm - 0.99 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core™ 3 - 304 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz (P-core), Turbo tối đa 4.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 2242 PCIe 4.0x4 NVMe | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 × USB-C (USB 5 Gbps), hỗ trợ USB PD 45–65W và DisplayPort 1.2 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Optimized with Dolby Audio 2W x 2 High Definition (HD) Audio Stereo speakers | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 240 mm - Rộng 343 mm - Dày 17 - 18 - 1.59 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-7-aero-13-bg1087au-r5-ai-340-bz7s1pa</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-3-304-83rr00a8vn</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:19:08</t>
+          <t>2026-07-30 11:59:52</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus TUF Gaming FX608JHI - TU209W (i7 14650HX, 16GB, 512GB, RTX5050 8GB, Full HD+ 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n">
-        <v>41590000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00AAVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>23590000</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>42990000</v>
+        <v>26490000</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 500.000đ mua Chuột Gaming Logitech dòng Pro X | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 14650HX | Số nhân:: 16 | Số luồng:: 24 | Tốc độ CPU:: 2.20 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 2TB) 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB 72% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: AI noise-canceling technology Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 269 mm - Dày 27.3 mm - 2.2 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-tuf-gaming-fx608jhi-i7-14650hx-tu209w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00aavn</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:33:46</t>
+          <t>2026-07-30 12:00:07</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1404MA - EB028W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="n">
-        <v>26490000</v>
+          <t>Laptop Lenovo Ideapad Slim 3 15IWC11 - 83RR00CVVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>20190000</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>31990000</v>
+        <v>22990000</v>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Core i5 - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 SO-DIMM | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Hãng không công bố | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 21.39 mm - Rộng 32.49 mm - Dày 1.79 mm - 1.4 kg | Chất liệu:: Khung nhôm - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1404ma-core-5-320-eb028w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00cvvn</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:34:00</t>
+          <t>2026-07-30 12:00:23</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1404MA - EB219W (Core 5 320, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="n">
-        <v>21390000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US002TVN (Ultra 5 322, 24GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>30090000</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>26990000</v>
+        <v>31990000</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 8 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 324.9 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.409 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 24 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1404ma-core-5-320-eb219w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-5-322-83us002tvn</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:34:11</t>
+          <t>2026-07-30 12:00:38</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1407AA - LY360W (Ultra 5 325, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="n">
-        <v>23790000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US002WVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>30090000</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>26990000</v>
+        <v>32990000</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 325 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB onboard + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) Hỗ trợ thêm 1 khe cắm SSD NVMe M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 19.9 mm - 1.46 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1407aa-ultra-5-325-ly360w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-7-355-83us002wvn</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:34:25</t>
+          <t>2026-07-30 12:50:54</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1407CA - LY203W (Ultra 5 225H, 16GB, 512GB, WUXGA OLED, Win11)</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="n">
-        <v>23990000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US003YVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>29490000</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>33490000</v>
+        <v>32990000</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>-28%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 19.9 mm - 1.46 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1407ca-ultra-5-225h-ly203w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-7-355-83us003yvn</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:34:39</t>
+          <t>2026-07-30 12:51:10</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ385W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="n">
-        <v>26090000</v>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 - 83S1006RVN (R7 AI 445, 16GB, 512GB, WUXGA OLED, Win11)</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>30590000</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>31990000</v>
+        <v>32990000</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.0 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 2 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 2-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-5-320-bq385w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-14agp11-r7-ai-445-83s1006rvn</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:34:53</t>
+          <t>2026-07-30 12:51:24</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ632W (Core 5 320, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="n">
-        <v>21390000</v>
+          <t>Laptop Lenovo IdeaPad Slim 5 14IPH11 - 83S5004FVN (Ultra 7 355, 16GB, 512GB, WUXGA OLED, Win11)</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>34490000</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>26990000</v>
+        <v>37990000</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 8 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-5-320-bq632w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-14iph11-ultra-7-355-83s5004fvn</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:35:07</t>
+          <t>2026-07-30 12:51:39</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ395W (Core 7 350, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="n">
-        <v>28490000</v>
+          <t>Laptop Lenovo IdeaPad Slim 5 OLED 14IMH10 - 83V6001GVN (Ultra 5 135H, 16GB, 512GB, WUXGA OLED, Win11)</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>23690000</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>35490000</v>
+        <v>25990000</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Wildcat Lake - 350 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 17 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 135H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Hãng không công bố | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 mở rộng (nâng cấp tối đa 1 TB) 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (USB 5Gbps/USB 3.2 Gen 1), Always On 1 x USB-A (USB 5Gbps/USB 3.2 Gen 1) HDMI 2.1 2 x USB 3.2 Gen 2 Type-C (hỗ trợ Power Delivery 3.0, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.39 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-7-350-bq395w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-oled-14imh10-ultra-5-135h-83v6001gvn</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:35:20</t>
+          <t>2026-07-30 12:51:54</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ633W (Core 7 350, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="n">
-        <v>25190000</v>
+          <t>Laptop Lenovo IdeaPad Slim 5 OLED 14IPH11 - 83S5000DVN (Ultra 5 322, 16GB, 512GB, WUXGA OLED, Win11)</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>29490000</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>30490000</v>
+        <v>32990000</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Wildcat Lake - 350 | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 8 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD NVMe M.2 PCIe Gen 4.0 mở rộng (2280) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 2 x USB Type-C 3.2 (hỗ trợ truyền dữ liệu, Power Delivery 3.0, and DisplayPort 1.2) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Nắp lưng và mặt đáy bằng nhôm</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-7-350-bq633w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-oled-14iph11-ultra-5-322-83s5000dvn</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:35:35</t>
+          <t>2026-07-30 12:52:08</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 16 X1607CA - MB387W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="n">
-        <v>24590000</v>
+          <t>Laptop Lenovo ThinkBook 14 G9 - 21V0005PVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>28290000</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>33490000</v>
+        <v>31190000</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>-27%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.7 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 SO-DIMM | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 25.06 mm - Rộng 35.7 mm - Dày 1.79 ~ 1.99 - 1.88 kg | Chất liệu:: Khung nhôm - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-16-x1607ca-ultra-5-225h-mb387w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-g9-r7-250-21v0005pvn</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:35:49</t>
+          <t>2026-07-30 12:52:22</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook Go 14 E1404FA - EB012W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="n">
-        <v>16590000</v>
+          <t>Laptop Lenovo ThinkBook 14 Gen 9 IRL - 21UY008TVN (i5 13420H, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>27290000</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>22990000</v>
+        <v>28890000</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>-28%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb012w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-gen-9-irl-i5-13420h-21uy008tvn</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:36:00</t>
+          <t>2026-07-30 12:52:35</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook Go 14 E1404FA - EB1832W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="n">
-        <v>16990000</v>
+          <t>Laptop Lenovo ThinkBook 16 G9 - 21UT005MVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>29690000</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>22990000</v>
+        <v>31590000</v>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>-26%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356 mm - Rộng 253.5 mm - Dày 17.5 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb1832w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-16-g9-r7-250-21ut005mvn</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:36:13</t>
+          <t>2026-07-30 12:52:50</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook S 16 S3607VA - RP155W (Core 5 210H, 16GB, 512GB, Full HD+ 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="n">
-        <v>30090000</v>
+          <t>Laptop Lenovo ThinkPad E14 Gen 7 - 21SX00BNVN (Ultra 5 135H, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>29690000</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>34990000</v>
+        <v>31590000</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Hãng không công bố | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare LED Backlit | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 259.6 mm - Dày 15.9 mm - 1.7 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 135H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.60 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x USB-A (USB 10Gbps/USB 3.2 Gen 2), Always On 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Audio by HARMAN Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 19.7 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-s-16-s3607va-core-5-210h-rp155w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-5-135h-21sx00bnvn</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:36:27</t>
+          <t>2026-07-30 12:53:05</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook S14 S3407AA - SF945W (Ultra 5 325, 16GB, 512GB, WUXGA OLED, Win11)</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="n">
-        <v>29790000</v>
+          <t>Laptop Lenovo ThinkPad E14 Gen 7 - 21SX005NVN (Ultra 5 225U, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>31490000</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>31990000</v>
+        <v>33890000</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
@@ -3402,342 +3395,342 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - Đang cập nhật | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Đang cập nhật | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 95% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 17.9 mm - 1.4 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4 với USB Power Delivery và DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Audio by HARMAN Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 19.7 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-s14-s3407aa-ultra-5-325-sf945w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-5-225u-21sx005nvn</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:36:52</t>
+          <t>2026-07-30 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook S14 S3407VA - LY256W (Core 7 240H, 16GB, 512GB, WUXGA OLED, Win11)</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="n">
-        <v>26990000</v>
+          <t>Laptop Lenovo ThinkPad X9 14 Gen 1 - 21QA006JVN (Ultra 7 258V, 32GB, 512GB, WUXGA OLED, Win11Pro)</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>53290000</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>29990000</v>
+        <v>55190000</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 17.9 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.80 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Chống chói Anti Glare Dolby Vision 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm HDMI 2.1 2 x USB-C (hỗ trợ Thunderbolt 4/USB 4, USB Power Delivery và DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.8 mm - Rộng 212.3 mm - Dày 17.18 mm - 1.21 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-s14-s3407va-core-7-240h-ly256w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-x9-14-gen-1-ultra-7-258v-21qa006jvn</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:37:06</t>
+          <t>2026-07-30 12:53:32</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Zenbook 14 UM3406GA - QD075W (R7 AI 445, 16GB, 512GB, WUXGA OLED, Win11)</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="n">
-        <v>34490000</v>
+          <t>Laptop Lenovo V14 G5 - 83HD0035VN (Core7 240H, 16G, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>26990000</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>39990000</v>
+        <v>28590000</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.0 GHz | NPU:: AMD XDNA | Card màn hình:: Card tích hợp | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 70% Less harmful blue light 400 nits 600 nits (Khi bật HDR) | Cổng giao tiếp:: 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 75 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.01 mm - Rộng 31.24 mm - Dày 1.49 mm - 1.2 kg | Chất liệu:: Nhôm nguyên khối</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) LAN (RJ45) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Ion, 47 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324.2 mm - Rộng 215.2 mm - Dày 17.9 mm - 1.37 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-zenbook-14-um3406ga-r7-ai-445-qd075w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-v14-g5-core7-240h-83hd0035vn</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:37:20</t>
+          <t>2026-07-30 12:53:47</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Zenbook A14 UX3407NA - QD132WS (X2E 88 100, 16GB, 512GB, WUXGA OLED, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="n">
-        <v>44490000</v>
+          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002LVN (Ultra 5 322, 16GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>37490000</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>48990000</v>
+        <v>39990000</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Snapdragon X2 Elite - X2E88100 | Số nhân:: 18 | Số luồng:: 18 | Tốc độ CPU:: Lên đến 4.0 GHz khi tải nặng | NPU:: Qualcomm Hexagon | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | Card màn hình:: Card tích hợp - Qualcomm Adreno GPU | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 9523 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: VESA DisplayHDR Thời gian phản hồi 0.2 ms Màn hình bảo vệ mắt - EYE CARE Low Blue Light Chống chói Anti Glare 400 nits 600 nits (Khi bật HDR) 1.07 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Công nghệ Smart AMP | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.7 mm - Rộng 213.9 mm - Dày 15.9 mm - 0.986 kg | Chất liệu:: Vỏ gốm nhôm Ceraluminum</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.45 mm - 1.38 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-zenbook-a14-ux3407na-x2e-88-100-qd132ws</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-5-322-83tc002lvn</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:37:37</t>
+          <t>2026-07-30 12:54:03</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Zenbook A14 UX3407NA - QD254W (X2E 88 100, 32GB, 1TB, WUXGA OLED, Win11)</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="n">
-        <v>58190000</v>
+          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002MVN (Ultra 7 355, 32GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>54490000</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>63990000</v>
+        <v>57990000</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Snapdragon X2 Elite - X2E88100 | Số nhân:: 18 | Số luồng:: 18 | Tốc độ CPU:: Lên đến 4.0 GHz khi tải nặng | NPU:: Qualcomm Hexagon | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | Card màn hình:: Card tích hợp - Qualcomm Adreno GPU | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 9523 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: VESA DisplayHDR Thời gian phản hồi 0.2 ms Màn hình bảo vệ mắt - EYE CARE Low Blue Light Chống chói Anti Glare 400 nits 600 nits (Khi bật HDR) 1.07 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Công nghệ Smart AMP | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.7 mm - Rộng 213.9 mm - Dày 15.9 mm - 0.986 kg | Chất liệu:: Vỏ gốm nhôm Ceraluminum</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.95 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-zenbook-a14-ux3407na-x2e-88-100-qd254w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-7-355-83tc002mvn</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:37:50</t>
+          <t>2026-07-30 12:54:17</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Zenbook S 16 UM5606GA - SS441W (R9 AI 465, 16GB, 512GB, 3K OLED 120Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="n">
-        <v>44990000</v>
+          <t>Laptop Lenovo Yoga 7 2in1 OLED 14IPH11 - 83TC002JVN (Ultra 7 355, 32GB, 1TB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>53490000</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>49490000</v>
+        <v>57990000</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 9 - 465 | Số nhân:: 10 | Số luồng:: 20 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Màn hình bảo vệ mắt - EYE CARE Low Blue Light DisplayHDR True Black 1000 500 nits Chống chói Anti Glare 1100 nits (peak) | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Công nghệ Smart AMP | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 83 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 353.6 mm - Rộng 243 mm - Dày 12.9 mm - 1.5 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Tiêu chuẩn Nền Intel Evo | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.45 mm - 1.38 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-zenbook-s-16-um5606ga-r9-ai-465-ss441w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-oled-14iph11-ultra-7-355-83tc002jvn</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:38:04</t>
+          <t>2026-07-30 12:54:31</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC14250-C3U085W11SLU-27 (Core 3 100U, 8GB, 512GB, Full HD+, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="n">
-        <v>18990000</v>
+          <t>Laptop Lenovo Yoga Slim 7 OLED 14AGP11 - 83QS001DVN (R7 AI 445, 16GB, 512GB, WUXGA OLED, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>37490000</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>19390000</v>
+        <v>39990000</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits ComfortView Plus | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 8000 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Glossy Display Chuẩn DisplayHDR True Black 500 Eyesafe Dolby Vision 400 nits X-Rite Flicker Free | Cổng giao tiếp:: 1 x USB Type-C (hỗ trợ DisplayPort 1.4) 2 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 221 mm - Dày 13.9 mm - 1.15 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-3-100u-dc14250-c3u085w11slu-27</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-oled-14agp11-r7-ai-445-83qs001dvn</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:38:19</t>
+          <t>2026-07-30 12:54:44</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC4C5375W1-2Y (Core 5 120U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="n">
-        <v>30990000</v>
+          <t>Laptop Lenovo Yoga Slim 7 OLED 14IPH11 - 83QM002FVN (Ultra 7 355, 32GB, 1TB, WUXGA OLED, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>52490000</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>32090000</v>
+        <v>55990000</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226 mm - Dày 18 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe 600nits (peak) Dolby Vision 400 nits X-Rite Flicker Free | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 2-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 221 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-5-120u-dc4c5375w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-oled-14iph11-ultra-7-355</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:38:32</t>
+          <t>2026-07-30 12:54:58</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - 71092478 (Core 7 150U, 16GB, 512GB, Full HD+ 120Hz, OfficeHS24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="n">
-        <v>27990000</v>
+          <t>Laptop MacBook Pro 14 inch M5 Pro 48GB/1TB</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>84990000</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>28390000</v>
+        <v>85490000</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
@@ -3746,1073 +3739,1067 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm giá 500,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Phiếu mua hàng Chuột, Bàn phím (Apple) trị giá 500,000đ | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng 50.000đ mua Chuột Logitech M240 | Tặng Phiếu mua hàng Balo, Túi chống sốc (giá trị trên 1,000,000đ) trị giá 300,000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.20 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Display with ComfortView Wide viewing angle Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD RGB | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Cirrus Logic CS42L43 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-Po, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 320 mm - Rộng 215.97 mm - Dày 18.02 mm - 1.83 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Apple M5 Pro | Số nhân:: 15 | Số luồng:: Hãng không công bố | Tốc độ CPU:: 307 GB/s memory bandwidth | Card màn hình:: Card tích hợp - 16 nhân GPU | RAM:: 48 GB | Loại RAM:: Hãng không công bố | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 1 TB SSD | Kích thước màn hình:: 14.2" | Độ phân giải:: Liquid Retina XDR display (3024 x 1964) | Tần số quét:: up to 120 Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: ProMotion Độ sáng XDR: toàn màn hình 1000 nits, cao nhất 1600 nits (chỉ nội dung HDR) Độ sáng SDR: lên đến 1000 nits Wide color (P3) True Tone Technology 1 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm MagSafe 3 3 x Thunderbolt 5 (hỗ trợ DisplayPort, Thunderbolt 5 (up to 120Gb/s), USB 4 (up to 120Gb/s)) HDMI | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Khe đọc thẻ nhớ:: SDXC | Webcam:: Camera 12MP Center Stage | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Hệ thống âm thanh 6 loa Spatial Audio 3 microphones Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-Po, 72.4 Wh | Hệ điều hành:: macOS Tahoe | Thời điểm ra mắt:: 03/2026 | Kích thước:: Dài 312.6 mm - Rộng 221.2 mm - Dày 15.5 mm - 1.6 kg | Chất liệu:: Vỏ nhôm tái chế 100% | Hãng:: MacBook. Xem thông tin hãng</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-71092478</t>
+          <t>https://www.thegioididong.com/laptop/macbook-pro-14-inch-m5-pro-48gb-1tb</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:38:46</t>
+          <t>2026-07-30 12:55:12</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - 71100515 (Core 7 150U, 16GB, 512GB, Full HD+ 120Hz, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="n">
-        <v>34790000</v>
+          <t>Laptop MacBook Pro 14 inch M5 Pro 48GB/2TB</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>98690000</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>35490000</v>
+        <v>99190000</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm giá 500,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Phiếu mua hàng Chuột, Bàn phím (Apple) trị giá 500,000đ | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng 50.000đ mua Chuột Logitech M240 | Tặng Phiếu mua hàng Balo, Túi chống sốc (giá trị trên 1,000,000đ) trị giá 300,000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 320 mm - Rộng 215.97 mm - Dày 18.02 mm - 1.83 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Apple M5 Pro | Số nhân:: 15 | Số luồng:: Hãng không công bố | Tốc độ CPU:: 307 GB/s memory bandwidth | Card màn hình:: Card tích hợp - 16 nhân GPU | RAM:: 48 GB | Loại RAM:: Hãng không công bố | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 2 TB SSD | Kích thước màn hình:: 14.2" | Độ phân giải:: Liquid Retina XDR display (3024 x 1964) | Tần số quét:: up to 120 Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: ProMotion Độ sáng XDR: toàn màn hình 1000 nits, cao nhất 1600 nits (chỉ nội dung HDR) Độ sáng SDR: lên đến 1000 nits Wide color (P3) True Tone Technology 1 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm MagSafe 3 3 x Thunderbolt 5 (hỗ trợ DisplayPort, Thunderbolt 5 (up to 120Gb/s), USB 4 (up to 120Gb/s)) HDMI | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Khe đọc thẻ nhớ:: SDXC | Webcam:: Camera 12MP Center Stage | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Hệ thống âm thanh 6 loa Spatial Audio 3 microphones Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-Po, 72.4 Wh | Hệ điều hành:: macOS Tahoe | Thời điểm ra mắt:: 03/2026 | Kích thước:: Dài 312.6 mm - Rộng 221.2 mm - Dày 15.5 mm - 1.6 kg | Chất liệu:: Vỏ nhôm tái chế 100% | Hãng:: MacBook. Xem thông tin hãng</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-71100515</t>
+          <t>https://www.thegioididong.com/laptop/macbook-pro-14-inch-m5-pro-48gb-2tb</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:39:00</t>
+          <t>2026-07-30 12:55:25</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC14250-C7U161W11SLU-27 (Core 7 150U, 16GB, 1TB, Full HD+, OfficeHS24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="n">
-        <v>29490000</v>
+          <t>Laptop MSI Gaming Cyborg 15 Black Edition A13VE - A13VE-2410VN (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>27990000</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>29890000</v>
+        <v>31990000</v>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.60 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Công nghệ âm thanh:: Hi-Res Audio DTS Audio | Tản nhiệt:: Cooler Boost 1 x Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 53.5 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.36 mm - Rộng 250.34 mm - Dày 22.9 mm - 1.98 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-dc14250-c7u161w11slu-27</t>
+          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-black-edition-a13ve-i5-13420h-a13ve-2410vn</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:39:15</t>
+          <t>2026-07-30 12:55:39</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC14250-C7U161W11SLU-2Y (Core 7 150U, 16GB, 1TB, Full HD+ ,OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="n">
-        <v>37290000</v>
+          <t>Laptop MSI Gaming Cyborg 15 C13WEO-417VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>35590000</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>37990000</v>
+        <v>36990000</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: E-core: 0.9 GHz - 3.3 GHz, P-core: 1.2 GHz - 4.7 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MT/s | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 PCIe Gen 4 x 4 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (M.2 2230)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Display with ComfortView Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.615 mm - Rộng 31.4 mm - Dày 1.669 ~ 1.807 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card rời - Intel UHD Graphics (tích hợp) + NVIDIA GeForce RTX 5050 GPU, 8GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB Type-A 1 x Headphone/ Microphone combo audio jack 1 x USB Type C (chỉ hỗ trợ Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: DTS Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.98 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-dc14250-c7u161w11slu-2y</t>
+          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-c13weo-417vn-i7-13620h</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:39:28</t>
+          <t>2026-07-30 12:55:52</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14255 - 71092477 (R7 350, 16GB, 1TB, Full HD+, OfficeHS24+365B, Win11)</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="n">
-        <v>32490000</v>
+          <t>Laptop MSI Gaming Raider 16 MAX HX B2WI - 095VN (Ultra 9 290HX Plus, 64GB, 2TB, RTX 5080 16GB, QHD+ OLED 240Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>1350000</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>33190000</v>
+        <v>1590000</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB onboard + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Display with ComfortView Wide viewing angle Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3204 Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-Po, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày `19.9 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 9 Arrow Lake - 290HX Plus | Số nhân:: 24 | Số luồng:: 24 | Tốc độ CPU:: 2.70 GHz (Lên đến 5.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 1334 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5080, 16 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 175 W | RAM:: 64 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe 32 GB) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: 128 GB | Ổ cứng:: 2 TB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 4 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: QHD+ (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 240Hz | Độ phủ màu:: 100% DCI-P3 | Cổng giao tiếp:: 2 x Thunderbolt 4 (hỗ trợ Power Delivery 3.1 và DisplayPort) 3 x USB Type-A 3.2 Gen 2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Cooler Boost 3 Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-Po, 91.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 363 mm - Rộng 269.7 mm - Dày 28.85 mm - 2.6 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14255-r7-350-71092477</t>
+          <t>https://www.thegioididong.com/laptop/msi-gaming-raider-16-max-hx-b2wi-ultra-9-290hx-plus-095vn</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:39:42</t>
+          <t>2026-07-30 12:56:06</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - 71100520 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="n">
-        <v>21990000</v>
+          <t>Laptop MSI Modern 15 F1MG-1264VN (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>19990000</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>22590000</v>
+        <v>22390000</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort 1.4, Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Bluetooth 5.0 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.5 mm - Dày 18.9 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core thế hệ 12 - 120U | Số nhân:: Hãng không công bố | Số luồng:: 12 | Tốc độ CPU:: 1.45 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (2280) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: Hãng không công bố | Cổng giao tiếp:: 3 x USB 3.2 Gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell, 46.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.7 kg | Chất liệu:: Plastic (nhựa dẻo)</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-71100520</t>
+          <t>https://www.thegioididong.com/laptop/msi-modern-15-f1mg-1264vn-core-5-120u</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:39:56</t>
+          <t>2026-07-30 12:56:20</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - CPH993 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="n">
-        <v>21990000</v>
+          <t>Laptop SingPC M16-i382 (i3 1215U, 8GB, 256GB, WUXGA, Win11 Pro)</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>13890000</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>22590000</v>
+        <v>15190000</v>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: Đang cập nhật | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 70% Less harmful blue light 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 16.96 mm đến 18.99 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i3 Alder Lake - 1215U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.2GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 256 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-cph993</t>
+          <t>https://www.thegioididong.com/laptop/singpc-m16-i382-i3-1215u</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:40:10</t>
+          <t>2026-07-30 12:56:33</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - DC5C3259W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="n">
-        <v>21990000</v>
+          <t>Laptop SingPC M16-i595 (i5 1235U, 16GB, 512GB, WUXGA, Win11 Pro)</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>18390000</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>22590000</v>
+        <v>19990000</v>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Alder Lake - 1235U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.30 GHz (Lên đến 4.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 72% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3259w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/singpc-m16-i595-i5-1235u</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 14:40:24</t>
+          <t>2026-07-30 12:56:46</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AG15-52P-52WT - NX.JWKSV.001 (Ultra 5 115U, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="n">
-        <v>21690000</v>
+          <t>Laptop Asus TUF Gaming FX608JHI - TU209W (i7 14650HX, 16GB, 512GB, RTX5050 8GB, Full HD+ 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>41590000</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>24990000</v>
+        <v>42990000</v>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 500.000đ mua Chuột Gaming Logitech dòng Pro X | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 115U | Số nhân:: 8 | Số luồng:: 10 | Tốc độ CPU:: 1.5 GHz (Lên đến 4.2 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB onboard + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 2 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357.5 mm - Rộng 229 mm - Dày 17.95 mm - 1.59 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 14650HX | Số nhân:: 16 | Số luồng:: 24 | Tốc độ CPU:: 2.20 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 2TB) 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB 72% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: AI noise-canceling technology Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 269 mm - Dày 27.3 mm - 2.2 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-go-15-ag15-52p-52wt-ultra-5-115u-nx-jwksv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-tuf-gaming-fx608jhi-i7-14650hx-tu209w</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:38:34</t>
+          <t>2026-07-30 10:55:59</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP - NX.DMCSV.003 (R7 7730U, 8GB, 512GB, Full HD+, Win11)</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="n">
-        <v>20990000</v>
+          <t>Laptop Asus Vivobook 14 X1404MA - EB028W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>31990000</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>22990000</v>
+        <v>1590000</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 680M Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14.5" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB Type - C 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 324 mm - Rộng 227.6 mm - Dày 17.9 mm - 1.3 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Core i5 - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 SO-DIMM | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Hãng không công bố | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 21.39 mm - Rộng 32.49 mm - Dày 1.79 mm - 1.4 kg | Chất liệu:: Khung nhôm - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-14-al14-44p-r0sp-r7-7730u-nx-dmcsv-003</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1404ma-core-5-320-eb028w</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:38:47</t>
+          <t>2026-07-30 10:56:13</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-45P-R7Z3 - NX.DPESV.002 (R3 5400U, 8GB, 512GB, Full HD+, Win11)</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="n">
-        <v>14990000</v>
+          <t>Laptop Asus Vivobook 14 X1404MA - EB219W (Core 5 320, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>21390000</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>17990000</v>
+        <v>26990000</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 3 - 5400U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.60 GHz (Lên đến 4.0 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.8 mm - Rộng 219.7 mm - Dày 19.1 mm - 1.3 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 8 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 324.9 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.409 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-14-al14-45p-r7z3-r3-5400u-nx-dpesv-002</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1404ma-core-5-320-eb219w</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:39:02</t>
+          <t>2026-07-30 10:56:25</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W - NX.DNRSV.002 (R5 40, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="n">
-        <v>19590000</v>
+          <t>Laptop ASUS Vivobook 14 X1407AA - LY360W (Ultra 5 325, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>24890000</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>22990000</v>
+        <v>26990000</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 53 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360.66 mm - Rộng 234.8 mm - Dày 16.95 mm - 1.45 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 325 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB onboard + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) Hỗ trợ thêm 1 khe cắm SSD NVMe M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 19.9 mm - 1.46 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-21p-r91w-r5-40-nx-dnrsv-002</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1407aa-ultra-5-325-ly360w</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:39:16</t>
+          <t>2026-07-30 10:56:39</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN - NX.DDASV.001 (Core 3 N350, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="n">
-        <v>16990000</v>
+          <t>Laptop Asus Vivobook 14 X1407CA - LY203W (Ultra 5 225H, 16GB, 512GB, WUXGA OLED, Win11)</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>23990000</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>18990000</v>
+        <v>33490000</v>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-28%</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Twin Lake - N350 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 3.90 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB 3.2 HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.0 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357.8 mm - Rộng 235.6 mm - Dày 19.7 mm - 1.53 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 19.9 mm - 1.46 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-36p-30tn-core-3-n350-nx-ddasv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1407ca-ultra-5-225h-ly203w</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:39:30</t>
+          <t>2026-07-30 10:56:52</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-44P-R4UH - NX.DJVSV.002 (R7 7730U, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="n">
-        <v>21990000</v>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ385W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>26090000</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>23990000</v>
+        <v>31990000</v>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB Type - C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 230.2 mm - Dày 18.6 mm - 1.49 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-44p-r4uh-r7-7730u-nx-djvsv-002</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-5-320-bq385w</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:39:43</t>
+          <t>2026-07-30 10:57:05</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-46P-R73C - NX.JXMSV.001 (R3 5400U, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="n">
-        <v>14490000</v>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ632W (Core 5 320, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>21390000</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>17990000</v>
+        <v>26990000</v>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>-19%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 3 - 5400U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.60 GHz (Lên đến 4.0 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 3.2. 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) 1 x USB 3.2 Gen 2 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 53 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360.66 mm - Rộng 234.8 mm - Dày 16.95 mm - 1.45 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 8 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-46p-r73c-r3-5400u-nx-jxmsv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-5-320-bq632w</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:39:57</t>
+          <t>2026-07-30 10:57:21</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-48P-R86Q - NX.DS1SV.002 (R7 5825U, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="n">
-        <v>18990000</v>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ395W (Core 7 350, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>28490000</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>21990000</v>
+        <v>35490000</v>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 5825U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) 1 x USB 3.2 Gen 2 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360.66 mm - Rộng 234.8 mm - Dày 16.95 mm - 1.45 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Wildcat Lake - 350 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 17 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-48p-r86q-r7-5825u-nx-ds1sv-002</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-7-350-bq395w</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:40:11</t>
+          <t>2026-07-30 10:57:34</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-49P-R6XX - NX.DRZSV.002 (R5 7430U, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="n">
-        <v>17990000</v>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ633W (Core 7 350, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="n">
+        <v>25190000</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>20990000</v>
+        <v>30490000</v>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 7430U | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) 1 x USB 3.2 Gen 2 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360.66 mm - Rộng 234.8 mm - Dày 16.95 mm - 1.45 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Wildcat Lake - 350 | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 8 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-49p-r6xx-r5-7430u-nx-drzsv-002</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-7-350-bq633w</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:40:24</t>
+          <t>2026-07-30 10:57:47</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC - NX.DG3SV.002.16G (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="n">
-        <v>21990000</v>
+          <t>Laptop Asus Vivobook 16 X1607CA - MB387W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="n">
+        <v>24590000</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>24990000</v>
+        <v>33490000</v>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-27%</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 357.6 mm - Rộng 228.5 mm - Dày 18.7 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.7 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 SO-DIMM | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 25.06 mm - Rộng 35.7 mm - Dày 1.79 ~ 1.99 - 1.88 kg | Chất liệu:: Khung nhôm - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-53p-56ec-core-5-120u-nx-dg3sv-002-16g</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-16-x1607ca-ultra-5-225h-mb387w</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:40:40</t>
+          <t>2026-07-30 10:58:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH - NX.DG3SV.001 (Core 5 120U, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="n">
-        <v>20990000</v>
+          <t>Laptop Asus Vivobook Go 14 E1404FA - EB012W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>16990000</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>24990000</v>
+        <v>22990000</v>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD WVA | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3x Type-A USB 3.2 Gen 1 1 x USB Type-C 3.2 gen 1 (hỗ trợ truyền dữ liệu và Power Delivery) HDMI 1.4 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) Wi-Fi Dual Band | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357.6 mm - Rộng 228.5 mm - Dày 18.7 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-53p-56qh-core-5-120u-nx-dg3sv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb012w</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:40:54</t>
+          <t>2026-07-30 10:58:12</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AL16-71P-582Q - NX.DRSSV.001 (Ultra 5 125H, 16GB, 512GB, Full HD+ 120Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="n">
-        <v>23990000</v>
+          <t>Laptop Asus Vivobook Go 14 E1404FA - EB1832W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>22990000</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>26990000</v>
+        <v>1590000</v>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 125H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357 mm - Rộng 245.5 mm - Dày 18.9 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-16-al16-71p-582q-ultra-5-125h-nx-drssv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb1832w</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:41:07</t>
+          <t>2026-07-30 10:58:25</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Aspire 7 A715-59G-59RD - NH.DXUSV.001 (Core 5 210H, 16GB, 512GB, RTX 3050 4GB, Fulll HD 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="n">
-        <v>25990000</v>
+          <t>Laptop Asus Vivobook S 16 S3607VA - RP155W (Core 5 210H, 16GB, 512GB, Full HD+ 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="n">
+        <v>31490000</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>31990000</v>
+        <v>34990000</v>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>-19%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 4 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35W - 80W | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 4 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle 350 nits Acer ComfyView | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C (hỗ trợ DisplayPort 1.4) LAN (RJ45) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn LED - 15 chế độ màu | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 359.5 mm - Rộng 238 mm - Dày 22.7 mm - 1.99 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Hãng không công bố | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare LED Backlit | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 259.6 mm - Dày 15.9 mm - 1.7 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-aspire-7-a715-59g-59rd-core-5-210h-nh-dxusv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-s-16-s3607va-core-5-210h-rp155w</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:41:21</t>
+          <t>2026-07-30 10:58:40</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel AN16S-61-R9CN - NH.QXGSV.001 (Ryzen AI 7 350, 16GB, 512GB, RTX 5070 8GB, 2K+ 180Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="n">
-        <v>55990000</v>
-      </c>
-      <c r="C99" s="2" t="n">
-        <v>59990000</v>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+          <t>Laptop Asus Vivobook S14 S3407AA - SF945W (Ultra 5 325, 16GB, 512GB, WUXGA OLED, Win11)</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="n">
+        <v>31990000</v>
+      </c>
+      <c r="C99" s="2" t="inlineStr"/>
+      <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.0 GHz (Lên đến 5.2 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe mở rộng (nâng cấp tối đa 2 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits 3ms | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: NVIDIA Optimus | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 19.9 mm - 2.18 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - Đang cập nhật | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Đang cập nhật | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 95% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 17.9 mm - 1.4 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-an16s-61-r9cn-ryzen-ai-7-350-nh-qxgsv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-s14-s3407aa-ultra-5-325-sf945w</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:41:35</t>
+          <t>2026-07-30 10:58:53</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-73Z8 - NH.QUASV.001 (Core 7 240H, 16GB, 512GB, RTX 4050 6GB, Full HD  180Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="n">
-        <v>37290000</v>
+          <t>Laptop Asus Vivobook S14 S3407VA - LY256W (Core 7 240H, 16GB, 512GB, WUXGA OLED, Win11)</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="n">
+        <v>28090000</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>37990000</v>
+        <v>29990000</v>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số luồng:: 16 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: IPS | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1x Ethernet 3 x USB 3.2 Gen 1 Type-A 1 x USB Type-C (65W) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: 720p at 30 fps HD camera Camera with Dual Microphone | Đèn bàn phím:: Đơn sắc - Màu cam | Công nghệ âm thanh:: Windows Spatial Sound High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 17.9 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-73z8-core-7-240h-nh-quasv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-s14-s3407va-core-7-240h-ly256w</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:41:49</t>
+          <t>2026-07-30 10:59:07</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV16-72-71T9 - NH.QUNSV.001 (Core 7 240H, 16GB, 512GB, RTX 5060 8GB, WUXGA 180Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="n">
-        <v>43990000</v>
+          <t>Laptop Asus Zenbook 14 UM3406GA - QD075W (R7 AI 445, 16GB, 512GB, WUXGA OLED, Win11)</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="n">
+        <v>34490000</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>45990000</v>
+        <v>39990000</v>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 95 W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD WVA NVIDIA Advanced Optimus | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 2 x USB 3.2 gen 2 Type-A LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (2 x 2) Wi-Fi Dual Band | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu cam | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio High SNR DAC with 2.1 Vrms out capability Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 360 mm - Rộng 274.5 mm - Dày 24.5 mm - 2.4 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.0 GHz | NPU:: AMD XDNA | Card màn hình:: Card tích hợp | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 70% Less harmful blue light 400 nits 600 nits (Khi bật HDR) | Cổng giao tiếp:: 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 75 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.01 mm - Rộng 31.24 mm - Dày 1.49 mm - 1.2 kg | Chất liệu:: Nhôm nguyên khối</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16-72-71t9-core-7-240h-nh-qunsv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-zenbook-14-um3406ga-r7-ai-445-qd075w</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:42:04</t>
+          <t>2026-07-30 10:59:21</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-61-R0B8 - NH.QXQSV.001 (Ryzen AI 5 340, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="n">
-        <v>43990000</v>
+          <t>Laptop Asus Zenbook A14 UX3407NA - QD132WS (X2E 88 100, 16GB, 512GB, WUXGA OLED, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n">
+        <v>44490000</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>47990000</v>
+        <v>48990000</v>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.40 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Snapdragon X2 Elite - X2E88100 | Số nhân:: 18 | Số luồng:: 18 | Tốc độ CPU:: Lên đến 4.0 GHz khi tải nặng | NPU:: Qualcomm Hexagon | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | Card màn hình:: Card tích hợp - Qualcomm Adreno GPU | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 9523 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: VESA DisplayHDR Thời gian phản hồi 0.2 ms Màn hình bảo vệ mắt - EYE CARE Low Blue Light Chống chói Anti Glare 400 nits 600 nits (Khi bật HDR) 1.07 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Công nghệ Smart AMP | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.7 mm - Rộng 213.9 mm - Dày 15.9 mm - 0.986 kg | Chất liệu:: Vỏ gốm nhôm Ceraluminum</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-61-r0b8-ryzen-ai-5-340-nh-qxqsv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-zenbook-a14-ux3407na-x2e-88-100-qd132ws</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:42:19</t>
+          <t>2026-07-30 10:59:36</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-71-58WQ - NH.QXBSV.001 (Core 5 210H, 16GB, 512GB, RTX 5050 8GB, 2K+ 180Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="n">
-        <v>42990000</v>
+          <t>Laptop Asus Zenbook A14 UX3407NA - QD254W (X2E 88 100, 32GB, 1TB, WUXGA OLED, Win11)</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>58190000</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>46990000</v>
+        <v>63990000</v>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
@@ -4821,342 +4808,324 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Snapdragon X2 Elite - X2E88100 | Số nhân:: 18 | Số luồng:: 18 | Tốc độ CPU:: Lên đến 4.0 GHz khi tải nặng | NPU:: Qualcomm Hexagon | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | Card màn hình:: Card tích hợp - Qualcomm Adreno GPU | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 9523 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: VESA DisplayHDR Thời gian phản hồi 0.2 ms Màn hình bảo vệ mắt - EYE CARE Low Blue Light Chống chói Anti Glare 400 nits 600 nits (Khi bật HDR) 1.07 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Công nghệ Smart AMP | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.7 mm - Rộng 213.9 mm - Dày 15.9 mm - 0.986 kg | Chất liệu:: Vỏ gốm nhôm Ceraluminum</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-71-58wq-core-5-210h-nh-qxbsv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-zenbook-a14-ux3407na-x2e-88-100-qd254w</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:42:33</t>
+          <t>2026-07-30 10:59:50</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Predator Helios Neo 16 PHN16-I31-50H7 - NH.U4SSV.001 (i5 14450HX, 32GB, 512GB, RTX 5050 8GB, Full HD+ 180Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="n">
-        <v>49990000</v>
-      </c>
-      <c r="C104" s="2" t="n">
-        <v>61990000</v>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>-19%</t>
-        </is>
-      </c>
+          <t>Laptop Asus Zenbook S 16 UM5606GA - SS441W (R9 AI 465, 16GB, 512GB, 3K OLED 120Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="n">
+        <v>49490000</v>
+      </c>
+      <c r="C104" s="2" t="inlineStr"/>
+      <c r="D104" s="2" t="inlineStr"/>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe mở rộng (nâng cấp tối đa 2 TB) 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 2 x Thunderbolt 4 with USB Type - C (hỗ trợ DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Hi-Res Audio Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Quạt kim loại 3D AeroBlade 2 quạt | Tính năng khác:: NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 26.75 mm - 2.5 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 9 - 465 | Số nhân:: 10 | Số luồng:: 20 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Màn hình bảo vệ mắt - EYE CARE Low Blue Light DisplayHDR True Black 1000 500 nits Chống chói Anti Glare 1100 nits (peak) | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Công nghệ Smart AMP | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 83 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 353.6 mm - Rộng 243 mm - Dày 12.9 mm - 1.5 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16-phn16-i31-50h7-i5-14450hx-nh-u4ssv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-zenbook-s-16-um5606ga-r9-ai-465-ss441w</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:42:48</t>
+          <t>2026-07-30 11:00:03</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Predator Helios Neo 16 PHN16-I31-72XE - NH.U4RSV.001 (i7 14650HX, 32GB, 512GB, RTX5060 8GB, 2K+ 180Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="n">
-        <v>59990000</v>
+          <t>Laptop Dell 14 DC14250 - DC14250-C3U085W11SLU-27 (Core 3 100U, 8GB, 512GB, Full HD+, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="n">
+        <v>19190000</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>71990000</v>
+        <v>19390000</v>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 14650HX | Số nhân:: 16 | Số luồng:: 24 | Tốc độ CPU:: 2.20 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe mở rộng (nâng cấp tối đa 2 TB) 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 2 x Thunderbolt 4 with USB Type - C (hỗ trợ DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Hi-Res Audio Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Quạt kim loại 3D AeroBlade 2 quạt | Tính năng khác:: NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 26.75 mm - 2.5 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits ComfortView Plus | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16-phn16-i31-72xe-i7-14650hx-nh-u4rsv-001</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-3-100u-dc14250-c3u085w11slu-27</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:43:02</t>
+          <t>2026-07-30 11:00:18</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Predator Helios Neo 16 PHN16-I31-74MN - NH.U4SSV.002 (i7 14650HX, 32GB, 512GB, RTX 5050 8GB, Full HD+ 180Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="n">
-        <v>54990000</v>
+          <t>Laptop Dell 14 DC14250 - DC4C5375W1-2Y (Core 5 120U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="n">
+        <v>30990000</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>66990000</v>
+        <v>32090000</v>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 14650HX | Số nhân:: 16 | Số luồng:: 24 | Tốc độ CPU:: 2.20 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView NVIDIA Advanced Optimus | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1x Ethernet 2 x Thunderbolt 4 with USB Type - C (hỗ trợ DisplayPort 2.1) 2 x USB 3.2 gen 2 Type-A HDMI 2.1 | Kết nối không dây:: Bluetooth 5.4 + LE Wi-Fi 6E (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Hi-Res certification Windows Spatial Sound High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Quạt kim loại 3D AeroBlade 2 quạt | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 26.75 mm - 2.5 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226 mm - Dày 18 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16-phn16-i31-74mn-i7-14650hx-nh-u4ssv-002</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-5-120u-dc4c5375w1-2y</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:43:16</t>
+          <t>2026-07-30 11:00:32</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Predator Helios Neo 16S PHN16S-I51-97T9 - NH.U3SSV.006 (Ultra 9 386H, 16GB, 512GB, RTX 5070 8GB, 2K+ 165Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="n">
-        <v>73990000</v>
-      </c>
-      <c r="C107" s="2" t="n">
-        <v>77990000</v>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>-5%</t>
-        </is>
-      </c>
+          <t>Laptop Dell 14 DC14250 - 71092478 (Core 7 150U, 16GB, 512GB, Full HD+ 120Hz, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>28390000</v>
+      </c>
+      <c r="C107" s="2" t="inlineStr"/>
+      <c r="D107" s="2" t="inlineStr"/>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 9 Panther Lake - 386H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 50 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: LED-backlit TFT LCD 500 nits Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 18.9 mm - 2.2 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.20 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Display with ComfortView Wide viewing angle Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD RGB | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Cirrus Logic CS42L43 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-Po, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 320 mm - Rộng 215.97 mm - Dày 18.02 mm - 1.83 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16s-phn16s-i51-97t9-ultra-9-386h</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-71092478</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:43:37</t>
+          <t>2026-07-30 11:00:45</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Nitro ProPanel ANV15-52-50RB - NH.QUASV.002 (Core 5 210H, 16GB, 512GB, RTX 4050 6GB, Full HD 180Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="n">
-        <v>35990000</v>
+          <t>Laptop Dell 14 DC14250 - 71100515 (Core 7 150U, 16GB, 512GB, Full HD+ 120Hz, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="n">
+        <v>35490000</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>37990000</v>
+        <v>1590000</v>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 60W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 300 nits Acer ComfyView 3ms | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2 microphones Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Tính năng khác:: Copilot Key | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 320 mm - Rộng 215.97 mm - Dày 18.02 mm - 1.83 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv15-52-50rb-core-5-210h-nh-quasv-002</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-71100515</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:43:50</t>
+          <t>2026-07-30 11:00:58</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP - NX.JZHSV.003 (Ultra 7 358H, 32GB, 1TB, 2.8K 120Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="n">
-        <v>47590000</v>
-      </c>
-      <c r="C109" s="2" t="n">
-        <v>50990000</v>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+          <t>Laptop Dell 14 DC14250 - DC14250-C7U161W11SLU-27 (Core 7 150U, 16GB, 1TB, Full HD+, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="n">
+        <v>29890000</v>
+      </c>
+      <c r="C109" s="2" t="inlineStr"/>
+      <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra X7 - 358H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 9600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: 2.8K (2880 x 1800) - OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 ACER CineCrystal WVA | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A HDMI 2.1 2 x USB-C (hỗ trợ Thunderbolt 4/USB 4, USB Power Delivery và DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res certification High SNR DAC with 2.1 Vrms out capability Công nghệ Smart AMP Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-ion, 71 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.5 mm - Rộng 218.9 mm - Dày 15.6 mm - 1.12 kg | Chất liệu:: Vỏ hợp kim Nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-swift-go-14-ai-sfg14-i71-70rp-ultra-7-358h-nx-jzhsv-003</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-dc14250-c7u161w11slu-27</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:44:04</t>
+          <t>2026-07-30 11:01:12</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming ROG Strix G16 G614PM - TS147W (R9 8940HX, 16GB, 512GB, RTX 5060 8GB, WQXGA 300Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="n">
-        <v>49990000</v>
+          <t>Laptop Dell 14 DC14250 - DC14250-C7U161W11SLU-2Y (Core 7 150U, 16GB, 1TB, Full HD+ ,OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="n">
+        <v>37990000</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>52990000</v>
+        <v>1590000</v>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115W - 140W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.288 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 7 - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: E-core: 0.9 GHz - 3.3 GHz, P-core: 1.2 GHz - 4.7 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MT/s | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 PCIe Gen 4 x 4 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (M.2 2230)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Display with ComfortView Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.615 mm - Rộng 31.4 mm - Dày 1.669 ~ 1.807 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pm-r9-8940hx-ts147w</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-dc14250-c7u161w11slu-2y</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:44:18</t>
+          <t>2026-07-30 11:01:26</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming ROG Strix G16 G614PR - TS103W (R9 8940HX, 16GB, 512GB, RTX 5070Ti 12GB, WQXGA 300Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="n">
-        <v>70590000</v>
+          <t>Laptop Dell 14 DC14255 - 71092477 (R7 350, 16GB, 1TB, Full HD+, OfficeHS24+365B, Win11)</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="n">
+        <v>32490000</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>71990000</v>
+        <v>33190000</v>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
@@ -5165,127 +5134,127 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070Ti, 12 GB | Số nhân GPU:: 5888 CUDA Cores | Công suất đồ hoạ - TGP:: 140 W | Hiệu năng xử lý AI (TOPS):: Lên đến 992 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.34 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB onboard + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Display with ComfortView Wide viewing angle Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3204 Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-Po, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày `19.9 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pr-r9-8940hx-ts103w</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14255-r7-350-71092477</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:44:32</t>
+          <t>2026-07-30 11:01:41</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming ROG Zephyrus GA403GM - SY004W (R9 AI 465, 32GB, 1TB, RTX 5060 8GB, 3K OLED 120Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="n">
-        <v>64590000</v>
+          <t>Laptop Dell 15 DC15250 - 71100520 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="n">
+        <v>21990000</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>65990000</v>
+        <v>22590000</v>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 9 - 465 | Số nhân:: 10 | Số luồng:: 20 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 623 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Anti-Reflective G-Sync ROG Nebula HDR Display 1000 nits Dolby Vision | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, G-SYNC) 1 x USB4 Type-C (hỗ trợ DisplayPort, Power Delivery) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 73 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311 mm - Rộng 220 mm - Dày 16.3 mm - 1.5 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort 1.4, Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Bluetooth 5.0 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.5 mm - Dày 18.9 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-zephyrus-ga403gm-r9-ai-465-sy004w</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-71100520</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:44:45</t>
+          <t>2026-07-30 11:01:54</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus TUF Gaming F16 FX608JHI - TU210W (i5 14450HX, 16GB, 512GB,RTX 5050 8GB, WUXGA 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="n">
-        <v>40990000</v>
+          <t>Laptop Dell 15 DC15250 - CPH993 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="n">
+        <v>21990000</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>47990000</v>
+        <v>22590000</v>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 2TB) 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 72% NTSC | Công nghệ màn hình:: G-Sync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 3 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: FHD 1080p | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Dolby Atmos | Tản nhiệt:: 2 quạt | Tính năng khác:: MUX Switch NVIDIA Optimus Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 269 mm - Dày 27.3 mm - 2.2 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: Đang cập nhật | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 70% Less harmful blue light 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 16.96 mm đến 18.99 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-tuf-gaming-f16-fx608jhi-i5-14450hx-tu210w</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-cph993</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:44:59</t>
+          <t>2026-07-30 11:02:07</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus TUF Gaming FA401EA - RG034W (RYZEN AI MAX+ 392, 64GB, 1TB, WQXGA 165Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="n">
-        <v>62990000</v>
+          <t>Laptop Dell 15 DC15250 - DC5C3259W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="n">
+        <v>21990000</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>64990000</v>
+        <v>22590000</v>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
@@ -5294,1034 +5263,1014 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI Max+ - 392 | Số nhân:: 12 | Số luồng:: 24 | Tốc độ CPU:: 3.2 GHz (Lên đến 5.0 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 8060S Graphics | RAM:: 64 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8000 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 2 x USB 3.2 gen 2 Type-A 1 x USB Type-C USB 4 (hỗ trợ DisplayPort và Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hi-Res certification AI noise-canceling technology Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 73 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311 mm - Rộng 227 mm - Dày 19.9 mm - 1.48 kg | Chất liệu:: Nắp lưng và chiếu nghỉ tay bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-tuf-gaming-fa401ea-ryzen-ai-max-392-rg034w</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3259w1-2y</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 11:45:13</t>
+          <t>2026-07-30 11:02:20</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP OmniBook X Flip 14 fk0082AU - BZ7N8PA (R7 AI 350, 32GB, 1TB, 2K, Cảm ứng, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="n">
-        <v>39890000</v>
-      </c>
-      <c r="C115" s="2" t="n">
-        <v>40890000</v>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
+          <t>Laptop Dell 15 DC15250 - DC5C3851W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>22590000</v>
+      </c>
+      <c r="C115" s="2" t="inlineStr"/>
+      <c r="D115" s="2" t="inlineStr"/>
+      <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: 2K (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Corning Gorilla Glass 3 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB Type-C (hỗ trợ truyền dữ liệu, DisplayPort 2.1, Power delivery 3.1, HP Sleep and Charge) Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E MT7922 Bluetooth 5.3 | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ | Thông tin Pin:: 3-cell Li-Po, 59 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 218.5 mm - Dày 14.6 mm - 1.39 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x Headphone/ Microphone combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 2 x USB 2.0 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 235 mm - Rộng 358.5 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-x-flip-14-fk0082au-r7-ai-350-bz7n8pa</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3851w1-2y</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:46:34</t>
+          <t>2026-07-30 12:57:41</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP Probook 4 G1ah 16 - C40JPAT (R5 220, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="n">
-        <v>25490000</v>
+          <t>Laptop Dell 15 DC15250 - CPH992 (i5 1334U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365B, Win11)</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="n">
+        <v>21990000</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>29890000</v>
+        <v>23490000</v>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 220 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 48 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x USB Type-C 3.2 Gen 2 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: FHD 1080p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 359.4 mm - Rộng 251 mm - Dày 17 mm - 1.785 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 1334U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 2666 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Bluetooth 5.0 Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235.6 mm - Dày 19 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-probook-4-g1ah-16-r5-220-c40jpat</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-i5-1334u-cph992</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:46:50</t>
+          <t>2026-07-30 12:57:55</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP ProBook 4 G1iR 14 - C40JKAT (Core 5 120U, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="n">
-        <v>26990000</v>
+          <t>Laptop Dell 15 DC15250 - DC15250-i5U165W11SLU-27 (i5 1334U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="n">
+        <v>21990000</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>34590000</v>
+        <v>23490000</v>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>-22%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB Type-A 2 x USB Type-C (hỗ trợ DisplayPort 1.4, Power delivery 3.0, HP Sleep and Charge) 1 x Headphone/microphone combo LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 56 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 1334U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.30 GHz (Lên đến 4.60 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm HDD SATA (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 18.99 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-probook-4-g1ir-14-core-5-120u-c40jkat</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-i5-1334u-dc15250-i5u165w11slu-27</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:47:03</t>
+          <t>2026-07-30 12:58:09</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming Legion 5 15AHP11 - 83Q7001HVN (R7 250, 16GB, 512GB, RTX 5050 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="n">
-        <v>55290000</v>
+          <t>Laptop Dell 15 DC15250 - DC15250-i7U161W11SLU-27 (i7 1355U, 16GB, 1TB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="n">
+        <v>26990000</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>55990000</v>
+        <v>27490000</v>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: Boost Clock 2662MHz, TGP 115W, 440 AI TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: 2.5K | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: DisplayHDR True Black 1000 | Cổng giao tiếp:: 1x Ethernet 2 x USB Type-C (USB4 40Gbps) hỗ trợ USB PD 65 - 100W và DisplayPort 1.4 1 x Headphone/ Microphone combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) 2×2 Bluetooth 6.0 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 244.5 mm - Rộng 344 mm - Dày 19~20 - 1.87 kg | Chất liệu:: Mặt trên: nhôm + Mặt dưới: nhựa PC-ABS</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 1355U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.70 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-Po, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 18.99 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15ahp11-r7-250-83q7001hvn</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-i7-1355u-dc15250-i7u161w11slu-27</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:47:18</t>
+          <t>2026-07-30 12:58:23</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming Legion 5 15AHP11 - 83Q7001JVN (R7 250, 16GB, 512GB, RTX 5060 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="n">
-        <v>55490000</v>
+          <t>Laptop Dell 15 DC15255 - DC5R5973W1-2Y (R5 7530U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="n">
+        <v>24990000</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>58990000</v>
+        <v>25690000</v>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 2TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WQXGA (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light 1000 nits (peak) G-Sync 500 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB4 Type-C (DisplayPort 1.4, Power Delivery) LAN (RJ45) HDMI 2.1 3 x USB A | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio Audio by HARMAN Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Legion ColdFont Hyper | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344 mm - Rộng 244.5 mm - Dày 19.95 mm - 1.87 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 7530U | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/microphone combo 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15ahp11-r7-250-83q7001jvn</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r5-7530u-dc5r5973w1-2y</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:47:32</t>
+          <t>2026-07-30 12:58:37</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming Legion 5 15IPH11 - 83RW0023VN (Ultra 7 356H, 16GB, 512GB, RTX 5060 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="n">
-        <v>59490000</v>
+          <t>Laptop Dell 16 DC16250 - 71092481 (Core 5 120U, 16GB, 1TB, Full HD+, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="n">
+        <v>27990000</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>64990000</v>
+        <v>28490000</v>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 365H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 15.3" | Độ phân giải:: WQXGA (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light 1000 nits (peak) 500 nits typical G-Sync DisplayHDR True Black 1000 High Gaming Performance Flicker Free | Cổng giao tiếp:: 3 x USB Jack tai nghe 3.5 mm 1 x USB Type-C (USB Power Delivery, DisplayPort 2.1) LAN (RJ45) HDMI 2.1 1 x Thunderbolt 4 (hỗ trợ DisplayPort 2.1, Power Delivery) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đèn chuyển màu RGB - 24 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Realtek Audio Audio by HARMAN Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Legion ColdFont Hyper | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344 mm - Rộng 244.5 mm - Dày 19.95 mm - 1.87 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Display with ComfortView Wide viewing angle Chống chói Anti Glare | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1x Global headset jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD RGB | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Bảo mật vân tay | Công nghệ âm thanh:: Realtek ALC32xx | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 249.52 mm - Dày 17.37 mm - 1.98 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15iph11-ultra-7-356h-83rw0023vn</t>
+          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-5-120u-71092481</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:47:45</t>
+          <t>2026-07-30 12:58:51</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming LOQ 15AHP11 - 83TN0040VN (R7 250, 16GB, 512GB, RTX 5050 8GB, WUXGA 165Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="n">
-        <v>43490000</v>
+          <t>Laptop Dell 16 DC16250 - DC16250-C7U161W11BLU-27 (Core 7 150U, 16GB, 1TB, Full HD+, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="n">
+        <v>35290000</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>46990000</v>
+        <v>35990000</v>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 2TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Low Blue Light G-Sync AMD Freesync 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm LAN (RJ45) HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) 3 x USB A | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344.9 mm - Rộng 254.83 mm - Dày 23.25 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits ComfortView Plus | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.3 mm - Rộng 250.6 mm - Dày 18.23 mm - 2 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15ahp11-r7-250-83tn0040vn</t>
+          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-7-150u-dc16250-c7u161w11blu-27</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:47:58</t>
+          <t>2026-07-30 12:59:04</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming LOQ 15ARP10E - 83S0004FVN (R7 7735HS, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="n">
-        <v>34490000</v>
+          <t>Laptop Dell Pro 14 PC14250 - PC14250-235U-16512WP-2Y (Ultra 5 235U, 16GB, 512GB, Full HD+, Win11Pro)</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="n">
+        <v>38290000</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>40990000</v>
+        <v>39990000</v>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7735HS | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 65 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: AMD Freesync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A 1x Ethernet 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery 3.0) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3 - cell Li-ion, 57.5 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 359.2 mm - Rộng 236 mm - Dày 22.95 mm - 1.8 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 235U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 2.0 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1x Global headset jack 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4, USB Power Delivery 3.1 and DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15arp10e-r7-7735hs-83s0004fvn</t>
+          <t>https://www.thegioididong.com/laptop/dell-pro-14-pc14250-ultra-5-235u-pc14250-235u-16512wp-2y</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:48:12</t>
+          <t>2026-07-30 12:59:18</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming LOQ 15IPH11 - 83SL000LVN (Ultra 7 356H, 16GB, 512GB, RTX 5060 8GB, WUXGA 165Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="n">
-        <v>51490000</v>
+          <t>Laptop Dell Pro 14 PC14250 - PC14250-255U-32512WH-2Y (Ultra 7 255U, 32GB, 512GB, Full HD+, Win11)</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="n">
+        <v>55290000</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>55990000</v>
+        <v>56690000</v>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 365H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 1TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Low Blue Light G-Sync AMD Freesync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 3 x USB Jack tai nghe 3.5 mm LAN (RJ45) HDMI 2.1 1 x Thunderbolt 4 (hỗ trợ DisplayPort 2.1, Power Delivery) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344.9 mm - Rộng 254.83 mm - Dày 23.25 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 2.0 GHz (Lên đến 5.2 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe trống) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1x Global headset jack 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4, USB Power Delivery 3.1 and DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15iph11-ultra-7-356h-83sl000lvn</t>
+          <t>https://www.thegioididong.com/laptop/dell-pro-14-pc14250-ultra-7-255u-pc14250-255u-32512wh-2y</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:48:25</t>
+          <t>2026-07-30 12:59:33</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming LOQ 15IRX9 - 83DV01H2VN (i7 13645HX, 16GB, 1TB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="n">
-        <v>34590000</v>
-      </c>
-      <c r="C124" s="2" t="n">
-        <v>36990000</v>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
+          <t>Laptop Dell Pro 15 Essential PV15250 - PV15250-100U-8512W-2Y (Core 3 100U, 8GB, 512GB, Full HD, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="n">
+        <v>23990000</v>
+      </c>
+      <c r="C124" s="2" t="inlineStr"/>
+      <c r="D124" s="2" t="inlineStr"/>
+      <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13645HX | Số nhân:: 14 | Số luồng:: 20 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 150 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD NVMe M.2 PCIe Gen 4.0x4 (2242) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1x Ethernet 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.86 mm - Rộng 258.7 mm - Dày 23.9 mm - 2.38 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Rộng 358.5 mm - Dày 17.5 mm | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15irx9-i7-13645hx-83dv01h2vn</t>
+          <t>https://www.thegioididong.com/laptop/dell-pro-15-essential-pv15250-core-3-100u-pv15250-100u-8512w-2y</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:48:39</t>
+          <t>2026-07-30 12:59:47</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming LOQ 15IRX9 - 83DV01H3VN (i7 13645HX, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="n">
-        <v>34590000</v>
+          <t>Laptop HP 15 fd1487TU - D0BH4PA (Ultra 5 125H, 24GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="n">
+        <v>22490000</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>36490000</v>
+        <v>24390000</v>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13645HX | Số nhân:: 14 | Số luồng:: 20 | Tốc độ CPU:: 2.60 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 105 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1x Ethernet 3 x USB 3.2 Gen 1 HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.86 mm - Rộng 258.7 mm - Dày 23.9 mm - 2.38 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 125H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 24 GB | Loại RAM:: DDR5 (1 khe RAM) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB Type-A HDMI 1.4b 1 x USB Type - C (hỗ trợ Power Delivery, DisplayPort 1.4b, HP Sleep and Charge) 1 x Headphone/microphone combo | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.8 mm - Rộng 236 mm - Dày 18.6 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15irx9-i7-13645hx-83dv01h3vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-15-fd1487tu-ultra-5-125h-d0bh4pa</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:48:53</t>
+          <t>2026-07-30 12:59:59</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming LOQ Essential 15ARP10E - 83S0000DVN (R5 7535HS, 16GB, 512GB, RTX 3050 6GB, Full HD 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="n">
-        <v>24190000</v>
+          <t>Laptop HP 15 fd2126TU - D72CBPA (Ultra 5 225U, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="n">
+        <v>22990000</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>35990000</v>
+        <v>26990000</v>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>-33%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 7535HS | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.30 GHz (Lên đến 4.55 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 6 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 65 W | Hiệu năng xử lý AI (TOPS):: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB onboard + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: AMD Freesync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery 3.0) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hyper Champer Cooling | Thông tin Pin:: 4-cell Li-ion, 57.5 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 359.2 mm - Rộng 236 mm - Dày 22.95 mm - 1.8 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: Hãng không công bố | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB Type-A 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack HDMI | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.8 mm - Rộng 236 mm - Dày 18.6 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-essential-15arp10e-r5-7535hs-83s0000dvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-15-fd2126tu-ultra-5-225u-d72cbpa</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:49:06</t>
+          <t>2026-07-30 13:00:14</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad 5 2in1 14IPH11 - 83UG0026VN (Ultra 5 322, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="n">
-        <v>30590000</v>
+          <t>Laptop HP 15 fd2127TU - D72CCPA (Ultra 5 225U, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="n">
+        <v>22990000</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>32990000</v>
+        <v>26990000</v>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.6 mm - Rộng 224.9 mm - Dày 17.4 mm - 1.54 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.40 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 2800 MHz | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB Type-A HDMI 1.4b 1 x USB Type - C (hỗ trợ Power Delivery 3.1, DisplayPort 1.4b, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.8 mm - Rộng 236 mm - Dày 18.6 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-5-2in1-14iph11-ultra-5-322-83ug0026vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-15-fd2127tu-ultra-5-225u-d72ccpa</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:49:21</t>
+          <t>2026-07-30 13:00:29</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad 5 2in1 14IPH11 - 83UG0027VN (Ultra 7 355, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="n">
-        <v>35590000</v>
+          <t>Laptop HP 240R G10 - C3SG9AT (Core 5 120U, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="n">
+        <v>20490000</v>
       </c>
       <c r="C128" s="2" t="n">
-        <v>37990000</v>
+        <v>23590000</v>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.6 mm - Rộng 224.9 mm - Dày 17.4 mm - 1.54 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack HDMI | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HP TrueVision Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 323.7 mm - Rộng 215 mm - Dày 13.2 mm - 1.404 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-5-2in1-14iph11-ultra-7-355-83ug0027vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-240r-g10-core-5-120u-c3sg9at</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:49:34</t>
+          <t>2026-07-30 13:00:47</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14ARP10 - 83K600E6VN (R5 7535HS, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="n">
-        <v>19690000</v>
+          <t>Laptop HP 240R G10 - CC9B9PT (Core 7 150U, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="n">
+        <v>23990000</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>24990000</v>
+        <v>29590000</v>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-19%</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 7533HS | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.30 GHz (Lên đến 4.55 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 660M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 1TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.39 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x USB Type-C (Power Delivery, DisplayPort 1.4, HP Sleep and Charge) 2 x USB Type-A HDMI 1.4b 1 x Headphone/ Microphone combo audio jack | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 323.7 mm - Rộng 215 mm - Dày 13.2 mm - 1.406 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14arp10-r5-7535hs-83k600e6vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-240r-g10-core-7-150u-cc9b9pt</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:49:49</t>
+          <t>2026-07-30 13:01:02</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14ARP10 - 83K6005WVN (R7 7735HS, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="n">
-        <v>19690000</v>
+          <t>Laptop HP 240R G9 - C40LGAT (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="n">
+        <v>24490000</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>26990000</v>
+        <v>26590000</v>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>-27%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7735HS | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 680M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.39 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HP TrueVision Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324 mm - Rộng 225.9 mm - Dày 9.4 mm - 1.406 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14arp10-r7-7735hs-83k6005wvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-240r-g9-core-5-120u-c40lgat</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:50:02</t>
+          <t>2026-07-30 13:01:18</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IPH11 - 83UQ003NVN (Ultra 5 322, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="n">
-        <v>25390000</v>
+          <t>Laptop HP 240R G9 - C40M2AT (Core 5 120U, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="n">
+        <v>18990000</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>27990000</v>
+        <v>23590000</v>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-19%</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.43 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HP TrueVision Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324 mm - Rộng 225.9 mm - Dày 9.4 mm - 1.406 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iph11-ultra-5-322-83uq003nvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-240r-g9-core-5-120u-c40m2at</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:50:17</t>
+          <t>2026-07-30 13:01:32</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IPH11 - 83UQ003PVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="n">
-        <v>30090000</v>
+          <t>Laptop HP 240R G9 - AX3C6AT (i3 1315U, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="n">
+        <v>14490000</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>32990000</v>
+        <v>16390000</v>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.43 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i3 Raptor Lake - 1315U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.50 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324 mm - Rộng 225.9 mm - Dày 9.4 mm - 1.397 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iph11-ultra-7-355-83uq003pvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-240r-g9-i3-1315u-ax3c6at</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:50:31</t>
+          <t>2026-07-30 13:01:47</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002NVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="n">
-        <v>24190000</v>
+          <t>Laptop HP EliteBook 6 G1a 14 - C0CE1PT (R5 AI 340, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="n">
+        <v>30190000</v>
       </c>
       <c r="C133" s="2" t="n">
-        <v>26490000</v>
+        <v>31590000</v>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.528 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002nvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r5-ai-340-c0ce1pt</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:50:45</t>
+          <t>2026-07-30 13:02:01</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002PVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="n">
-        <v>20790000</v>
+          <t>Laptop HP EliteBook 6 G1a 14 - C0CF2PT (R5 AI 340, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="n">
+        <v>31190000</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>22990000</v>
+        <v>32590000</v>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.528 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002pvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r5-ai-340-c0cf2pt</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:50:58</t>
+          <t>2026-07-30 13:02:16</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15ARP10 - 83K700YUVN (R5 7535HS, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="n">
-        <v>18690000</v>
+          <t>Laptop HP EliteBook 6 G1a 14 - C0CE2PT (R7 AI 350, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="n">
+        <v>34290000</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>24990000</v>
+        <v>35690000</v>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 7535HS | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.30 GHz (Lên đến 4.55 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 660M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe RAM) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB Type-C 3.2 Gen 1 (hỗ trợ DisplayPort 1.2 và Power delivery 3.0) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Nắp lưng và chiếu nghỉ tay bằng nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.549 kg | Chất liệu:: Nắp lưng và chiếu nghỉ tay bằng kim loại</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15arp10-r5-7535hs-83k700yuvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r7-ai-350-c0ce2pt</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:51:12</t>
+          <t>2026-07-30 13:02:31</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15ARP10 - 83K700YVVN (R7 7735HS, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="n">
-        <v>19890000</v>
+          <t>Laptop HP EliteBook 6 G1a 14 - C0CG2PT (R7 AI 350, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="n">
+        <v>33290000</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>26990000</v>
+        <v>34690000</v>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>-26%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7735HS | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 660M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.531 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15arp10-r7-7735hs-83k700yvvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r7-ai-350-c0cg2pt</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:51:25</t>
+          <t>2026-07-30 13:02:45</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IPH11 - 83UR00A4VN (Ultra 5 322, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="n">
-        <v>24990000</v>
+          <t>Laptop HP EliteBook 8 G1a 14 - C0CE5PT (R7 AI PRO 350, 32GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="n">
+        <v>37790000</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>27990000</v>
+        <v>39190000</v>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 2.50 GHz (Lên đến 4.40 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.63 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x USB 3.2. 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1 x Headphone/microphone combo 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 62 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 315.6 mm - Rộng 222 mm - Dày 15.5 mm - 1.564 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iph11-ultra-5-322-83ur00a4vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-elitebook-8-g1a-14-ai-350-c0ce5pt</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:51:39</t>
+          <t>2026-07-30 13:03:01</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IPH11 - 83UR0075VN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="n">
-        <v>28990000</v>
+          <t>Laptop HP EliteBook 8 G1a 14 - C0CE3PT (R5 AI PRO 340, 32GB, 512GB, WUXGA, Cảm ứng, Win11 Pro)</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="n">
+        <v>40790000</v>
       </c>
       <c r="C138" s="2" t="n">
-        <v>32990000</v>
+        <v>42190000</v>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -6331,184 +6280,184 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4 1 x USB Type-C (hỗ trợ USB, Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.63 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 5 Pro - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x USB A 2 x Thunderbolt 4 (Hỗ trợ Power Delivery, DisplayPort 2.1, HP Sleep and Charge) 1 x Headphone/microphone combo HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 62 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 315.6 mm - Rộng 222 mm - Dày 15.5 mm - 1.39 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iph11-ultra-7-355-83ur0075vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-elitebook-8-g1a-14-r5-ai-pro-340-c0ce3pt</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:51:53</t>
+          <t>2026-07-30 13:03:15</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IPH11 - 83UR00A5VN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="n">
-        <v>29490000</v>
+          <t>Laptop HP EliteBook 8 G1a 14 - C0CE6PT (R7 AI PRO 350, 32GB, 512GB, WUXGA, Cảm ứng, Win11 Pro)</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="n">
+        <v>46190000</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>32990000</v>
+        <v>1590000</v>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.63 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 Pro - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x USB 3.2. 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1 x Headphone/microphone combo 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 62 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 315.6 mm - Rộng 222 mm - Dày 15.5 mm - 1.558 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iph11-ultra-7-355-83ur00a5vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-elitebook-8-g1a-14-r7-ai-pro-350-c0ce6pt</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:52:06</t>
+          <t>2026-07-30 13:03:29</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00A8VN (Core 3 304, 8GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="n">
-        <v>18990000</v>
+          <t>Laptop HP Gaming HyperX Omen 15 ga0092TX - D72D8PA (i5 14450HX, 16GB, 512GB, RTX 5050 8GB, WUXGA 165Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="n">
+        <v>45590000</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>20890000</v>
+        <v>46990000</v>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core™ 3 - 304 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz (P-core), Turbo tối đa 4.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 2242 PCIe 4.0x4 NVMe | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 240Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 × USB-C (USB 5 Gbps), hỗ trợ USB PD 45–65W và DisplayPort 1.2 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Optimized with Dolby Audio 2W x 2 High Definition (HD) Audio Stereo speakers | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 240 mm - Rộng 343 mm - Dày 17 - 18 - 1.59 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 421 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.37 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-3-304-83rr00a8vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-gaming-hyperx-omen-15-ga0092tx-i5-14450hx-d72d8pa</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:52:20</t>
+          <t>2026-07-30 13:03:43</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00AAVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="n">
-        <v>23590000</v>
+          <t>Laptop HP Gaming VICTUS 15 fa2451TX - D17WPPA (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="n">
+        <v>27490000</v>
       </c>
       <c r="C141" s="2" t="n">
-        <v>26490000</v>
+        <v>31990000</v>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35W - 115W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x USB 3.2 1 x USB 3.2 (hỗ trợ HP Sleep and Charge) 1 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358 mm - Rộng 255 mm - Dày 23.5 mm - 2.29 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00aavn</t>
+          <t>https://www.thegioididong.com/laptop/hp-gaming-victus-15-fa2451tx-i5-13420h-d17wppa</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:52:34</t>
+          <t>2026-07-30 13:03:58</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Ideapad Slim 3 15IWC11 - 83RR00CVVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="n">
-        <v>20190000</v>
+          <t>Laptop HP HyperX Omen 15 ga0091TX - D72D7PA (i5 14450HX, 16GB, 512GB, RTX 5060 8GB, WUXGA 165Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="n">
+        <v>48590000</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>22990000</v>
+        <v>49990000</v>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3840 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 614 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.363 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00cvvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-hyperx-omen-15-ga0091tx-i5-14450h-d72d7pa</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -6518,21 +6467,21 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:52:47</t>
+          <t>2026-07-30 13:04:12</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US002TVN (Ultra 5 322, 24GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="n">
-        <v>30090000</v>
+          <t>Laptop HP OmniBook 7 Aero 13 bg1087AU - BZ7S1PA (R5 AI 340, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="n">
+        <v>27990000</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>31990000</v>
+        <v>29790000</v>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
@@ -6541,27 +6490,27 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 24 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCie Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4TB) | Kích thước màn hình:: 13.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 400 nits | Cổng giao tiếp:: 2 x USB Type-A 2 x USB Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/microphone combo HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E MT7922 Bluetooth 5.3 | Webcam:: HP 5MP Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Poly Studio HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 43 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 297.3 mm - Rộng 211.2 mm - Dày 17.4 mm - 0.99 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-5-322-83us002tvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-7-aero-13-bg1087au-r5-ai-340-bz7s1pa</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:53:00</t>
+          <t>2026-07-30 13:04:27</t>
         </is>
       </c>
     </row>

--- a/laptop_tgdd_all.xlsx
+++ b/laptop_tgdd_all.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0&quot;đ&quot;"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -57,15 +55,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -433,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I143"/>
+  <dimension ref="A1:I142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -500,20 +495,20 @@
           <t>Laptop Acer Aspire Go 15 AG15-52P-52WT - NX.JWKSV.001 (Ultra 5 115U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>22790000</v>
+      <c r="B2" s="2" t="n">
+        <v>21690000</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>24990000</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -533,7 +528,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:48:01</t>
+          <t>2026-07-31 11:12:09</t>
         </is>
       </c>
     </row>
@@ -543,7 +538,7 @@
           <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP - NX.DMCSV.003 (R7 7730U, 8GB, 512GB, Full HD+, Win11)</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="2" t="n">
         <v>20990000</v>
       </c>
       <c r="C3" s="2" t="n">
@@ -576,7 +571,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:48:16</t>
+          <t>2026-07-31 11:12:23</t>
         </is>
       </c>
     </row>
@@ -586,7 +581,7 @@
           <t>Laptop Acer Aspire Lite 14 AL14-45P-R7Z3 - NX.DPESV.002 (R3 5400U, 8GB, 512GB, Full HD+, Win11)</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="2" t="n">
         <v>14990000</v>
       </c>
       <c r="C4" s="2" t="n">
@@ -599,7 +594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +614,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:48:30</t>
+          <t>2026-07-31 11:12:36</t>
         </is>
       </c>
     </row>
@@ -629,7 +624,7 @@
           <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W - NX.DNRSV.002 (R5 40, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="2" t="n">
         <v>19590000</v>
       </c>
       <c r="C5" s="2" t="n">
@@ -662,7 +657,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:48:44</t>
+          <t>2026-07-31 11:12:49</t>
         </is>
       </c>
     </row>
@@ -672,20 +667,20 @@
           <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN - NX.DDASV.001 (Core 3 N350, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>17890000</v>
+      <c r="B6" s="2" t="n">
+        <v>16990000</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>18990000</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -705,7 +700,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:48:57</t>
+          <t>2026-07-31 11:13:03</t>
         </is>
       </c>
     </row>
@@ -715,7 +710,7 @@
           <t>Laptop Acer Aspire Lite 15 AL15-44P-R4UH - NX.DJVSV.002 (R7 7730U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="2" t="n">
         <v>21990000</v>
       </c>
       <c r="C7" s="2" t="n">
@@ -748,7 +743,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:49:10</t>
+          <t>2026-07-31 11:13:17</t>
         </is>
       </c>
     </row>
@@ -758,7 +753,7 @@
           <t>Laptop Acer Aspire Lite 15 AL15-46P-R73C - NX.JXMSV.001 (R3 5400U, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="2" t="n">
         <v>14490000</v>
       </c>
       <c r="C8" s="2" t="n">
@@ -771,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -791,7 +786,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:49:24</t>
+          <t>2026-07-31 11:13:32</t>
         </is>
       </c>
     </row>
@@ -801,7 +796,7 @@
           <t>Laptop Acer Aspire Lite 15 AL15-48P-R86Q - NX.DS1SV.002 (R7 5825U, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="2" t="n">
         <v>18990000</v>
       </c>
       <c r="C9" s="2" t="n">
@@ -834,7 +829,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:50:01</t>
+          <t>2026-07-31 11:13:46</t>
         </is>
       </c>
     </row>
@@ -844,20 +839,20 @@
           <t>Laptop Acer Aspire Lite 15 AL15-49P-R6XX - NX.DRZSV.002 (R5 7430U, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="2" t="n">
+        <v>17990000</v>
+      </c>
+      <c r="C10" s="2" t="n">
         <v>20990000</v>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>1590000</v>
-      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:50:15</t>
+          <t>2026-07-31 11:13:59</t>
         </is>
       </c>
     </row>
@@ -887,20 +882,20 @@
           <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC - NX.DG3SV.002.16G (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="2" t="n">
+        <v>21990000</v>
+      </c>
+      <c r="C11" s="2" t="n">
         <v>24990000</v>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>1590000</v>
-      </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -920,7 +915,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:50:28</t>
+          <t>2026-07-31 11:14:13</t>
         </is>
       </c>
     </row>
@@ -930,20 +925,20 @@
           <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH - NX.DG3SV.001 (Core 5 120U, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="2" t="n">
+        <v>20990000</v>
+      </c>
+      <c r="C12" s="2" t="n">
         <v>24990000</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>1590000</v>
-      </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -963,7 +958,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:50:42</t>
+          <t>2026-07-31 11:14:27</t>
         </is>
       </c>
     </row>
@@ -973,20 +968,20 @@
           <t>Laptop Acer Aspire Lite 16 AL16-71P-582Q - NX.DRSSV.001 (Ultra 5 125H, 16GB, 512GB, Full HD+ 120Hz, Win11)</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="2" t="n">
+        <v>23990000</v>
+      </c>
+      <c r="C13" s="2" t="n">
         <v>26990000</v>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>1590000</v>
-      </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1006,7 +1001,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:50:56</t>
+          <t>2026-07-31 11:14:41</t>
         </is>
       </c>
     </row>
@@ -1016,14 +1011,20 @@
           <t>Laptop Acer Gaming Aspire 7 A715-59G-59RD - NH.DXUSV.001 (Core 5 210H, 16GB, 512GB, RTX 3050 4GB, Fulll HD 144Hz, Win11)</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="2" t="n">
+        <v>25990000</v>
+      </c>
+      <c r="C14" s="2" t="n">
         <v>31990000</v>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-19%</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1043,7 +1044,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:51:11</t>
+          <t>2026-07-31 11:14:55</t>
         </is>
       </c>
     </row>
@@ -1053,20 +1054,20 @@
           <t>Laptop Acer Gaming Nitro ProPanel AN16S-61-R9CN - NH.QXGSV.001 (Ryzen AI 7 350, 16GB, 512GB, RTX 5070 8GB, 2K+ 180Hz, Win11)</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="2" t="n">
+        <v>55990000</v>
+      </c>
+      <c r="C15" s="2" t="n">
         <v>59990000</v>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>1590000</v>
-      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1086,7 +1087,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:51:25</t>
+          <t>2026-07-31 11:15:09</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1097,7 @@
           <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-73Z8 - NH.QUASV.001 (Core 7 240H, 16GB, 512GB, RTX 4050 6GB, Full HD  180Hz, Win11)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="2" t="n">
         <v>37290000</v>
       </c>
       <c r="C16" s="2" t="n">
@@ -1129,7 +1130,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:51:39</t>
+          <t>2026-07-31 11:15:24</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1140,7 @@
           <t>Laptop Acer Gaming Nitro ProPanel ANV16-72-71T9 - NH.QUNSV.001 (Core 7 240H, 16GB, 512GB, RTX 5060 8GB, WUXGA 180Hz, Win11)</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="2" t="n">
         <v>43990000</v>
       </c>
       <c r="C17" s="2" t="n">
@@ -1172,7 +1173,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:51:53</t>
+          <t>2026-07-31 11:15:37</t>
         </is>
       </c>
     </row>
@@ -1182,20 +1183,20 @@
           <t>Laptop Acer Gaming Nitro ProPanel ANV16S-61-R0B8 - NH.QXQSV.001 (Ryzen AI 5 340, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>45390000</v>
+      <c r="B18" s="2" t="n">
+        <v>43990000</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>47990000</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1215,7 +1216,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:52:06</t>
+          <t>2026-07-31 11:15:51</t>
         </is>
       </c>
     </row>
@@ -1225,14 +1226,20 @@
           <t>Laptop Acer Gaming Nitro ProPanel ANV16S-71-58WQ - NH.QXBSV.001 (Core 5 210H, 16GB, 512GB, RTX 5050 8GB, 2K+ 180Hz, Win11)</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="2" t="n">
+        <v>42990000</v>
+      </c>
+      <c r="C19" s="2" t="n">
         <v>46990000</v>
       </c>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1252,7 +1259,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:52:21</t>
+          <t>2026-07-31 11:16:04</t>
         </is>
       </c>
     </row>
@@ -1262,20 +1269,20 @@
           <t>Laptop Acer Gaming Predator Helios Neo 16 PHN16-I31-50H7 - NH.U4SSV.001 (i5 14450HX, 32GB, 512GB, RTX 5050 8GB, Full HD+ 180Hz, Win11)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>51390000</v>
+      <c r="B20" s="2" t="n">
+        <v>49990000</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>61990000</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-19%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1295,7 +1302,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:52:35</t>
+          <t>2026-07-31 11:16:19</t>
         </is>
       </c>
     </row>
@@ -1305,20 +1312,20 @@
           <t>Laptop Acer Gaming Predator Helios Neo 16 PHN16-I31-72XE - NH.U4RSV.001 (i7 14650HX, 32GB, 512GB, RTX5060 8GB, 2K+ 180Hz, Win11)</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
-        <v>61390000</v>
+      <c r="B21" s="2" t="n">
+        <v>59990000</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>71990000</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1338,7 +1345,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:52:49</t>
+          <t>2026-07-31 11:16:33</t>
         </is>
       </c>
     </row>
@@ -1348,14 +1355,20 @@
           <t>Laptop Acer Gaming Predator Helios Neo 16 PHN16-I31-74MN - NH.U4SSV.002 (i7 14650HX, 32GB, 512GB, RTX 5050 8GB, Full HD+ 180Hz, Win11)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="2" t="n">
+        <v>54990000</v>
+      </c>
+      <c r="C22" s="2" t="n">
         <v>66990000</v>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-18%</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1375,7 +1388,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:53:02</t>
+          <t>2026-07-31 11:16:47</t>
         </is>
       </c>
     </row>
@@ -1385,14 +1398,20 @@
           <t>Laptop Acer Gaming Predator Helios Neo 16S PHN16S-I51-97T9 - NH.U3SSV.006 (Ultra 9 386H, 16GB, 512GB, RTX 5070 8GB, 2K+ 165Hz, Win11)</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="2" t="n">
+        <v>73990000</v>
+      </c>
+      <c r="C23" s="2" t="n">
         <v>77990000</v>
       </c>
-      <c r="C23" s="2" t="inlineStr"/>
-      <c r="D23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1412,7 +1431,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:53:15</t>
+          <t>2026-07-31 11:17:01</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1441,7 @@
           <t>Laptop Acer Nitro ProPanel ANV15-52-50RB - NH.QUASV.002 (Core 5 210H, 16GB, 512GB, RTX 4050 6GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="2" t="n">
         <v>35990000</v>
       </c>
       <c r="C24" s="2" t="n">
@@ -1455,7 +1474,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:53:29</t>
+          <t>2026-07-31 11:17:16</t>
         </is>
       </c>
     </row>
@@ -1465,14 +1484,20 @@
           <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP - NX.JZHSV.003 (Ultra 7 358H, 32GB, 1TB, 2.8K 120Hz, Win11)</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="2" t="n">
+        <v>47590000</v>
+      </c>
+      <c r="C25" s="2" t="n">
         <v>50990000</v>
       </c>
-      <c r="C25" s="2" t="inlineStr"/>
-      <c r="D25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1492,7 +1517,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:53:44</t>
+          <t>2026-07-31 11:17:29</t>
         </is>
       </c>
     </row>
@@ -1502,20 +1527,20 @@
           <t>Laptop Asus Gaming ROG Strix G16 G614PM - TS147W (R9 8940HX, 16GB, 512GB, RTX 5060 8GB, WQXGA 300Hz, Win11)</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="2" t="n">
+        <v>49990000</v>
+      </c>
+      <c r="C26" s="2" t="n">
         <v>52990000</v>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>1590000</v>
-      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1535,7 +1560,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:53:58</t>
+          <t>2026-07-31 11:17:43</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1570,7 @@
           <t>Laptop Asus Gaming ROG Strix G16 G614PR - TS103W (R9 8940HX, 16GB, 512GB, RTX 5070Ti 12GB, WQXGA 300Hz, Win11)</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="2" t="n">
         <v>70590000</v>
       </c>
       <c r="C27" s="2" t="n">
@@ -1578,7 +1603,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:54:12</t>
+          <t>2026-07-31 11:17:56</t>
         </is>
       </c>
     </row>
@@ -1588,14 +1613,20 @@
           <t>Laptop Asus Gaming ROG Zephyrus GA403GM - SY004W (R9 AI 465, 32GB, 1TB, RTX 5060 8GB, 3K OLED 120Hz, Win11)</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="2" t="n">
+        <v>64590000</v>
+      </c>
+      <c r="C28" s="2" t="n">
         <v>65990000</v>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1615,7 +1646,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:54:26</t>
+          <t>2026-07-31 11:18:10</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1656,7 @@
           <t>Laptop Asus TUF Gaming F16 FX608JHI - TU210W (i5 14450HX, 16GB, 512GB,RTX 5050 8GB, WUXGA 144Hz, Win11)</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="2" t="n">
         <v>40990000</v>
       </c>
       <c r="C29" s="2" t="n">
@@ -1638,7 +1669,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1658,7 +1689,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:54:40</t>
+          <t>2026-07-31 11:18:25</t>
         </is>
       </c>
     </row>
@@ -1668,14 +1699,20 @@
           <t>Laptop Asus TUF Gaming FA401EA - RG034W (RYZEN AI MAX+ 392, 64GB, 1TB, WQXGA 165Hz, Win11)</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="2" t="n">
+        <v>62990000</v>
+      </c>
+      <c r="C30" s="2" t="n">
         <v>64990000</v>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1695,111 +1732,111 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:55:09</t>
+          <t>2026-07-31 11:18:38</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP OmniBook X Flip 14 fk0082AU - BZ7N8PA (R7 AI 350, 32GB, 1TB, 2K, Cảm ứng, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>39890000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US002WVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>30090000</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>40890000</v>
+        <v>32990000</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: 2K (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Corning Gorilla Glass 3 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB Type-C (hỗ trợ truyền dữ liệu, DisplayPort 2.1, Power delivery 3.1, HP Sleep and Charge) Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E MT7922 Bluetooth 5.3 | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ | Thông tin Pin:: 3-cell Li-Po, 59 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 218.5 mm - Dày 14.6 mm - 1.39 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-x-flip-14-fk0082au-r7-ai-350-bz7n8pa</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-7-355-83us002wvn</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:41</t>
+          <t>2026-07-31 13:24:33</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP Probook 4 G1ah 16 - C40JPAT (R5 220, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>25490000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US003YVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>29490000</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>29890000</v>
+        <v>32990000</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 220 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 48 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x USB Type-C 3.2 Gen 2 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: FHD 1080p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 359.4 mm - Rộng 251 mm - Dày 17 mm - 1.785 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-probook-4-g1ah-16-r5-220-c40jpat</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-7-355-83us003yvn</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:53:56</t>
+          <t>2026-07-31 13:24:47</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP ProBook 4 G1iR 14 - C40JKAT (Core 5 120U, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>26990000</v>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 - 83S1006RVN (R7 AI 445, 16GB, 512GB, WUXGA OLED, Win11)</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>30590000</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>34590000</v>
+        <v>32990000</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-22%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1809,98 +1846,98 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB Type-A 2 x USB Type-C (hỗ trợ DisplayPort 1.4, Power delivery 3.0, HP Sleep and Charge) 1 x Headphone/microphone combo LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 56 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.0 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 2 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 2-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-probook-4-g1ir-14-core-5-120u-c40jkat</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-14agp11-r7-ai-445-83s1006rvn</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:11</t>
+          <t>2026-07-31 13:25:02</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming Legion 5 15AHP11 - 83Q7001HVN (R7 250, 16GB, 512GB, RTX 5050 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>55290000</v>
+          <t>Laptop Lenovo IdeaPad Slim 5 14IPH11 - 83S5004FVN (Ultra 7 355, 16GB, 512GB, WUXGA OLED, Win11)</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>34490000</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>55990000</v>
+        <v>37990000</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: Boost Clock 2662MHz, TGP 115W, 440 AI TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: 2.5K | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: DisplayHDR True Black 1000 | Cổng giao tiếp:: 1x Ethernet 2 x USB Type-C (USB4 40Gbps) hỗ trợ USB PD 65 - 100W và DisplayPort 1.4 1 x Headphone/ Microphone combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) 2×2 Bluetooth 6.0 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 244.5 mm - Rộng 344 mm - Dày 19~20 - 1.87 kg | Chất liệu:: Mặt trên: nhôm + Mặt dưới: nhựa PC-ABS</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15ahp11-r7-250-83q7001hvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-14iph11-ultra-7-355-83s5004fvn</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:26</t>
+          <t>2026-07-31 13:25:16</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming Legion 5 15AHP11 - 83Q7001JVN (R7 250, 16GB, 512GB, RTX 5060 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>55490000</v>
+          <t>Laptop Lenovo IdeaPad Slim 5 OLED 14IPH11 - 83S5000DVN (Ultra 5 322, 16GB, 512GB, WUXGA OLED, Win11)</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>29490000</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>58990000</v>
+        <v>32990000</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 2TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WQXGA (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light 1000 nits (peak) G-Sync 500 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB4 Type-C (DisplayPort 1.4, Power Delivery) LAN (RJ45) HDMI 2.1 3 x USB A | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio Audio by HARMAN Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Legion ColdFont Hyper | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344 mm - Rộng 244.5 mm - Dày 19.95 mm - 1.87 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD NVMe M.2 PCIe Gen 4.0 mở rộng (2280) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 2 x USB Type-C 3.2 (hỗ trợ truyền dữ liệu, Power Delivery 3.0, and DisplayPort 1.2) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Nắp lưng và mặt đáy bằng nhôm</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15ahp11-r7-250-83q7001jvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-oled-14iph11-ultra-5-322-83s5000dvn</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1910,83 +1947,83 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:41</t>
+          <t>2026-07-31 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming Legion 5 15IPH11 - 83RW0023VN (Ultra 7 356H, 16GB, 512GB, RTX 5060 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>59490000</v>
+          <t>Laptop Lenovo ThinkBook 14 G9 - 21V0005PVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>28290000</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>64990000</v>
+        <v>31190000</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 365H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 15.3" | Độ phân giải:: WQXGA (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light 1000 nits (peak) 500 nits typical G-Sync DisplayHDR True Black 1000 High Gaming Performance Flicker Free | Cổng giao tiếp:: 3 x USB Jack tai nghe 3.5 mm 1 x USB Type-C (USB Power Delivery, DisplayPort 2.1) LAN (RJ45) HDMI 2.1 1 x Thunderbolt 4 (hỗ trợ DisplayPort 2.1, Power Delivery) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đèn chuyển màu RGB - 24 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Realtek Audio Audio by HARMAN Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Legion ColdFont Hyper | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344 mm - Rộng 244.5 mm - Dày 19.95 mm - 1.87 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15iph11-ultra-7-356h-83rw0023vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-g9-r7-250-21v0005pvn</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:54:56</t>
+          <t>2026-07-31 13:25:45</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming LOQ 15AHP11 - 83TN0040VN (R7 250, 16GB, 512GB, RTX 5050 8GB, WUXGA 165Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>43490000</v>
+          <t>Laptop Lenovo ThinkBook 14 Gen 9 IRL - 21UY008TVN (i5 13420H, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>27290000</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46990000</v>
+        <v>28890000</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 2TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Low Blue Light G-Sync AMD Freesync 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm LAN (RJ45) HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) 3 x USB A | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344.9 mm - Rộng 254.83 mm - Dày 23.25 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15ahp11-r7-250-83tn0040vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-gen-9-irl-i5-13420h-21uy008tvn</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1996,279 +2033,279 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:55:11</t>
+          <t>2026-07-31 13:25:58</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming LOQ 15ARP10E - 83S0004FVN (R7 7735HS, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>34490000</v>
+          <t>Laptop Lenovo ThinkBook 16 G9 - 21UT005MVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>29690000</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>40990000</v>
+        <v>31590000</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7735HS | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 65 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: AMD Freesync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A 1x Ethernet 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery 3.0) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3 - cell Li-ion, 57.5 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 359.2 mm - Rộng 236 mm - Dày 22.95 mm - 1.8 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356 mm - Rộng 253.5 mm - Dày 17.5 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15arp10e-r7-7735hs-83s0004fvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-16-g9-r7-250-21ut005mvn</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:55:25</t>
+          <t>2026-07-31 13:26:11</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming LOQ 15IPH11 - 83SL000LVN (Ultra 7 356H, 16GB, 512GB, RTX 5060 8GB, WUXGA 165Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>51490000</v>
+          <t>Laptop Lenovo ThinkPad E14 Gen 7 - 21SX00BNVN (Ultra 5 135H, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>29690000</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>55990000</v>
+        <v>31590000</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 365H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 1TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Low Blue Light G-Sync AMD Freesync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 3 x USB Jack tai nghe 3.5 mm LAN (RJ45) HDMI 2.1 1 x Thunderbolt 4 (hỗ trợ DisplayPort 2.1, Power Delivery) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344.9 mm - Rộng 254.83 mm - Dày 23.25 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 135H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.60 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x USB-A (USB 10Gbps/USB 3.2 Gen 2), Always On 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Audio by HARMAN Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 19.7 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15iph11-ultra-7-356h-83sl000lvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-5-135h-21sx00bnvn</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:55:40</t>
+          <t>2026-07-31 13:26:24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming LOQ 15IRX9 - 83DV01H2VN (i7 13645HX, 16GB, 1TB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>34590000</v>
+          <t>Laptop Lenovo ThinkPad E14 Gen 7 - 21SX005NVN (Ultra 5 225U, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>31490000</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>36990000</v>
+        <v>33890000</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13645HX | Số nhân:: 14 | Số luồng:: 20 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 150 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD NVMe M.2 PCIe Gen 4.0x4 (2242) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1x Ethernet 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.86 mm - Rộng 258.7 mm - Dày 23.9 mm - 2.38 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4 với USB Power Delivery và DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Audio by HARMAN Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 19.7 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15irx9-i7-13645hx-83dv01h2vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-5-225u-21sx005nvn</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:55:55</t>
+          <t>2026-07-31 13:26:38</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming LOQ 15IRX9 - 83DV01H3VN (i7 13645HX, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>34590000</v>
+          <t>Laptop Lenovo ThinkPad X9 14 Gen 1 - 21QA006JVN (Ultra 7 258V, 32GB, 512GB, WUXGA OLED, Win11Pro)</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>53290000</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>36490000</v>
+        <v>55190000</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13645HX | Số nhân:: 14 | Số luồng:: 20 | Tốc độ CPU:: 2.60 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 105 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1x Ethernet 3 x USB 3.2 Gen 1 HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.86 mm - Rộng 258.7 mm - Dày 23.9 mm - 2.38 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.80 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Chống chói Anti Glare Dolby Vision 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm HDMI 2.1 2 x USB-C (hỗ trợ Thunderbolt 4/USB 4, USB Power Delivery và DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.8 mm - Rộng 212.3 mm - Dày 17.18 mm - 1.21 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15irx9-i7-13645hx-83dv01h3vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-x9-14-gen-1-ultra-7-258v-21qa006jvn</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:56:12</t>
+          <t>2026-07-31 13:26:53</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming LOQ Essential 15ARP10E - 83S0000DVN (R5 7535HS, 16GB, 512GB, RTX 3050 6GB, Full HD 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>24190000</v>
+          <t>Laptop Lenovo V14 G5 - 83HD0035VN (Core7 240H, 16G, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>26990000</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>35990000</v>
+        <v>28590000</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>-33%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 7535HS | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.30 GHz (Lên đến 4.55 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 6 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 65 W | Hiệu năng xử lý AI (TOPS):: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB onboard + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: AMD Freesync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery 3.0) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hyper Champer Cooling | Thông tin Pin:: 4-cell Li-ion, 57.5 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 359.2 mm - Rộng 236 mm - Dày 22.95 mm - 1.8 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) LAN (RJ45) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Ion, 47 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324.2 mm - Rộng 215.2 mm - Dày 17.9 mm - 1.37 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-essential-15arp10e-r5-7535hs-83s0000dvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-v14-g5-core7-240h-83hd0035vn</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:56:25</t>
+          <t>2026-07-31 13:27:07</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad 5 2in1 14IPH11 - 83UG0026VN (Ultra 5 322, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>30590000</v>
+          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002LVN (Ultra 5 322, 16GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>37490000</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>32990000</v>
+        <v>39990000</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.6 mm - Rộng 224.9 mm - Dày 17.4 mm - 1.54 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.45 mm - 1.38 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-5-2in1-14iph11-ultra-5-322-83ug0026vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-5-322-83tc002lvn</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:56:40</t>
+          <t>2026-07-31 13:27:21</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad 5 2in1 14IPH11 - 83UG0027VN (Ultra 7 355, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>35590000</v>
+          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002MVN (Ultra 7 355, 32GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>54490000</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>37990000</v>
+        <v>57990000</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
@@ -2277,60 +2314,60 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.6 mm - Rộng 224.9 mm - Dày 17.4 mm - 1.54 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.95 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-5-2in1-14iph11-ultra-7-355-83ug0027vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-7-355-83tc002mvn</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:56:54</t>
+          <t>2026-07-31 13:27:34</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14ARP10 - 83K600E6VN (R5 7535HS, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n">
-        <v>19690000</v>
+          <t>Laptop Lenovo Yoga 7 2in1 OLED 14IPH11 - 83TC002JVN (Ultra 7 355, 32GB, 1TB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>53490000</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>24990000</v>
+        <v>57990000</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 7533HS | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.30 GHz (Lên đến 4.55 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 660M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 1TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.39 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Tiêu chuẩn Nền Intel Evo | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.45 mm - 1.38 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14arp10-r5-7535hs-83k600e6vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-oled-14iph11-ultra-7-355-83tc002jvn</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2340,322 +2377,322 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:57:09</t>
+          <t>2026-07-31 13:27:47</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14ARP10 - 83K6005WVN (R7 7735HS, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n">
-        <v>19690000</v>
+          <t>Laptop Lenovo Yoga Slim 7 OLED 14AGP11 - 83QS001DVN (R7 AI 445, 16GB, 512GB, WUXGA OLED, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>37490000</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>26990000</v>
+        <v>39990000</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>-27%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7735HS | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 680M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.39 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 8000 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Glossy Display Chuẩn DisplayHDR True Black 500 Eyesafe Dolby Vision 400 nits X-Rite Flicker Free | Cổng giao tiếp:: 1 x USB Type-C (hỗ trợ DisplayPort 1.4) 2 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 221 mm - Dày 13.9 mm - 1.15 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14arp10-r7-7735hs-83k6005wvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-oled-14agp11-r7-ai-445-83qs001dvn</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:57:23</t>
+          <t>2026-07-31 13:28:01</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IPH11 - 83UQ003NVN (Ultra 5 322, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>25390000</v>
+          <t>Laptop Lenovo Yoga Slim 7 OLED 14IPH11 - 83QM002FVN (Ultra 7 355, 32GB, 1TB, WUXGA OLED, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>52490000</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>27990000</v>
+        <v>55990000</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.43 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe 600nits (peak) Dolby Vision 400 nits X-Rite Flicker Free | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 2-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 221 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iph11-ultra-5-322-83uq003nvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-oled-14iph11-ultra-7-355</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:57:37</t>
+          <t>2026-07-31 13:28:14</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IPH11 - 83UQ003PVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="n">
-        <v>30090000</v>
+          <t>Laptop MacBook Pro 14 inch M5 Pro 48GB/1TB</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>84990000</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>32990000</v>
+        <v>85490000</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm giá 500,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Phiếu mua hàng Chuột, Bàn phím (Apple) trị giá 500,000đ | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng 50.000đ mua Chuột Logitech M240 | Tặng Phiếu mua hàng Balo, Túi chống sốc (giá trị trên 1,000,000đ) trị giá 300,000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.43 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Apple M5 Pro | Số nhân:: 15 | Số luồng:: Hãng không công bố | Tốc độ CPU:: 307 GB/s memory bandwidth | Card màn hình:: Card tích hợp - 16 nhân GPU | RAM:: 48 GB | Loại RAM:: Hãng không công bố | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 1 TB SSD | Kích thước màn hình:: 14.2" | Độ phân giải:: Liquid Retina XDR display (3024 x 1964) | Tần số quét:: up to 120 Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: ProMotion Độ sáng XDR: toàn màn hình 1000 nits, cao nhất 1600 nits (chỉ nội dung HDR) Độ sáng SDR: lên đến 1000 nits Wide color (P3) True Tone Technology 1 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm MagSafe 3 3 x Thunderbolt 5 (hỗ trợ DisplayPort, Thunderbolt 5 (up to 120Gb/s), USB 4 (up to 120Gb/s)) HDMI | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Khe đọc thẻ nhớ:: SDXC | Webcam:: Camera 12MP Center Stage | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Hệ thống âm thanh 6 loa Spatial Audio 3 microphones Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-Po, 72.4 Wh | Hệ điều hành:: macOS Tahoe | Thời điểm ra mắt:: 03/2026 | Kích thước:: Dài 312.6 mm - Rộng 221.2 mm - Dày 15.5 mm - 1.6 kg | Chất liệu:: Vỏ nhôm tái chế 100% | Hãng:: MacBook. Xem thông tin hãng</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iph11-ultra-7-355-83uq003pvn</t>
+          <t>https://www.thegioididong.com/laptop/macbook-pro-14-inch-m5-pro-48gb-1tb</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:57:52</t>
+          <t>2026-07-31 13:28:27</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002NVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="n">
-        <v>24190000</v>
+          <t>Laptop MacBook Pro 14 inch M5 Pro 48GB/2TB</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>98690000</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>26490000</v>
+        <v>99190000</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm giá 500,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Phiếu mua hàng Chuột, Bàn phím (Apple) trị giá 500,000đ | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng 50.000đ mua Chuột Logitech M240 | Tặng Phiếu mua hàng Balo, Túi chống sốc (giá trị trên 1,000,000đ) trị giá 300,000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Apple M5 Pro | Số nhân:: 15 | Số luồng:: Hãng không công bố | Tốc độ CPU:: 307 GB/s memory bandwidth | Card màn hình:: Card tích hợp - 16 nhân GPU | RAM:: 48 GB | Loại RAM:: Hãng không công bố | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 2 TB SSD | Kích thước màn hình:: 14.2" | Độ phân giải:: Liquid Retina XDR display (3024 x 1964) | Tần số quét:: up to 120 Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: ProMotion Độ sáng XDR: toàn màn hình 1000 nits, cao nhất 1600 nits (chỉ nội dung HDR) Độ sáng SDR: lên đến 1000 nits Wide color (P3) True Tone Technology 1 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm MagSafe 3 3 x Thunderbolt 5 (hỗ trợ DisplayPort, Thunderbolt 5 (up to 120Gb/s), USB 4 (up to 120Gb/s)) HDMI | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Khe đọc thẻ nhớ:: SDXC | Webcam:: Camera 12MP Center Stage | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Hệ thống âm thanh 6 loa Spatial Audio 3 microphones Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-Po, 72.4 Wh | Hệ điều hành:: macOS Tahoe | Thời điểm ra mắt:: 03/2026 | Kích thước:: Dài 312.6 mm - Rộng 221.2 mm - Dày 15.5 mm - 1.6 kg | Chất liệu:: Vỏ nhôm tái chế 100% | Hãng:: MacBook. Xem thông tin hãng</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002nvn</t>
+          <t>https://www.thegioididong.com/laptop/macbook-pro-14-inch-m5-pro-48gb-2tb</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:58:07</t>
+          <t>2026-07-31 13:28:41</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002PVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="n">
-        <v>20790000</v>
+          <t>Laptop MSI Gaming Cyborg 15 Black Edition A13VE - A13VE-2410VN (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>27990000</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>22990000</v>
+        <v>31990000</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.60 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Công nghệ âm thanh:: Hi-Res Audio DTS Audio | Tản nhiệt:: Cooler Boost 1 x Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 53.5 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.36 mm - Rộng 250.34 mm - Dày 22.9 mm - 1.98 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002pvn</t>
+          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-black-edition-a13ve-i5-13420h-a13ve-2410vn</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:58:22</t>
+          <t>2026-07-31 13:28:54</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15ARP10 - 83K700YUVN (R5 7535HS, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="n">
-        <v>18690000</v>
+          <t>Laptop MSI Gaming Cyborg 15 C13WEO-417VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>35590000</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>24990000</v>
+        <v>36990000</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 7535HS | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.30 GHz (Lên đến 4.55 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 660M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe RAM) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB Type-C 3.2 Gen 1 (hỗ trợ DisplayPort 1.2 và Power delivery 3.0) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Nắp lưng và chiếu nghỉ tay bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card rời - Intel UHD Graphics (tích hợp) + NVIDIA GeForce RTX 5050 GPU, 8GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB Type-A 1 x Headphone/ Microphone combo audio jack 1 x USB Type C (chỉ hỗ trợ Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: DTS Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.98 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15arp10-r5-7535hs-83k700yuvn</t>
+          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-c13weo-417vn-i7-13620h</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:58:37</t>
+          <t>2026-07-31 13:29:07</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15ARP10 - 83K700YVVN (R7 7735HS, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>19890000</v>
+          <t>Laptop MSI Gaming Raider 16 MAX HX B2WI - 095VN (Ultra 9 290HX Plus, 64GB, 2TB, RTX 5080 16GB, QHD+ OLED 240Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>1350000</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>26990000</v>
+        <v>1590000</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>-26%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7735HS | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 660M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 9 Arrow Lake - 290HX Plus | Số nhân:: 24 | Số luồng:: 24 | Tốc độ CPU:: 2.70 GHz (Lên đến 5.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 1334 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5080, 16 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 175 W | RAM:: 64 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe 32 GB) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: 128 GB | Ổ cứng:: 2 TB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 4 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: QHD+ (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 240Hz | Độ phủ màu:: 100% DCI-P3 | Cổng giao tiếp:: 2 x Thunderbolt 4 (hỗ trợ Power Delivery 3.1 và DisplayPort) 3 x USB Type-A 3.2 Gen 2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Cooler Boost 3 Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-Po, 91.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 363 mm - Rộng 269.7 mm - Dày 28.85 mm - 2.6 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15arp10-r7-7735hs-83k700yvvn</t>
+          <t>https://www.thegioididong.com/laptop/msi-gaming-raider-16-max-hx-b2wi-ultra-9-290hx-plus-095vn</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:58:51</t>
+          <t>2026-07-31 13:29:22</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IPH11 - 83UR00A4VN (Ultra 5 322, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="n">
-        <v>24990000</v>
+          <t>Laptop MSI Modern 15 F1MG-1264VN (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>19990000</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>27990000</v>
+        <v>22390000</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
@@ -2664,385 +2701,385 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 2.50 GHz (Lên đến 4.40 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.63 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core thế hệ 12 - 120U | Số nhân:: Hãng không công bố | Số luồng:: 12 | Tốc độ CPU:: 1.45 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (2280) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: Hãng không công bố | Cổng giao tiếp:: 3 x USB 3.2 Gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell, 46.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.7 kg | Chất liệu:: Plastic (nhựa dẻo)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iph11-ultra-5-322-83ur00a4vn</t>
+          <t>https://www.thegioididong.com/laptop/msi-modern-15-f1mg-1264vn-core-5-120u</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:59:06</t>
+          <t>2026-07-31 13:29:35</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IPH11 - 83UR0075VN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="n">
-        <v>28990000</v>
+          <t>Laptop SingPC M16-i382 (i3 1215U, 8GB, 256GB, WUXGA, Win11 Pro)</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>13890000</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>32990000</v>
+        <v>15190000</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4 1 x USB Type-C (hỗ trợ USB, Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.63 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i3 Alder Lake - 1215U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.2GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 256 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iph11-ultra-7-355-83ur0075vn</t>
+          <t>https://www.thegioididong.com/laptop/singpc-m16-i382-i3-1215u</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:59:22</t>
+          <t>2026-07-31 13:29:49</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IPH11 - 83UR00A5VN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="n">
-        <v>29490000</v>
+          <t>Laptop SingPC M16-i595 (i5 1235U, 16GB, 512GB, WUXGA, Win11 Pro)</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>18390000</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>32990000</v>
+        <v>19990000</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.63 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Alder Lake - 1235U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.30 GHz (Lên đến 4.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 72% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iph11-ultra-7-355-83ur00a5vn</t>
+          <t>https://www.thegioididong.com/laptop/singpc-m16-i595-i5-1235u</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:59:37</t>
+          <t>2026-07-31 13:30:02</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00A8VN (Core 3 304, 8GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="n">
-        <v>18990000</v>
+          <t>Laptop HP OmniBook X Flip 14 fk0082AU - BZ7N8PA (R7 AI 350, 32GB, 1TB, 2K, Cảm ứng, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>39890000</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>20890000</v>
+        <v>40890000</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core™ 3 - 304 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz (P-core), Turbo tối đa 4.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 2242 PCIe 4.0x4 NVMe | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 × USB-C (USB 5 Gbps), hỗ trợ USB PD 45–65W và DisplayPort 1.2 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Optimized with Dolby Audio 2W x 2 High Definition (HD) Audio Stereo speakers | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 240 mm - Rộng 343 mm - Dày 17 - 18 - 1.59 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: 2K (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Corning Gorilla Glass 3 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB Type-C (hỗ trợ truyền dữ liệu, DisplayPort 2.1, Power delivery 3.1, HP Sleep and Charge) Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E MT7922 Bluetooth 5.3 | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ | Thông tin Pin:: 3-cell Li-Po, 59 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 218.5 mm - Dày 14.6 mm - 1.39 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-3-304-83rr00a8vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-x-flip-14-fk0082au-r7-ai-350-bz7n8pa</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:59:52</t>
+          <t>2026-07-31 13:30:56</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00AAVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n">
-        <v>23590000</v>
+          <t>Laptop HP Probook 4 G1ah 16 - C40JPAT (R5 220, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>25490000</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>26490000</v>
+        <v>29890000</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 220 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 48 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x USB Type-C 3.2 Gen 2 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: FHD 1080p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 359.4 mm - Rộng 251 mm - Dày 17 mm - 1.785 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00aavn</t>
+          <t>https://www.thegioididong.com/laptop/hp-probook-4-g1ah-16-r5-220-c40jpat</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:00:07</t>
+          <t>2026-07-31 13:31:10</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Ideapad Slim 3 15IWC11 - 83RR00CVVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="n">
-        <v>20190000</v>
+          <t>Laptop HP ProBook 4 G1iR 14 - C40JKAT (Core 5 120U, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>26990000</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>22990000</v>
+        <v>34590000</v>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB Type-A 2 x USB Type-C (hỗ trợ DisplayPort 1.4, Power delivery 3.0, HP Sleep and Charge) 1 x Headphone/microphone combo LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 56 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00cvvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-probook-4-g1ir-14-core-5-120u-c40jkat</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:00:23</t>
+          <t>2026-07-31 13:31:23</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US002TVN (Ultra 5 322, 24GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="n">
-        <v>30090000</v>
+          <t>Laptop Lenovo Gaming Legion 5 15AHP11 - 83Q7001HVN (R7 250, 16GB, 512GB, RTX 5050 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>55290000</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>31990000</v>
+        <v>55990000</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 24 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: Boost Clock 2662MHz, TGP 115W, 440 AI TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: 2.5K | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: DisplayHDR True Black 1000 | Cổng giao tiếp:: 1x Ethernet 2 x USB Type-C (USB4 40Gbps) hỗ trợ USB PD 65 - 100W và DisplayPort 1.4 1 x Headphone/ Microphone combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) 2×2 Bluetooth 6.0 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 244.5 mm - Rộng 344 mm - Dày 19~20 - 1.87 kg | Chất liệu:: Mặt trên: nhôm + Mặt dưới: nhựa PC-ABS</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-5-322-83us002tvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15ahp11-r7-250-83q7001hvn</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:00:38</t>
+          <t>2026-07-31 13:31:37</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US002WVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="n">
-        <v>30090000</v>
+          <t>Laptop Lenovo Gaming Legion 5 15AHP11 - 83Q7001JVN (R7 250, 16GB, 512GB, RTX 5060 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>55490000</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>32990000</v>
+        <v>58990000</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 2TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WQXGA (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light 1000 nits (peak) G-Sync 500 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB4 Type-C (DisplayPort 1.4, Power Delivery) LAN (RJ45) HDMI 2.1 3 x USB A | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio Audio by HARMAN Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Legion ColdFont Hyper | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344 mm - Rộng 244.5 mm - Dày 19.95 mm - 1.87 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-7-355-83us002wvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15ahp11-r7-250-83q7001jvn</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:50:54</t>
+          <t>2026-07-31 13:31:51</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US003YVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="n">
-        <v>29490000</v>
+          <t>Laptop Lenovo Gaming Legion 5 15IPH11 - 83RW0023VN (Ultra 7 356H, 16GB, 512GB, RTX 5060 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>59490000</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>32990000</v>
+        <v>64990000</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 365H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 15.3" | Độ phân giải:: WQXGA (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light 1000 nits (peak) 500 nits typical G-Sync DisplayHDR True Black 1000 High Gaming Performance Flicker Free | Cổng giao tiếp:: 3 x USB Jack tai nghe 3.5 mm 1 x USB Type-C (USB Power Delivery, DisplayPort 2.1) LAN (RJ45) HDMI 2.1 1 x Thunderbolt 4 (hỗ trợ DisplayPort 2.1, Power Delivery) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đèn chuyển màu RGB - 24 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Realtek Audio Audio by HARMAN Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Legion ColdFont Hyper | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344 mm - Rộng 244.5 mm - Dày 19.95 mm - 1.87 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-7-355-83us003yvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15iph11-ultra-7-356h-83rw0023vn</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:51:10</t>
+          <t>2026-07-31 13:32:04</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 - 83S1006RVN (R7 AI 445, 16GB, 512GB, WUXGA OLED, Win11)</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="n">
-        <v>30590000</v>
+          <t>Laptop Lenovo Gaming LOQ 15AHP11 - 83TN0040VN (R7 250, 16GB, 512GB, RTX 5050 8GB, WUXGA 165Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>43490000</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>32990000</v>
+        <v>46990000</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
@@ -3051,146 +3088,146 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.0 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 2 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 2-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 2TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Low Blue Light G-Sync AMD Freesync 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm LAN (RJ45) HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) 3 x USB A | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344.9 mm - Rộng 254.83 mm - Dày 23.25 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-14agp11-r7-ai-445-83s1006rvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15ahp11-r7-250-83tn0040vn</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:51:24</t>
+          <t>2026-07-31 13:32:17</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14IPH11 - 83S5004FVN (Ultra 7 355, 16GB, 512GB, WUXGA OLED, Win11)</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="n">
+          <t>Laptop Lenovo Gaming LOQ 15ARP10E - 83S0004FVN (R7 7735HS, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
         <v>34490000</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>37990000</v>
+        <v>40990000</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 7735HS | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 65 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: AMD Freesync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A 1x Ethernet 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery 3.0) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3 - cell Li-ion, 57.5 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 359.2 mm - Rộng 236 mm - Dày 22.95 mm - 1.8 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-14iph11-ultra-7-355-83s5004fvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15arp10e-r7-7735hs-83s0004fvn</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:51:39</t>
+          <t>2026-07-31 13:32:30</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 OLED 14IMH10 - 83V6001GVN (Ultra 5 135H, 16GB, 512GB, WUXGA OLED, Win11)</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="n">
-        <v>23690000</v>
+          <t>Laptop Lenovo Gaming LOQ 15IPH11 - 83SL000LVN (Ultra 7 356H, 16GB, 512GB, RTX 5060 8GB, WUXGA 165Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>51490000</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>25990000</v>
+        <v>55990000</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 135H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Hãng không công bố | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 mở rộng (nâng cấp tối đa 1 TB) 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (USB 5Gbps/USB 3.2 Gen 1), Always On 1 x USB-A (USB 5Gbps/USB 3.2 Gen 1) HDMI 2.1 2 x USB 3.2 Gen 2 Type-C (hỗ trợ Power Delivery 3.0, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.39 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 365H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 1TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Low Blue Light G-Sync AMD Freesync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 3 x USB Jack tai nghe 3.5 mm LAN (RJ45) HDMI 2.1 1 x Thunderbolt 4 (hỗ trợ DisplayPort 2.1, Power Delivery) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344.9 mm - Rộng 254.83 mm - Dày 23.25 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-oled-14imh10-ultra-5-135h-83v6001gvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15iph11-ultra-7-356h-83sl000lvn</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:51:54</t>
+          <t>2026-07-31 13:32:43</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 OLED 14IPH11 - 83S5000DVN (Ultra 5 322, 16GB, 512GB, WUXGA OLED, Win11)</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="n">
-        <v>29490000</v>
+          <t>Laptop Lenovo Gaming LOQ 15IRX9 - 83DV01H2VN (i7 13645HX, 16GB, 1TB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>34590000</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>32990000</v>
+        <v>36990000</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD NVMe M.2 PCIe Gen 4.0 mở rộng (2280) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 2 x USB Type-C 3.2 (hỗ trợ truyền dữ liệu, Power Delivery 3.0, and DisplayPort 1.2) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Nắp lưng và mặt đáy bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13645HX | Số nhân:: 14 | Số luồng:: 20 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 150 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD NVMe M.2 PCIe Gen 4.0x4 (2242) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1x Ethernet 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.86 mm - Rộng 258.7 mm - Dày 23.9 mm - 2.38 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-oled-14iph11-ultra-5-322-83s5000dvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15irx9-i7-13645hx-83dv01h2vn</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3200,111 +3237,111 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:52:08</t>
+          <t>2026-07-31 13:32:56</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkBook 14 G9 - 21V0005PVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="n">
-        <v>28290000</v>
+          <t>Laptop Lenovo Gaming LOQ 15IRX9 - 83DV01H3VN (i7 13645HX, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>34590000</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>31190000</v>
+        <v>36490000</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13645HX | Số nhân:: 14 | Số luồng:: 20 | Tốc độ CPU:: 2.60 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 105 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1x Ethernet 3 x USB 3.2 Gen 1 HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.86 mm - Rộng 258.7 mm - Dày 23.9 mm - 2.38 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-g9-r7-250-21v0005pvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15irx9-i7-13645hx-83dv01h3vn</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:52:22</t>
+          <t>2026-07-31 13:33:09</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkBook 14 Gen 9 IRL - 21UY008TVN (i5 13420H, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="n">
-        <v>27290000</v>
+          <t>Laptop Lenovo Gaming LOQ Essential 15ARP10E - 83S0000DVN (R5 7535HS, 16GB, 512GB, RTX 3050 6GB, Full HD 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>24190000</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>28890000</v>
+        <v>35990000</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-33%</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 7535HS | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.30 GHz (Lên đến 4.55 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 6 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 65 W | Hiệu năng xử lý AI (TOPS):: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB onboard + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: AMD Freesync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery 3.0) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hyper Champer Cooling | Thông tin Pin:: 4-cell Li-ion, 57.5 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 359.2 mm - Rộng 236 mm - Dày 22.95 mm - 1.8 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-gen-9-irl-i5-13420h-21uy008tvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-essential-15arp10e-r5-7535hs-83s0000dvn</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:52:35</t>
+          <t>2026-07-31 13:33:22</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkBook 16 G9 - 21UT005MVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="n">
-        <v>29690000</v>
+          <t>Laptop Lenovo IdeaPad 5 2in1 14IPH11 - 83UG0026VN (Ultra 5 322, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>30590000</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>31590000</v>
+        <v>32990000</v>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3314,36 +3351,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356 mm - Rộng 253.5 mm - Dày 17.5 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.6 mm - Rộng 224.9 mm - Dày 17.4 mm - 1.54 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-16-g9-r7-250-21ut005mvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-5-2in1-14iph11-ultra-5-322-83ug0026vn</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:52:50</t>
+          <t>2026-07-31 13:33:36</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad E14 Gen 7 - 21SX00BNVN (Ultra 5 135H, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="n">
-        <v>29690000</v>
+          <t>Laptop Lenovo IdeaPad 5 2in1 14IPH11 - 83UG0027VN (Ultra 7 355, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>35590000</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>31590000</v>
+        <v>37990000</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
@@ -3352,232 +3389,232 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 135H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.60 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x USB-A (USB 10Gbps/USB 3.2 Gen 2), Always On 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Audio by HARMAN Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 19.7 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.6 mm - Rộng 224.9 mm - Dày 17.4 mm - 1.54 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-5-135h-21sx00bnvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-5-2in1-14iph11-ultra-7-355-83ug0027vn</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:53:05</t>
+          <t>2026-07-31 13:33:49</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad E14 Gen 7 - 21SX005NVN (Ultra 5 225U, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="n">
-        <v>31490000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 14ARP10 - 83K600E6VN (R5 7535HS, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>19690000</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>33890000</v>
+        <v>24990000</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4 với USB Power Delivery và DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Audio by HARMAN Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 19.7 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 7533HS | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.30 GHz (Lên đến 4.55 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 660M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 1TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.39 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-5-225u-21sx005nvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14arp10-r5-7535hs-83k600e6vn</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:53:19</t>
+          <t>2026-07-31 13:34:02</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad X9 14 Gen 1 - 21QA006JVN (Ultra 7 258V, 32GB, 512GB, WUXGA OLED, Win11Pro)</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="n">
-        <v>53290000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 14ARP10 - 83K6005WVN (R7 7735HS, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>19690000</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>55190000</v>
+        <v>26990000</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-27%</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.80 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Chống chói Anti Glare Dolby Vision 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm HDMI 2.1 2 x USB-C (hỗ trợ Thunderbolt 4/USB 4, USB Power Delivery và DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.8 mm - Rộng 212.3 mm - Dày 17.18 mm - 1.21 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 7735HS | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 680M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.39 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-x9-14-gen-1-ultra-7-258v-21qa006jvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14arp10-r7-7735hs-83k6005wvn</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:53:32</t>
+          <t>2026-07-31 13:34:15</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo V14 G5 - 83HD0035VN (Core7 240H, 16G, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="n">
-        <v>26990000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IPH11 - 83UQ003NVN (Ultra 5 322, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>25390000</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>28590000</v>
+        <v>27990000</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) LAN (RJ45) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Ion, 47 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324.2 mm - Rộng 215.2 mm - Dày 17.9 mm - 1.37 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.43 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-v14-g5-core7-240h-83hd0035vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iph11-ultra-5-322-83uq003nvn</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:53:47</t>
+          <t>2026-07-31 13:34:29</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002LVN (Ultra 5 322, 16GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="n">
-        <v>37490000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IPH11 - 83UQ003PVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>30090000</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>39990000</v>
+        <v>32990000</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.45 mm - 1.38 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.43 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-5-322-83tc002lvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iph11-ultra-7-355-83uq003pvn</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:54:03</t>
+          <t>2026-07-31 13:34:42</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002MVN (Ultra 7 355, 32GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="n">
-        <v>54490000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002NVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>24190000</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>57990000</v>
+        <v>26490000</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.95 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-7-355-83tc002mvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002nvn</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3587,83 +3624,83 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:54:17</t>
+          <t>2026-07-31 13:34:55</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga 7 2in1 OLED 14IPH11 - 83TC002JVN (Ultra 7 355, 32GB, 1TB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="n">
-        <v>53490000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002PVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>20790000</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>57990000</v>
+        <v>22990000</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Tiêu chuẩn Nền Intel Evo | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.45 mm - 1.38 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-oled-14iph11-ultra-7-355-83tc002jvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002pvn</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:54:31</t>
+          <t>2026-07-31 13:35:08</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 OLED 14AGP11 - 83QS001DVN (R7 AI 445, 16GB, 512GB, WUXGA OLED, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="n">
-        <v>37490000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 15ARP10 - 83K700YUVN (R5 7535HS, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>18690000</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>39990000</v>
+        <v>24990000</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 8000 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Glossy Display Chuẩn DisplayHDR True Black 500 Eyesafe Dolby Vision 400 nits X-Rite Flicker Free | Cổng giao tiếp:: 1 x USB Type-C (hỗ trợ DisplayPort 1.4) 2 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 221 mm - Dày 13.9 mm - 1.15 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 7535HS | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.30 GHz (Lên đến 4.55 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 660M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe RAM) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB Type-C 3.2 Gen 1 (hỗ trợ DisplayPort 1.2 và Power delivery 3.0) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Nắp lưng và chiếu nghỉ tay bằng nhôm</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-oled-14agp11-r7-ai-445-83qs001dvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15arp10-r5-7535hs-83k700yuvn</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3673,283 +3710,283 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:54:44</t>
+          <t>2026-07-31 13:35:21</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 OLED 14IPH11 - 83QM002FVN (Ultra 7 355, 32GB, 1TB, WUXGA OLED, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="n">
-        <v>52490000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 15ARP10 - 83K700YVVN (R7 7735HS, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>19890000</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>55990000</v>
+        <v>26990000</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe 600nits (peak) Dolby Vision 400 nits X-Rite Flicker Free | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 2-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 221 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 7735HS | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 660M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-oled-14iph11-ultra-7-355</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15arp10-r7-7735hs-83k700yvvn</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:54:58</t>
+          <t>2026-07-31 13:35:35</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Laptop MacBook Pro 14 inch M5 Pro 48GB/1TB</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="n">
-        <v>84990000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IPH11 - 83UR00A4VN (Ultra 5 322, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>24990000</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>85490000</v>
+        <v>27990000</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm giá 500,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Phiếu mua hàng Chuột, Bàn phím (Apple) trị giá 500,000đ | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng 50.000đ mua Chuột Logitech M240 | Tặng Phiếu mua hàng Balo, Túi chống sốc (giá trị trên 1,000,000đ) trị giá 300,000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Apple M5 Pro | Số nhân:: 15 | Số luồng:: Hãng không công bố | Tốc độ CPU:: 307 GB/s memory bandwidth | Card màn hình:: Card tích hợp - 16 nhân GPU | RAM:: 48 GB | Loại RAM:: Hãng không công bố | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 1 TB SSD | Kích thước màn hình:: 14.2" | Độ phân giải:: Liquid Retina XDR display (3024 x 1964) | Tần số quét:: up to 120 Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: ProMotion Độ sáng XDR: toàn màn hình 1000 nits, cao nhất 1600 nits (chỉ nội dung HDR) Độ sáng SDR: lên đến 1000 nits Wide color (P3) True Tone Technology 1 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm MagSafe 3 3 x Thunderbolt 5 (hỗ trợ DisplayPort, Thunderbolt 5 (up to 120Gb/s), USB 4 (up to 120Gb/s)) HDMI | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Khe đọc thẻ nhớ:: SDXC | Webcam:: Camera 12MP Center Stage | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Hệ thống âm thanh 6 loa Spatial Audio 3 microphones Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-Po, 72.4 Wh | Hệ điều hành:: macOS Tahoe | Thời điểm ra mắt:: 03/2026 | Kích thước:: Dài 312.6 mm - Rộng 221.2 mm - Dày 15.5 mm - 1.6 kg | Chất liệu:: Vỏ nhôm tái chế 100% | Hãng:: MacBook. Xem thông tin hãng</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 2.50 GHz (Lên đến 4.40 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.63 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/macbook-pro-14-inch-m5-pro-48gb-1tb</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iph11-ultra-5-322-83ur00a4vn</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:55:12</t>
+          <t>2026-07-31 13:35:48</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Laptop MacBook Pro 14 inch M5 Pro 48GB/2TB</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="n">
-        <v>98690000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IPH11 - 83UR0075VN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>28990000</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>99190000</v>
+        <v>32990000</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm giá 500,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Phiếu mua hàng Chuột, Bàn phím (Apple) trị giá 500,000đ | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng 50.000đ mua Chuột Logitech M240 | Tặng Phiếu mua hàng Balo, Túi chống sốc (giá trị trên 1,000,000đ) trị giá 300,000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Apple M5 Pro | Số nhân:: 15 | Số luồng:: Hãng không công bố | Tốc độ CPU:: 307 GB/s memory bandwidth | Card màn hình:: Card tích hợp - 16 nhân GPU | RAM:: 48 GB | Loại RAM:: Hãng không công bố | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 2 TB SSD | Kích thước màn hình:: 14.2" | Độ phân giải:: Liquid Retina XDR display (3024 x 1964) | Tần số quét:: up to 120 Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: ProMotion Độ sáng XDR: toàn màn hình 1000 nits, cao nhất 1600 nits (chỉ nội dung HDR) Độ sáng SDR: lên đến 1000 nits Wide color (P3) True Tone Technology 1 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm MagSafe 3 3 x Thunderbolt 5 (hỗ trợ DisplayPort, Thunderbolt 5 (up to 120Gb/s), USB 4 (up to 120Gb/s)) HDMI | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Khe đọc thẻ nhớ:: SDXC | Webcam:: Camera 12MP Center Stage | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Hệ thống âm thanh 6 loa Spatial Audio 3 microphones Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-Po, 72.4 Wh | Hệ điều hành:: macOS Tahoe | Thời điểm ra mắt:: 03/2026 | Kích thước:: Dài 312.6 mm - Rộng 221.2 mm - Dày 15.5 mm - 1.6 kg | Chất liệu:: Vỏ nhôm tái chế 100% | Hãng:: MacBook. Xem thông tin hãng</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4 1 x USB Type-C (hỗ trợ USB, Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.63 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/macbook-pro-14-inch-m5-pro-48gb-2tb</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iph11-ultra-7-355-83ur0075vn</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:55:25</t>
+          <t>2026-07-31 13:36:01</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Gaming Cyborg 15 Black Edition A13VE - A13VE-2410VN (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="n">
-        <v>27990000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IPH11 - 83UR00A5VN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>29490000</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>31990000</v>
+        <v>32990000</v>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.60 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Công nghệ âm thanh:: Hi-Res Audio DTS Audio | Tản nhiệt:: Cooler Boost 1 x Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 53.5 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.36 mm - Rộng 250.34 mm - Dày 22.9 mm - 1.98 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.63 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-black-edition-a13ve-i5-13420h-a13ve-2410vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iph11-ultra-7-355-83ur00a5vn</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:55:39</t>
+          <t>2026-07-31 13:36:14</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Gaming Cyborg 15 C13WEO-417VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="n">
-        <v>35590000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00A8VN (Core 3 304, 8GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>18990000</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>36990000</v>
+        <v>20890000</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card rời - Intel UHD Graphics (tích hợp) + NVIDIA GeForce RTX 5050 GPU, 8GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB Type-A 1 x Headphone/ Microphone combo audio jack 1 x USB Type C (chỉ hỗ trợ Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: DTS Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.98 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core™ 3 - 304 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz (P-core), Turbo tối đa 4.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 2242 PCIe 4.0x4 NVMe | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 × USB-C (USB 5 Gbps), hỗ trợ USB PD 45–65W và DisplayPort 1.2 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Optimized with Dolby Audio 2W x 2 High Definition (HD) Audio Stereo speakers | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 240 mm - Rộng 343 mm - Dày 17 - 18 - 1.59 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-c13weo-417vn-i7-13620h</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-3-304-83rr00a8vn</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:55:52</t>
+          <t>2026-07-31 13:36:27</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Gaming Raider 16 MAX HX B2WI - 095VN (Ultra 9 290HX Plus, 64GB, 2TB, RTX 5080 16GB, QHD+ OLED 240Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="n">
-        <v>1350000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00AAVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>23590000</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1590000</v>
+        <v>26490000</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 9 Arrow Lake - 290HX Plus | Số nhân:: 24 | Số luồng:: 24 | Tốc độ CPU:: 2.70 GHz (Lên đến 5.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 1334 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5080, 16 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 175 W | RAM:: 64 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe 32 GB) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: 128 GB | Ổ cứng:: 2 TB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 4 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: QHD+ (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 240Hz | Độ phủ màu:: 100% DCI-P3 | Cổng giao tiếp:: 2 x Thunderbolt 4 (hỗ trợ Power Delivery 3.1 và DisplayPort) 3 x USB Type-A 3.2 Gen 2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Cooler Boost 3 Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-Po, 91.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 363 mm - Rộng 269.7 mm - Dày 28.85 mm - 2.6 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-gaming-raider-16-max-hx-b2wi-ultra-9-290hx-plus-095vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00aavn</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:56:06</t>
+          <t>2026-07-31 13:36:40</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 F1MG-1264VN (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="n">
-        <v>19990000</v>
+          <t>Laptop Lenovo Ideapad Slim 3 15IWC11 - 83RR00CVVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>20190000</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>22390000</v>
+        <v>22990000</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -3959,595 +3996,563 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core thế hệ 12 - 120U | Số nhân:: Hãng không công bố | Số luồng:: 12 | Tốc độ CPU:: 1.45 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (2280) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: Hãng không công bố | Cổng giao tiếp:: 3 x USB 3.2 Gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell, 46.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.7 kg | Chất liệu:: Plastic (nhựa dẻo)</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-modern-15-f1mg-1264vn-core-5-120u</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00cvvn</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:56:20</t>
+          <t>2026-07-31 13:36:54</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Laptop SingPC M16-i382 (i3 1215U, 8GB, 256GB, WUXGA, Win11 Pro)</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="n">
-        <v>13890000</v>
+          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US002TVN (Ultra 5 322, 24GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>30090000</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>15190000</v>
+        <v>31990000</v>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i3 Alder Lake - 1215U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.2GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 256 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 24 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/singpc-m16-i382-i3-1215u</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-5-322-83us002tvn</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:56:33</t>
+          <t>2026-07-31 13:37:07</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Laptop SingPC M16-i595 (i5 1235U, 16GB, 512GB, WUXGA, Win11 Pro)</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="n">
-        <v>18390000</v>
-      </c>
-      <c r="C85" s="2" t="n">
-        <v>19990000</v>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>-8%</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
+          <t>Laptop Dell 15 DC15250 - DC5C3851W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>22590000</v>
+      </c>
+      <c r="C85" s="2" t="inlineStr"/>
+      <c r="D85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Alder Lake - 1235U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.30 GHz (Lên đến 4.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 72% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x Headphone/ Microphone combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 2 x USB 2.0 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 235 mm - Rộng 358.5 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/singpc-m16-i595-i5-1235u</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3851w1-2y</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:56:46</t>
+          <t>2026-07-31 14:37:36</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus TUF Gaming FX608JHI - TU209W (i7 14650HX, 16GB, 512GB, RTX5050 8GB, Full HD+ 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="n">
-        <v>41590000</v>
+          <t>Laptop Dell 15 DC15250 - CPH992 (i5 1334U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365B, Win11)</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>21990000</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>42990000</v>
+        <v>23490000</v>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 500.000đ mua Chuột Gaming Logitech dòng Pro X | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 14650HX | Số nhân:: 16 | Số luồng:: 24 | Tốc độ CPU:: 2.20 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 2TB) 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB 72% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: AI noise-canceling technology Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 269 mm - Dày 27.3 mm - 2.2 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 1334U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 2666 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Bluetooth 5.0 Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235.6 mm - Dày 19 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-tuf-gaming-fx608jhi-i7-14650hx-tu209w</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-i5-1334u-cph992</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:55:59</t>
+          <t>2026-07-31 14:37:50</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1404MA - EB028W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="n">
-        <v>31990000</v>
+          <t>Laptop Dell 15 DC15250 - DC15250-i5U165W11SLU-27 (i5 1334U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>21990000</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>1590000</v>
+        <v>23490000</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Core i5 - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 SO-DIMM | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Hãng không công bố | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 21.39 mm - Rộng 32.49 mm - Dày 1.79 mm - 1.4 kg | Chất liệu:: Khung nhôm - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 1334U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.30 GHz (Lên đến 4.60 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm HDD SATA (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 18.99 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1404ma-core-5-320-eb028w</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-i5-1334u-dc15250-i5u165w11slu-27</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:56:13</t>
+          <t>2026-07-31 14:38:03</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1404MA - EB219W (Core 5 320, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="n">
-        <v>21390000</v>
+          <t>Laptop Dell 15 DC15250 - DC15250-i7U161W11SLU-27 (i7 1355U, 16GB, 1TB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>26990000</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>26990000</v>
+        <v>27490000</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 8 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 324.9 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.409 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 1355U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.70 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-Po, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 18.99 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1404ma-core-5-320-eb219w</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-i7-1355u-dc15250-i7u161w11slu-27</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:56:25</t>
+          <t>2026-07-31 14:38:16</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1407AA - LY360W (Ultra 5 325, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="n">
-        <v>24890000</v>
+          <t>Laptop Dell 15 DC15255 - DC5R5973W1-2Y (R5 7530U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>24990000</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>26990000</v>
+        <v>25690000</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 325 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB onboard + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) Hỗ trợ thêm 1 khe cắm SSD NVMe M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 19.9 mm - 1.46 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 7530U | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/microphone combo 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1407aa-ultra-5-325-ly360w</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r5-7530u-dc5r5973w1-2y</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:56:39</t>
+          <t>2026-07-31 14:38:30</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1407CA - LY203W (Ultra 5 225H, 16GB, 512GB, WUXGA OLED, Win11)</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="n">
-        <v>23990000</v>
+          <t>Laptop Dell 16 DC16250 - 71092481 (Core 5 120U, 16GB, 1TB, Full HD+, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>27990000</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>33490000</v>
+        <v>28490000</v>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>-28%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 19.9 mm - 1.46 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Display with ComfortView Wide viewing angle Chống chói Anti Glare | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1x Global headset jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD RGB | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Bảo mật vân tay | Công nghệ âm thanh:: Realtek ALC32xx | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 249.52 mm - Dày 17.37 mm - 1.98 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1407ca-ultra-5-225h-ly203w</t>
+          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-5-120u-71092481</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:56:52</t>
+          <t>2026-07-31 14:38:43</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ385W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="n">
-        <v>26090000</v>
-      </c>
-      <c r="C91" s="2" t="n">
-        <v>31990000</v>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>-18%</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
+          <t>Laptop Dell 16 DC16250 - 71100513 (Core 5 120U, 16GB, 1TB, Full HD+, OfficeH24+365B, Win11)</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr"/>
+      <c r="D91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits eDP Wide View Angle | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2W x 2 Realtek ALC3254 Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 05/2025 | Kích thước:: Dài 357.3 mm - Rộng 250.6 mm - Dày 18.23 mm - 2 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-5-320-bq385w</t>
+          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-5-120u-71100513</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:57:05</t>
+          <t>2026-07-31 14:38:57</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ632W (Core 5 320, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="n">
-        <v>21390000</v>
+          <t>Laptop Dell 16 DC16250 - DC16250-C7U161W11BLU-27 (Core 7 150U, 16GB, 1TB, Full HD+, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>35290000</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>26990000</v>
+        <v>35990000</v>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 8 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits ComfortView Plus | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.3 mm - Rộng 250.6 mm - Dày 18.23 mm - 2 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-5-320-bq632w</t>
+          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-7-150u-dc16250-c7u161w11blu-27</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:57:21</t>
+          <t>2026-07-31 14:39:11</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ395W (Core 7 350, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="n">
-        <v>28490000</v>
+          <t>Laptop Dell Pro 14 PC14250 - PC14250-235U-16512WP-2Y (Ultra 5 235U, 16GB, 512GB, Full HD+, Win11Pro)</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>38290000</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>35490000</v>
+        <v>39990000</v>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Wildcat Lake - 350 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 17 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 235U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 2.0 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1x Global headset jack 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4, USB Power Delivery 3.1 and DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-7-350-bq395w</t>
+          <t>https://www.thegioididong.com/laptop/dell-pro-14-pc14250-ultra-5-235u-pc14250-235u-16512wp-2y</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:57:34</t>
+          <t>2026-07-31 14:39:24</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ633W (Core 7 350, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="n">
-        <v>25190000</v>
+          <t>Laptop Dell Pro 14 PC14250 - PC14250-255U-32512WH-2Y (Ultra 7 255U, 32GB, 512GB, Full HD+, Win11)</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>55290000</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>30490000</v>
+        <v>56690000</v>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Wildcat Lake - 350 | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 8 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 2.0 GHz (Lên đến 5.2 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe trống) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1x Global headset jack 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4, USB Power Delivery 3.1 and DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-7-350-bq633w</t>
+          <t>https://www.thegioididong.com/laptop/dell-pro-14-pc14250-ultra-7-255u-pc14250-255u-32512wh-2y</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:57:47</t>
+          <t>2026-07-31 14:39:39</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 16 X1607CA - MB387W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="n">
-        <v>24590000</v>
-      </c>
-      <c r="C95" s="2" t="n">
-        <v>33490000</v>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>-27%</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
-        </is>
-      </c>
+          <t>Laptop Dell Pro 15 Essential PV15250 - PV15250-100U-8512W-2Y (Core 3 100U, 8GB, 512GB, Full HD, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>23990000</v>
+      </c>
+      <c r="C95" s="2" t="inlineStr"/>
+      <c r="D95" s="2" t="inlineStr"/>
+      <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.7 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 SO-DIMM | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 25.06 mm - Rộng 35.7 mm - Dày 1.79 ~ 1.99 - 1.88 kg | Chất liệu:: Khung nhôm - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Rộng 358.5 mm - Dày 17.5 mm | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-16-x1607ca-ultra-5-225h-mb387w</t>
+          <t>https://www.thegioididong.com/laptop/dell-pro-15-essential-pv15250-core-3-100u-pv15250-100u-8512w-2y</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:58:00</t>
+          <t>2026-07-31 14:39:53</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook Go 14 E1404FA - EB012W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="n">
-        <v>16990000</v>
+          <t>Laptop HP 15 fd1487TU - D0BH4PA (Ultra 5 125H, 24GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>22490000</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>22990000</v>
+        <v>24390000</v>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>-26%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 125H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 24 GB | Loại RAM:: DDR5 (1 khe RAM) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB Type-A HDMI 1.4b 1 x USB Type - C (hỗ trợ Power Delivery, DisplayPort 1.4b, HP Sleep and Charge) 1 x Headphone/microphone combo | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.8 mm - Rộng 236 mm - Dày 18.6 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb012w</t>
+          <t>https://www.thegioididong.com/laptop/hp-15-fd1487tu-ultra-5-125h-d0bh4pa</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:58:12</t>
+          <t>2026-07-31 14:40:05</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook Go 14 E1404FA - EB1832W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="n">
+          <t>Laptop HP 15 fd2126TU - D72CBPA (Ultra 5 225U, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n">
         <v>22990000</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>1590000</v>
+        <v>26990000</v>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
@@ -4556,619 +4561,643 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: Hãng không công bố | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB Type-A 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack HDMI | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.8 mm - Rộng 236 mm - Dày 18.6 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb1832w</t>
+          <t>https://www.thegioididong.com/laptop/hp-15-fd2126tu-ultra-5-225u-d72cbpa</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:58:25</t>
+          <t>2026-07-31 14:40:18</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook S 16 S3607VA - RP155W (Core 5 210H, 16GB, 512GB, Full HD+ 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="n">
-        <v>31490000</v>
+          <t>Laptop HP 15 fd2127TU - D72CCPA (Ultra 5 225U, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>22990000</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>34990000</v>
+        <v>26990000</v>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Hãng không công bố | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare LED Backlit | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 259.6 mm - Dày 15.9 mm - 1.7 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.40 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 2800 MHz | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB Type-A HDMI 1.4b 1 x USB Type - C (hỗ trợ Power Delivery 3.1, DisplayPort 1.4b, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.8 mm - Rộng 236 mm - Dày 18.6 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-s-16-s3607va-core-5-210h-rp155w</t>
+          <t>https://www.thegioididong.com/laptop/hp-15-fd2127tu-ultra-5-225u-d72ccpa</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:58:40</t>
+          <t>2026-07-31 14:40:32</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook S14 S3407AA - SF945W (Ultra 5 325, 16GB, 512GB, WUXGA OLED, Win11)</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="n">
-        <v>31990000</v>
-      </c>
-      <c r="C99" s="2" t="inlineStr"/>
-      <c r="D99" s="2" t="inlineStr"/>
+          <t>Laptop HP 240R G10 - C3SG9AT (Core 5 120U, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>20490000</v>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>23590000</v>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - Đang cập nhật | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Đang cập nhật | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 95% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 17.9 mm - 1.4 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack HDMI | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HP TrueVision Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 323.7 mm - Rộng 215 mm - Dày 13.2 mm - 1.404 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-s14-s3407aa-ultra-5-325-sf945w</t>
+          <t>https://www.thegioididong.com/laptop/hp-240r-g10-core-5-120u-c3sg9at</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:58:53</t>
+          <t>2026-07-31 14:40:45</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook S14 S3407VA - LY256W (Core 7 240H, 16GB, 512GB, WUXGA OLED, Win11)</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="n">
-        <v>28090000</v>
+          <t>Laptop HP 240R G10 - CC9B9PT (Core 7 150U, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>23990000</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>29990000</v>
+        <v>29590000</v>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-19%</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 17.9 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x USB Type-C (Power Delivery, DisplayPort 1.4, HP Sleep and Charge) 2 x USB Type-A HDMI 1.4b 1 x Headphone/ Microphone combo audio jack | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 323.7 mm - Rộng 215 mm - Dày 13.2 mm - 1.406 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-s14-s3407va-core-7-240h-ly256w</t>
+          <t>https://www.thegioididong.com/laptop/hp-240r-g10-core-7-150u-cc9b9pt</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:59:07</t>
+          <t>2026-07-31 14:40:58</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Zenbook 14 UM3406GA - QD075W (R7 AI 445, 16GB, 512GB, WUXGA OLED, Win11)</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="n">
-        <v>34490000</v>
+          <t>Laptop HP 240R G9 - C40LGAT (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>24490000</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>39990000</v>
+        <v>26590000</v>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.0 GHz | NPU:: AMD XDNA | Card màn hình:: Card tích hợp | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 70% Less harmful blue light 400 nits 600 nits (Khi bật HDR) | Cổng giao tiếp:: 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 75 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.01 mm - Rộng 31.24 mm - Dày 1.49 mm - 1.2 kg | Chất liệu:: Nhôm nguyên khối</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HP TrueVision Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324 mm - Rộng 225.9 mm - Dày 9.4 mm - 1.406 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-zenbook-14-um3406ga-r7-ai-445-qd075w</t>
+          <t>https://www.thegioididong.com/laptop/hp-240r-g9-core-5-120u-c40lgat</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:59:21</t>
+          <t>2026-07-31 14:41:12</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Zenbook A14 UX3407NA - QD132WS (X2E 88 100, 16GB, 512GB, WUXGA OLED, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="n">
-        <v>44490000</v>
+          <t>Laptop HP 240R G9 - C40M2AT (Core 5 120U, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>18990000</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>48990000</v>
+        <v>23590000</v>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-19%</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Snapdragon X2 Elite - X2E88100 | Số nhân:: 18 | Số luồng:: 18 | Tốc độ CPU:: Lên đến 4.0 GHz khi tải nặng | NPU:: Qualcomm Hexagon | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | Card màn hình:: Card tích hợp - Qualcomm Adreno GPU | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 9523 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: VESA DisplayHDR Thời gian phản hồi 0.2 ms Màn hình bảo vệ mắt - EYE CARE Low Blue Light Chống chói Anti Glare 400 nits 600 nits (Khi bật HDR) 1.07 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Công nghệ Smart AMP | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.7 mm - Rộng 213.9 mm - Dày 15.9 mm - 0.986 kg | Chất liệu:: Vỏ gốm nhôm Ceraluminum</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HP TrueVision Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324 mm - Rộng 225.9 mm - Dày 9.4 mm - 1.406 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-zenbook-a14-ux3407na-x2e-88-100-qd132ws</t>
+          <t>https://www.thegioididong.com/laptop/hp-240r-g9-core-5-120u-c40m2at</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:59:36</t>
+          <t>2026-07-31 14:41:26</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Zenbook A14 UX3407NA - QD254W (X2E 88 100, 32GB, 1TB, WUXGA OLED, Win11)</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="n">
-        <v>58190000</v>
+          <t>Laptop HP 240R G9 - AX3C6AT (i3 1315U, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>14490000</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>63990000</v>
+        <v>16390000</v>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Snapdragon X2 Elite - X2E88100 | Số nhân:: 18 | Số luồng:: 18 | Tốc độ CPU:: Lên đến 4.0 GHz khi tải nặng | NPU:: Qualcomm Hexagon | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | Card màn hình:: Card tích hợp - Qualcomm Adreno GPU | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 9523 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: VESA DisplayHDR Thời gian phản hồi 0.2 ms Màn hình bảo vệ mắt - EYE CARE Low Blue Light Chống chói Anti Glare 400 nits 600 nits (Khi bật HDR) 1.07 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Công nghệ Smart AMP | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.7 mm - Rộng 213.9 mm - Dày 15.9 mm - 0.986 kg | Chất liệu:: Vỏ gốm nhôm Ceraluminum</t>
+          <t>Công nghệ CPU:: Intel Core i3 Raptor Lake - 1315U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.50 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324 mm - Rộng 225.9 mm - Dày 9.4 mm - 1.397 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-zenbook-a14-ux3407na-x2e-88-100-qd254w</t>
+          <t>https://www.thegioididong.com/laptop/hp-240r-g9-i3-1315u-ax3c6at</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:59:50</t>
+          <t>2026-07-31 14:41:40</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Zenbook S 16 UM5606GA - SS441W (R9 AI 465, 16GB, 512GB, 3K OLED 120Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="n">
-        <v>49490000</v>
-      </c>
-      <c r="C104" s="2" t="inlineStr"/>
-      <c r="D104" s="2" t="inlineStr"/>
+          <t>Laptop HP EliteBook 6 G1a 14 - C0CE1PT (R5 AI 340, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>30190000</v>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>31590000</v>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 9 - 465 | Số nhân:: 10 | Số luồng:: 20 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Màn hình bảo vệ mắt - EYE CARE Low Blue Light DisplayHDR True Black 1000 500 nits Chống chói Anti Glare 1100 nits (peak) | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Công nghệ Smart AMP | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 83 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 353.6 mm - Rộng 243 mm - Dày 12.9 mm - 1.5 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.528 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-zenbook-s-16-um5606ga-r9-ai-465-ss441w</t>
+          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r5-ai-340-c0ce1pt</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:00:03</t>
+          <t>2026-07-31 14:41:54</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC14250-C3U085W11SLU-27 (Core 3 100U, 8GB, 512GB, Full HD+, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="n">
-        <v>19190000</v>
+          <t>Laptop HP EliteBook 6 G1a 14 - C0CF2PT (R5 AI 340, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>31190000</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>19390000</v>
+        <v>32590000</v>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits ComfortView Plus | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.528 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-3-100u-dc14250-c3u085w11slu-27</t>
+          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r5-ai-340-c0cf2pt</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:00:18</t>
+          <t>2026-07-31 14:42:08</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC4C5375W1-2Y (Core 5 120U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="n">
-        <v>30990000</v>
+          <t>Laptop HP EliteBook 6 G1a 14 - C0CE2PT (R7 AI 350, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>34290000</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>32090000</v>
+        <v>35690000</v>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226 mm - Dày 18 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.549 kg | Chất liệu:: Nắp lưng và chiếu nghỉ tay bằng kim loại</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-5-120u-dc4c5375w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r7-ai-350-c0ce2pt</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:00:32</t>
+          <t>2026-07-31 14:42:22</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - 71092478 (Core 7 150U, 16GB, 512GB, Full HD+ 120Hz, OfficeHS24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="n">
-        <v>28390000</v>
-      </c>
-      <c r="C107" s="2" t="inlineStr"/>
-      <c r="D107" s="2" t="inlineStr"/>
+          <t>Laptop HP EliteBook 6 G1a 14 - C0CG2PT (R7 AI 350, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>33290000</v>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>34690000</v>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.20 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Display with ComfortView Wide viewing angle Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD RGB | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Cirrus Logic CS42L43 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-Po, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 320 mm - Rộng 215.97 mm - Dày 18.02 mm - 1.83 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.531 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-71092478</t>
+          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r7-ai-350-c0cg2pt</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:00:45</t>
+          <t>2026-07-31 14:42:35</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - 71100515 (Core 7 150U, 16GB, 512GB, Full HD+ 120Hz, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="n">
-        <v>35490000</v>
+          <t>Laptop HP EliteBook 8 G1a 14 - C0CE5PT (R7 AI PRO 350, 32GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>37790000</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>1590000</v>
+        <v>39190000</v>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 320 mm - Rộng 215.97 mm - Dày 18.02 mm - 1.83 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x USB 3.2. 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1 x Headphone/microphone combo 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 62 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 315.6 mm - Rộng 222 mm - Dày 15.5 mm - 1.564 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-71100515</t>
+          <t>https://www.thegioididong.com/laptop/hp-elitebook-8-g1a-14-ai-350-c0ce5pt</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:00:58</t>
+          <t>2026-07-31 14:42:50</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC14250-C7U161W11SLU-27 (Core 7 150U, 16GB, 1TB, Full HD+, OfficeHS24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="n">
-        <v>29890000</v>
-      </c>
-      <c r="C109" s="2" t="inlineStr"/>
-      <c r="D109" s="2" t="inlineStr"/>
+          <t>Laptop HP EliteBook 8 G1a 14 - C0CE3PT (R5 AI PRO 340, 32GB, 512GB, WUXGA, Cảm ứng, Win11 Pro)</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>40790000</v>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>42190000</v>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 5 Pro - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x USB A 2 x Thunderbolt 4 (Hỗ trợ Power Delivery, DisplayPort 2.1, HP Sleep and Charge) 1 x Headphone/microphone combo HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 62 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 315.6 mm - Rộng 222 mm - Dày 15.5 mm - 1.39 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-dc14250-c7u161w11slu-27</t>
+          <t>https://www.thegioididong.com/laptop/hp-elitebook-8-g1a-14-r5-ai-pro-340-c0ce3pt</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:01:12</t>
+          <t>2026-07-31 14:43:04</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC14250-C7U161W11SLU-2Y (Core 7 150U, 16GB, 1TB, Full HD+ ,OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="n">
-        <v>37990000</v>
+          <t>Laptop HP Gaming HyperX Omen 15 ga0092TX - D72D8PA (i5 14450HX, 16GB, 512GB, RTX 5050 8GB, WUXGA 165Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>45590000</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>1590000</v>
+        <v>46990000</v>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: E-core: 0.9 GHz - 3.3 GHz, P-core: 1.2 GHz - 4.7 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MT/s | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 PCIe Gen 4 x 4 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (M.2 2230)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Display with ComfortView Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.615 mm - Rộng 31.4 mm - Dày 1.669 ~ 1.807 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 421 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.37 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-dc14250-c7u161w11slu-2y</t>
+          <t>https://www.thegioididong.com/laptop/hp-gaming-hyperx-omen-15-ga0092tx-i5-14450hx-d72d8pa</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:01:26</t>
+          <t>2026-07-31 14:43:17</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14255 - 71092477 (R7 350, 16GB, 1TB, Full HD+, OfficeHS24+365B, Win11)</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="n">
-        <v>32490000</v>
+          <t>Laptop HP Gaming VICTUS 15 fa2451TX - D17WPPA (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>27490000</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>33190000</v>
+        <v>31990000</v>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB onboard + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Display with ComfortView Wide viewing angle Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3204 Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-Po, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày `19.9 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35W - 115W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x USB 3.2 1 x USB 3.2 (hỗ trợ HP Sleep and Charge) 1 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358 mm - Rộng 255 mm - Dày 23.5 mm - 2.29 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14255-r7-350-71092477</t>
+          <t>https://www.thegioididong.com/laptop/hp-gaming-victus-15-fa2451tx-i5-13420h-d17wppa</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:01:41</t>
+          <t>2026-07-31 14:43:31</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - 71100520 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="n">
-        <v>21990000</v>
+          <t>Laptop HP HyperX Omen 15 ga0091TX - D72D7PA (i5 14450HX, 16GB, 512GB, RTX 5060 8GB, WUXGA 165Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>48590000</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>22590000</v>
+        <v>49990000</v>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
@@ -5177,84 +5206,84 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort 1.4, Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Bluetooth 5.0 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.5 mm - Dày 18.9 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3840 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 614 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.363 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-71100520</t>
+          <t>https://www.thegioididong.com/laptop/hp-hyperx-omen-15-ga0091tx-i5-14450h-d72d7pa</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:01:54</t>
+          <t>2026-07-31 14:43:44</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - CPH993 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="n">
-        <v>21990000</v>
+          <t>Laptop HP OmniBook 7 Aero 13 bg1087AU - BZ7S1PA (R5 AI 340, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>27990000</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>22590000</v>
+        <v>29790000</v>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: Đang cập nhật | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 70% Less harmful blue light 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 16.96 mm đến 18.99 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCie Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4TB) | Kích thước màn hình:: 13.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 400 nits | Cổng giao tiếp:: 2 x USB Type-A 2 x USB Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/microphone combo HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E MT7922 Bluetooth 5.3 | Webcam:: HP 5MP Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Poly Studio HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 43 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 297.3 mm - Rộng 211.2 mm - Dày 17.4 mm - 0.99 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-cph993</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-7-aero-13-bg1087au-r5-ai-340-bz7s1pa</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:02:07</t>
+          <t>2026-07-31 14:43:58</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - DC5C3259W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="n">
-        <v>21990000</v>
+          <t>Laptop Asus TUF Gaming FX608JHI - TU209W (i7 14650HX, 16GB, 512GB, RTX5050 8GB, Full HD+ 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>41590000</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>22590000</v>
+        <v>42990000</v>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
@@ -5263,1096 +5292,1116 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 500.000đ mua Chuột Gaming Logitech dòng Pro X | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 14650HX | Số nhân:: 16 | Số luồng:: 24 | Tốc độ CPU:: 2.20 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 2TB) 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB 72% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: AI noise-canceling technology Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 269 mm - Dày 27.3 mm - 2.2 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3259w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/asus-tuf-gaming-fx608jhi-i7-14650hx-tu209w</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:02:20</t>
+          <t>2026-07-31 14:03:47</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - DC5C3851W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="n">
-        <v>22590000</v>
-      </c>
-      <c r="C115" s="2" t="inlineStr"/>
-      <c r="D115" s="2" t="inlineStr"/>
-      <c r="E115" s="2" t="inlineStr"/>
+          <t>Laptop Asus Vivobook 14 X1404MA - EB028W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>26490000</v>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>31990000</v>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>-17%</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+        </is>
+      </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x Headphone/ Microphone combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 2 x USB 2.0 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 235 mm - Rộng 358.5 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Core i5 - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 SO-DIMM | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Hãng không công bố | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 21.39 mm - Rộng 32.49 mm - Dày 1.79 mm - 1.4 kg | Chất liệu:: Khung nhôm - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3851w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1404ma-core-5-320-eb028w</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:57:41</t>
+          <t>2026-07-31 14:04:02</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - CPH992 (i5 1334U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365B, Win11)</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="n">
-        <v>21990000</v>
+          <t>Laptop Asus Vivobook 14 X1404MA - EB219W (Core 5 320, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>21390000</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>23490000</v>
+        <v>26990000</v>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 1334U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 2666 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Bluetooth 5.0 Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235.6 mm - Dày 19 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 8 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 324.9 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.409 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-i5-1334u-cph992</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1404ma-core-5-320-eb219w</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:57:55</t>
+          <t>2026-07-31 14:04:14</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - DC15250-i5U165W11SLU-27 (i5 1334U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="n">
-        <v>21990000</v>
+          <t>Laptop ASUS Vivobook 14 X1407AA - LY360W (Ultra 5 325, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>23790000</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>23490000</v>
+        <v>26990000</v>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 1334U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.30 GHz (Lên đến 4.60 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm HDD SATA (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 18.99 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 325 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB onboard + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) Hỗ trợ thêm 1 khe cắm SSD NVMe M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 19.9 mm - 1.46 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-i5-1334u-dc15250-i5u165w11slu-27</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1407aa-ultra-5-325-ly360w</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:58:09</t>
+          <t>2026-07-31 14:04:28</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - DC15250-i7U161W11SLU-27 (i7 1355U, 16GB, 1TB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="n">
-        <v>26990000</v>
+          <t>Laptop Asus Vivobook 14 X1407CA - LY203W (Ultra 5 225H, 16GB, 512GB, WUXGA OLED, Win11)</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>23990000</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>27490000</v>
+        <v>33490000</v>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-28%</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 1355U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.70 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-Po, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 18.99 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 19.9 mm - 1.46 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-i7-1355u-dc15250-i7u161w11slu-27</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1407ca-ultra-5-225h-ly203w</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:58:23</t>
+          <t>2026-07-31 14:04:41</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15255 - DC5R5973W1-2Y (R5 7530U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="n">
-        <v>24990000</v>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ385W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>26090000</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>25690000</v>
+        <v>31990000</v>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 7530U | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/microphone combo 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r5-7530u-dc5r5973w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-5-320-bq385w</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:58:37</t>
+          <t>2026-07-31 14:04:54</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 16 DC16250 - 71092481 (Core 5 120U, 16GB, 1TB, Full HD+, OfficeHS24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="n">
-        <v>27990000</v>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ632W (Core 5 320, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>21390000</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>28490000</v>
+        <v>26990000</v>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Display with ComfortView Wide viewing angle Chống chói Anti Glare | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1x Global headset jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD RGB | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Bảo mật vân tay | Công nghệ âm thanh:: Realtek ALC32xx | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 249.52 mm - Dày 17.37 mm - 1.98 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 8 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-5-120u-71092481</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-5-320-bq632w</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:58:51</t>
+          <t>2026-07-31 14:05:08</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 16 DC16250 - DC16250-C7U161W11BLU-27 (Core 7 150U, 16GB, 1TB, Full HD+, OfficeHS24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="n">
-        <v>35290000</v>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ395W (Core 7 350, 16GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>28490000</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>35990000</v>
+        <v>35490000</v>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits ComfortView Plus | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.3 mm - Rộng 250.6 mm - Dày 18.23 mm - 2 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Wildcat Lake - 350 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 17 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-7-150u-dc16250-c7u161w11blu-27</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-7-350-bq395w</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:59:04</t>
+          <t>2026-07-31 14:05:22</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell Pro 14 PC14250 - PC14250-235U-16512WP-2Y (Ultra 5 235U, 16GB, 512GB, Full HD+, Win11Pro)</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="n">
-        <v>38290000</v>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ633W (Core 7 350, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>25190000</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>39990000</v>
+        <v>30490000</v>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 235U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 2.0 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1x Global headset jack 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4, USB Power Delivery 3.1 and DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Wildcat Lake - 350 | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 8 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-pro-14-pc14250-ultra-5-235u-pc14250-235u-16512wp-2y</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-7-350-bq633w</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:59:18</t>
+          <t>2026-07-31 14:05:36</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell Pro 14 PC14250 - PC14250-255U-32512WH-2Y (Ultra 7 255U, 32GB, 512GB, Full HD+, Win11)</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="n">
-        <v>55290000</v>
+          <t>Laptop Asus Vivobook 16 X1607CA - MB387W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>24590000</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>56690000</v>
+        <v>33490000</v>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-27%</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 2.0 GHz (Lên đến 5.2 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe trống) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1x Global headset jack 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4, USB Power Delivery 3.1 and DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.7 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 SO-DIMM | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 25.06 mm - Rộng 35.7 mm - Dày 1.79 ~ 1.99 - 1.88 kg | Chất liệu:: Khung nhôm - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-pro-14-pc14250-ultra-7-255u-pc14250-255u-32512wh-2y</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-16-x1607ca-ultra-5-225h-mb387w</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:59:33</t>
+          <t>2026-07-31 14:05:51</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell Pro 15 Essential PV15250 - PV15250-100U-8512W-2Y (Core 3 100U, 8GB, 512GB, Full HD, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="n">
-        <v>23990000</v>
-      </c>
-      <c r="C124" s="2" t="inlineStr"/>
-      <c r="D124" s="2" t="inlineStr"/>
-      <c r="E124" s="2" t="inlineStr"/>
+          <t>Laptop Asus Vivobook Go 14 E1404FA - EB012W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>16590000</v>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>22990000</v>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>-28%</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Rộng 358.5 mm - Dày 17.5 mm | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-pro-15-essential-pv15250-core-3-100u-pv15250-100u-8512w-2y</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb012w</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:59:47</t>
+          <t>2026-07-31 14:06:04</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 15 fd1487TU - D0BH4PA (Ultra 5 125H, 24GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="n">
-        <v>22490000</v>
+          <t>Laptop Asus Vivobook Go 14 E1404FA - EB1832W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>16990000</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>24390000</v>
+        <v>22990000</v>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 125H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 24 GB | Loại RAM:: DDR5 (1 khe RAM) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB Type-A HDMI 1.4b 1 x USB Type - C (hỗ trợ Power Delivery, DisplayPort 1.4b, HP Sleep and Charge) 1 x Headphone/microphone combo | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.8 mm - Rộng 236 mm - Dày 18.6 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-15-fd1487tu-ultra-5-125h-d0bh4pa</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb1832w</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:59:59</t>
+          <t>2026-07-31 14:06:18</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 15 fd2126TU - D72CBPA (Ultra 5 225U, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="n">
-        <v>22990000</v>
+          <t>Laptop Asus Vivobook S 16 S3607VA - RP155W (Core 5 210H, 16GB, 512GB, Full HD+ 144Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>30090000</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>26990000</v>
+        <v>34990000</v>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: Hãng không công bố | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB Type-A 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack HDMI | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.8 mm - Rộng 236 mm - Dày 18.6 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Hãng không công bố | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare LED Backlit | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 259.6 mm - Dày 15.9 mm - 1.7 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-15-fd2126tu-ultra-5-225u-d72cbpa</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-s-16-s3607va-core-5-210h-rp155w</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:00:14</t>
+          <t>2026-07-31 14:06:31</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 15 fd2127TU - D72CCPA (Ultra 5 225U, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="n">
-        <v>22990000</v>
+          <t>Laptop Asus Vivobook S14 S3407AA - SF945W (Ultra 5 325, 16GB, 512GB, WUXGA OLED, Win11)</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>29790000</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>26990000</v>
+        <v>31990000</v>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.40 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 2800 MHz | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB Type-A HDMI 1.4b 1 x USB Type - C (hỗ trợ Power Delivery 3.1, DisplayPort 1.4b, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.8 mm - Rộng 236 mm - Dày 18.6 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - Đang cập nhật | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Đang cập nhật | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 95% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 17.9 mm - 1.4 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-15-fd2127tu-ultra-5-225u-d72ccpa</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-s14-s3407aa-ultra-5-325-sf945w</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:00:29</t>
+          <t>2026-07-31 14:06:46</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 240R G10 - C3SG9AT (Core 5 120U, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="n">
-        <v>20490000</v>
+          <t>Laptop Asus Vivobook S14 S3407VA - LY256W (Core 7 240H, 16GB, 512GB, WUXGA OLED, Win11)</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>26990000</v>
       </c>
       <c r="C128" s="2" t="n">
-        <v>23590000</v>
+        <v>29990000</v>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack HDMI | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HP TrueVision Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 323.7 mm - Rộng 215 mm - Dày 13.2 mm - 1.404 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 17.9 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-240r-g10-core-5-120u-c3sg9at</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-s14-s3407va-core-7-240h-ly256w</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:00:47</t>
+          <t>2026-07-31 14:07:00</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 240R G10 - CC9B9PT (Core 7 150U, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="n">
-        <v>23990000</v>
+          <t>Laptop Asus Zenbook 14 UM3406GA - QD075W (R7 AI 445, 16GB, 512GB, WUXGA OLED, Win11)</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>34490000</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>29590000</v>
+        <v>39990000</v>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>-19%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x USB Type-C (Power Delivery, DisplayPort 1.4, HP Sleep and Charge) 2 x USB Type-A HDMI 1.4b 1 x Headphone/ Microphone combo audio jack | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 323.7 mm - Rộng 215 mm - Dày 13.2 mm - 1.406 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.0 GHz | NPU:: AMD XDNA | Card màn hình:: Card tích hợp | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 70% Less harmful blue light 400 nits 600 nits (Khi bật HDR) | Cổng giao tiếp:: 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 75 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.01 mm - Rộng 31.24 mm - Dày 1.49 mm - 1.2 kg | Chất liệu:: Nhôm nguyên khối</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-240r-g10-core-7-150u-cc9b9pt</t>
+          <t>https://www.thegioididong.com/laptop/asus-zenbook-14-um3406ga-r7-ai-445-qd075w</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:01:02</t>
+          <t>2026-07-31 14:07:13</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 240R G9 - C40LGAT (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="n">
-        <v>24490000</v>
+          <t>Laptop Asus Zenbook A14 UX3407NA - QD132WS (X2E 88 100, 16GB, 512GB, WUXGA OLED, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>44490000</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>26590000</v>
+        <v>48990000</v>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HP TrueVision Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324 mm - Rộng 225.9 mm - Dày 9.4 mm - 1.406 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Snapdragon X2 Elite - X2E88100 | Số nhân:: 18 | Số luồng:: 18 | Tốc độ CPU:: Lên đến 4.0 GHz khi tải nặng | NPU:: Qualcomm Hexagon | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | Card màn hình:: Card tích hợp - Qualcomm Adreno GPU | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 9523 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: VESA DisplayHDR Thời gian phản hồi 0.2 ms Màn hình bảo vệ mắt - EYE CARE Low Blue Light Chống chói Anti Glare 400 nits 600 nits (Khi bật HDR) 1.07 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Công nghệ Smart AMP | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.7 mm - Rộng 213.9 mm - Dày 15.9 mm - 0.986 kg | Chất liệu:: Vỏ gốm nhôm Ceraluminum</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-240r-g9-core-5-120u-c40lgat</t>
+          <t>https://www.thegioididong.com/laptop/asus-zenbook-a14-ux3407na-x2e-88-100-qd132ws</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:01:18</t>
+          <t>2026-07-31 14:07:27</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 240R G9 - C40M2AT (Core 5 120U, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="n">
-        <v>18990000</v>
+          <t>Laptop Asus Zenbook A14 UX3407NA - QD254W (X2E 88 100, 32GB, 1TB, WUXGA OLED, Win11)</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>58190000</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>23590000</v>
+        <v>63990000</v>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>-19%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HP TrueVision Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324 mm - Rộng 225.9 mm - Dày 9.4 mm - 1.406 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Snapdragon X2 Elite - X2E88100 | Số nhân:: 18 | Số luồng:: 18 | Tốc độ CPU:: Lên đến 4.0 GHz khi tải nặng | NPU:: Qualcomm Hexagon | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | Card màn hình:: Card tích hợp - Qualcomm Adreno GPU | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 9523 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: VESA DisplayHDR Thời gian phản hồi 0.2 ms Màn hình bảo vệ mắt - EYE CARE Low Blue Light Chống chói Anti Glare 400 nits 600 nits (Khi bật HDR) 1.07 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Công nghệ Smart AMP | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.7 mm - Rộng 213.9 mm - Dày 15.9 mm - 0.986 kg | Chất liệu:: Vỏ gốm nhôm Ceraluminum</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-240r-g9-core-5-120u-c40m2at</t>
+          <t>https://www.thegioididong.com/laptop/asus-zenbook-a14-ux3407na-x2e-88-100-qd254w</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:01:32</t>
+          <t>2026-07-31 14:07:41</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 240R G9 - AX3C6AT (i3 1315U, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="n">
-        <v>14490000</v>
+          <t>Laptop Asus Zenbook S 16 UM5606GA - SS441W (R9 AI 465, 16GB, 512GB, 3K OLED 120Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>44990000</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>16390000</v>
+        <v>49490000</v>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i3 Raptor Lake - 1315U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.50 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324 mm - Rộng 225.9 mm - Dày 9.4 mm - 1.397 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 9 - 465 | Số nhân:: 10 | Số luồng:: 20 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Màn hình bảo vệ mắt - EYE CARE Low Blue Light DisplayHDR True Black 1000 500 nits Chống chói Anti Glare 1100 nits (peak) | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Công nghệ Smart AMP | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 83 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 353.6 mm - Rộng 243 mm - Dày 12.9 mm - 1.5 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-240r-g9-i3-1315u-ax3c6at</t>
+          <t>https://www.thegioididong.com/laptop/asus-zenbook-s-16-um5606ga-r9-ai-465-ss441w</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:01:47</t>
+          <t>2026-07-31 14:07:55</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP EliteBook 6 G1a 14 - C0CE1PT (R5 AI 340, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="n">
-        <v>30190000</v>
+          <t>Laptop Dell 14 DC14250 - DC14250-C3U085W11SLU-27 (Core 3 100U, 8GB, 512GB, Full HD+, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>18990000</v>
       </c>
       <c r="C133" s="2" t="n">
-        <v>31590000</v>
+        <v>19390000</v>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.528 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits ComfortView Plus | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r5-ai-340-c0ce1pt</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-3-100u-dc14250-c3u085w11slu-27</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:02:01</t>
+          <t>2026-07-31 14:08:09</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP EliteBook 6 G1a 14 - C0CF2PT (R5 AI 340, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="n">
-        <v>31190000</v>
+          <t>Laptop Dell 14 DC14250 - DC4C5375W1-2Y (Core 5 120U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>30990000</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>32590000</v>
+        <v>32090000</v>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.528 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226 mm - Dày 18 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r5-ai-340-c0cf2pt</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-5-120u-dc4c5375w1-2y</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:02:16</t>
+          <t>2026-07-31 14:08:22</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP EliteBook 6 G1a 14 - C0CE2PT (R7 AI 350, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="n">
-        <v>34290000</v>
+          <t>Laptop Dell 14 DC14250 - 71092478 (Core 7 150U, 16GB, 512GB, Full HD+ 120Hz, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>27990000</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>35690000</v>
+        <v>28390000</v>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.549 kg | Chất liệu:: Nắp lưng và chiếu nghỉ tay bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.20 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Display with ComfortView Wide viewing angle Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD RGB | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Cirrus Logic CS42L43 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-Po, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 320 mm - Rộng 215.97 mm - Dày 18.02 mm - 1.83 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r7-ai-350-c0ce2pt</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-71092478</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:02:31</t>
+          <t>2026-07-31 14:08:36</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP EliteBook 6 G1a 14 - C0CG2PT (R7 AI 350, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="n">
-        <v>33290000</v>
+          <t>Laptop Dell 14 DC14250 - 71100515 (Core 7 150U, 16GB, 512GB, Full HD+ 120Hz, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>34790000</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>34690000</v>
+        <v>35490000</v>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.531 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 320 mm - Rộng 215.97 mm - Dày 18.02 mm - 1.83 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r7-ai-350-c0cg2pt</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-71100515</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:02:45</t>
+          <t>2026-07-31 14:08:50</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP EliteBook 8 G1a 14 - C0CE5PT (R7 AI PRO 350, 32GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="n">
-        <v>37790000</v>
+          <t>Laptop Dell 14 DC14250 - DC14250-C7U161W11SLU-27 (Core 7 150U, 16GB, 1TB, Full HD+, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>29490000</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>39190000</v>
+        <v>29890000</v>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x USB 3.2. 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1 x Headphone/microphone combo 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 62 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 315.6 mm - Rộng 222 mm - Dày 15.5 mm - 1.564 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-8-g1a-14-ai-350-c0ce5pt</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-dc14250-c7u161w11slu-27</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:03:01</t>
+          <t>2026-07-31 14:09:03</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP EliteBook 8 G1a 14 - C0CE3PT (R5 AI PRO 340, 32GB, 512GB, WUXGA, Cảm ứng, Win11 Pro)</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="n">
-        <v>40790000</v>
+          <t>Laptop Dell 14 DC14250 - DC14250-C7U161W11SLU-2Y (Core 7 150U, 16GB, 1TB, Full HD+ ,OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>37290000</v>
       </c>
       <c r="C138" s="2" t="n">
-        <v>42190000</v>
+        <v>37990000</v>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 Pro - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x USB A 2 x Thunderbolt 4 (Hỗ trợ Power Delivery, DisplayPort 2.1, HP Sleep and Charge) 1 x Headphone/microphone combo HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 62 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 315.6 mm - Rộng 222 mm - Dày 15.5 mm - 1.39 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 7 - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: E-core: 0.9 GHz - 3.3 GHz, P-core: 1.2 GHz - 4.7 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MT/s | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 PCIe Gen 4 x 4 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (M.2 2230)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Display with ComfortView Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.615 mm - Rộng 31.4 mm - Dày 1.669 ~ 1.807 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-8-g1a-14-r5-ai-pro-340-c0ce3pt</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-dc14250-c7u161w11slu-2y</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:03:15</t>
+          <t>2026-07-31 14:09:18</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP EliteBook 8 G1a 14 - C0CE6PT (R7 AI PRO 350, 32GB, 512GB, WUXGA, Cảm ứng, Win11 Pro)</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="n">
-        <v>46190000</v>
+          <t>Laptop Dell 14 DC14255 - 71092477 (R7 350, 16GB, 1TB, Full HD+, OfficeHS24+365B, Win11)</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>32490000</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>1590000</v>
+        <v>33190000</v>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 Pro - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x USB 3.2. 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1 x Headphone/microphone combo 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 62 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 315.6 mm - Rộng 222 mm - Dày 15.5 mm - 1.558 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB onboard + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Display with ComfortView Wide viewing angle Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3204 Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-Po, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày `19.9 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-8-g1a-14-r7-ai-pro-350-c0ce6pt</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14255-r7-350-71092477</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:03:29</t>
+          <t>2026-07-31 14:09:32</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP Gaming HyperX Omen 15 ga0092TX - D72D8PA (i5 14450HX, 16GB, 512GB, RTX 5050 8GB, WUXGA 165Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="n">
-        <v>45590000</v>
+          <t>Laptop Dell 15 DC15250 - 71100520 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>21990000</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>46990000</v>
+        <v>22590000</v>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
@@ -6361,84 +6410,84 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 421 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.37 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort 1.4, Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Bluetooth 5.0 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.5 mm - Dày 18.9 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-gaming-hyperx-omen-15-ga0092tx-i5-14450hx-d72d8pa</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-71100520</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:03:43</t>
+          <t>2026-07-31 14:09:47</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP Gaming VICTUS 15 fa2451TX - D17WPPA (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="n">
-        <v>27490000</v>
+          <t>Laptop Dell 15 DC15250 - CPH993 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>21990000</v>
       </c>
       <c r="C141" s="2" t="n">
-        <v>31990000</v>
+        <v>22590000</v>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35W - 115W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x USB 3.2 1 x USB 3.2 (hỗ trợ HP Sleep and Charge) 1 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358 mm - Rộng 255 mm - Dày 23.5 mm - 2.29 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: Đang cập nhật | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 70% Less harmful blue light 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 16.96 mm đến 18.99 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-gaming-victus-15-fa2451tx-i5-13420h-d17wppa</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-cph993</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:03:58</t>
+          <t>2026-07-31 14:10:01</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP HyperX Omen 15 ga0091TX - D72D7PA (i5 14450HX, 16GB, 512GB, RTX 5060 8GB, WUXGA 165Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B142" s="3" t="n">
-        <v>48590000</v>
+          <t>Laptop Dell 15 DC15250 - DC5C3259W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>21990000</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>49990000</v>
+        <v>22590000</v>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
@@ -6447,70 +6496,27 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3840 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 614 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.363 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-hyperx-omen-15-ga0091tx-i5-14450h-d72d7pa</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3259w1-2y</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:04:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>Laptop HP OmniBook 7 Aero 13 bg1087AU - BZ7S1PA (R5 AI 340, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="n">
-        <v>27990000</v>
-      </c>
-      <c r="C143" s="2" t="n">
-        <v>29790000</v>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCie Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4TB) | Kích thước màn hình:: 13.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 400 nits | Cổng giao tiếp:: 2 x USB Type-A 2 x USB Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/microphone combo HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E MT7922 Bluetooth 5.3 | Webcam:: HP 5MP Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Poly Studio HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 43 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 297.3 mm - Rộng 211.2 mm - Dày 17.4 mm - 0.99 kg | Chất liệu:: Vỏ kim loại</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-7-aero-13-bg1087au-r5-ai-340-bz7s1pa</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-30 13:04:27</t>
+          <t>2026-07-31 14:10:16</t>
         </is>
       </c>
     </row>

--- a/laptop_tgdd_all.xlsx
+++ b/laptop_tgdd_all.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I142"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -492,1777 +492,1777 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AG15-52P-52WT - NX.JWKSV.001 (Ultra 5 115U, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Lenovo Gaming Legion 5 15AHP11 - 83Q7001HVN (R7 250, 16GB, 512GB, RTX 5050 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>21690000</v>
+        <v>55290000</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>24990000</v>
+        <v>55990000</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 115U | Số nhân:: 8 | Số luồng:: 10 | Tốc độ CPU:: 1.5 GHz (Lên đến 4.2 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB onboard + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 2 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357.5 mm - Rộng 229 mm - Dày 17.95 mm - 1.59 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: Boost Clock 2662MHz, TGP 115W, 440 AI TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: 2.5K | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: DisplayHDR True Black 1000 | Cổng giao tiếp:: 1x Ethernet 2 x USB Type-C (USB4 40Gbps) hỗ trợ USB PD 65 - 100W và DisplayPort 1.4 1 x Headphone/ Microphone combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) 2×2 Bluetooth 6.0 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 244.5 mm - Rộng 344 mm - Dày 19~20 - 1.87 kg | Chất liệu:: Mặt trên: nhôm + Mặt dưới: nhựa PC-ABS</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-go-15-ag15-52p-52wt-ultra-5-115u-nx-jwksv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15ahp11-r7-250-83q7001hvn</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:12:09</t>
+          <t>2026-08-01 14:51:30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP - NX.DMCSV.003 (R7 7730U, 8GB, 512GB, Full HD+, Win11)</t>
+          <t>Laptop Lenovo Gaming Legion 5 15IPH11 - 83RW0023VN (Ultra 7 356H, 16GB, 512GB, RTX 5060 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>20990000</v>
+        <v>59990000</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>22990000</v>
+        <v>64990000</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 680M Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14.5" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB Type - C 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 324 mm - Rộng 227.6 mm - Dày 17.9 mm - 1.3 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 365H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 15.3" | Độ phân giải:: WQXGA (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light 1000 nits (peak) 500 nits typical G-Sync DisplayHDR True Black 1000 High Gaming Performance Flicker Free | Cổng giao tiếp:: 3 x USB Jack tai nghe 3.5 mm 1 x USB Type-C (USB Power Delivery, DisplayPort 2.1) LAN (RJ45) HDMI 2.1 1 x Thunderbolt 4 (hỗ trợ DisplayPort 2.1, Power Delivery) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đèn chuyển màu RGB - 24 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Realtek Audio Audio by HARMAN Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Legion ColdFont Hyper | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344 mm - Rộng 244.5 mm - Dày 19.95 mm - 1.87 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-14-al14-44p-r0sp-r7-7730u-nx-dmcsv-003</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15iph11-ultra-7-356h-83rw0023vn</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:12:23</t>
+          <t>2026-08-01 14:51:44</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-45P-R7Z3 - NX.DPESV.002 (R3 5400U, 8GB, 512GB, Full HD+, Win11)</t>
+          <t>Laptop Lenovo Gaming LOQ 15AHP11 - 83TN0040VN (R7 250, 16GB, 512GB, RTX 5050 8GB, WUXGA 165Hz, Win11)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14990000</v>
+        <v>45590000</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>17990000</v>
+        <v>46990000</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 3 - 5400U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.60 GHz (Lên đến 4.0 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.8 mm - Rộng 219.7 mm - Dày 19.1 mm - 1.3 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 2TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Low Blue Light G-Sync AMD Freesync 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm LAN (RJ45) HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) 3 x USB A | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344.9 mm - Rộng 254.83 mm - Dày 23.25 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-14-al14-45p-r7z3-r3-5400u-nx-dpesv-002</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15ahp11-r7-250-83tn0040vn</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:12:36</t>
+          <t>2026-08-01 14:51:57</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W - NX.DNRSV.002 (R5 40, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Lenovo Gaming LOQ 15IPH11 - 83SL000LVN (Ultra 7 356H, 16GB, 512GB, RTX 5060 8GB, WUXGA 165Hz, Win11)</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>19590000</v>
+        <v>54590000</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>22990000</v>
+        <v>55990000</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 53 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360.66 mm - Rộng 234.8 mm - Dày 16.95 mm - 1.45 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 365H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 1TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Low Blue Light G-Sync AMD Freesync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 3 x USB Jack tai nghe 3.5 mm LAN (RJ45) HDMI 2.1 1 x Thunderbolt 4 (hỗ trợ DisplayPort 2.1, Power Delivery) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344.9 mm - Rộng 254.83 mm - Dày 23.25 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-21p-r91w-r5-40-nx-dnrsv-002</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15iph11-ultra-7-356h-83sl000lvn</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:12:49</t>
+          <t>2026-08-01 14:52:11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN - NX.DDASV.001 (Core 3 N350, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Lenovo IdeaPad 5 2in1 14IPH11 - 83UG0026VN (Ultra 5 322, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>16990000</v>
+        <v>30990000</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>18990000</v>
+        <v>32990000</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Twin Lake - N350 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 3.90 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB 3.2 HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.0 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357.8 mm - Rộng 235.6 mm - Dày 19.7 mm - 1.53 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.6 mm - Rộng 224.9 mm - Dày 17.4 mm - 1.54 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-36p-30tn-core-3-n350-nx-ddasv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-5-2in1-14iph11-ultra-5-322-83ug0026vn</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:13:03</t>
+          <t>2026-08-01 14:52:25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-44P-R4UH - NX.DJVSV.002 (R7 7730U, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Lenovo IdeaPad 5 2in1 14IPH11 - 83UG0027VN (Ultra 7 355, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>21990000</v>
+        <v>35990000</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>23990000</v>
+        <v>37990000</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB Type - C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 230.2 mm - Dày 18.6 mm - 1.49 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.6 mm - Rộng 224.9 mm - Dày 17.4 mm - 1.54 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-44p-r4uh-r7-7730u-nx-djvsv-002</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-5-2in1-14iph11-ultra-7-355-83ug0027vn</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:13:17</t>
+          <t>2026-08-01 14:52:40</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-46P-R73C - NX.JXMSV.001 (R3 5400U, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IPH11 - 83UQ003NVN (Ultra 5 322, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>14490000</v>
+        <v>24990000</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>17990000</v>
+        <v>27990000</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-19%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 3 - 5400U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.60 GHz (Lên đến 4.0 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 3.2. 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) 1 x USB 3.2 Gen 2 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 53 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360.66 mm - Rộng 234.8 mm - Dày 16.95 mm - 1.45 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.43 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-46p-r73c-r3-5400u-nx-jxmsv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iph11-ultra-5-322-83uq003nvn</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:13:32</t>
+          <t>2026-08-01 14:52:55</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-48P-R86Q - NX.DS1SV.002 (R7 5825U, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IPH11 - 83UQ003PVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>18990000</v>
+        <v>29990000</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>21990000</v>
+        <v>32990000</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 5825U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) 1 x USB 3.2 Gen 2 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360.66 mm - Rộng 234.8 mm - Dày 16.95 mm - 1.45 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.43 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-48p-r86q-r7-5825u-nx-ds1sv-002</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iph11-ultra-7-355-83uq003pvn</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:13:46</t>
+          <t>2026-08-01 14:53:08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-49P-R6XX - NX.DRZSV.002 (R5 7430U, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002NVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>17990000</v>
+        <v>23990000</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>20990000</v>
+        <v>26490000</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 7430U | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) 1 x USB 3.2 Gen 2 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360.66 mm - Rộng 234.8 mm - Dày 16.95 mm - 1.45 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-49p-r6xx-r5-7430u-nx-drzsv-002</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002nvn</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:13:59</t>
+          <t>2026-08-01 14:53:22</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC - NX.DG3SV.002.16G (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002PVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>21990000</v>
+        <v>19990000</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>24990000</v>
+        <v>22990000</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 357.6 mm - Rộng 228.5 mm - Dày 18.7 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-53p-56ec-core-5-120u-nx-dg3sv-002-16g</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002pvn</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:14:13</t>
+          <t>2026-08-01 14:53:36</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH - NX.DG3SV.001 (Core 5 120U, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IPH11 - 83UR00A4VN (Ultra 5 322, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>20990000</v>
+        <v>24990000</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>24990000</v>
+        <v>27990000</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD WVA | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3x Type-A USB 3.2 Gen 1 1 x USB Type-C 3.2 gen 1 (hỗ trợ truyền dữ liệu và Power Delivery) HDMI 1.4 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) Wi-Fi Dual Band | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357.6 mm - Rộng 228.5 mm - Dày 18.7 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 2.50 GHz (Lên đến 4.40 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.63 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-53p-56qh-core-5-120u-nx-dg3sv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iph11-ultra-5-322-83ur00a4vn</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:14:27</t>
+          <t>2026-08-01 14:53:49</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AL16-71P-582Q - NX.DRSSV.001 (Ultra 5 125H, 16GB, 512GB, Full HD+ 120Hz, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IPH11 - 83UR00A5VN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>23990000</v>
+        <v>29990000</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>26990000</v>
+        <v>32990000</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 125H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357 mm - Rộng 245.5 mm - Dày 18.9 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.63 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-16-al16-71p-582q-ultra-5-125h-nx-drssv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iph11-ultra-7-355-83ur00a5vn</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:14:41</t>
+          <t>2026-08-01 14:54:02</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Aspire 7 A715-59G-59RD - NH.DXUSV.001 (Core 5 210H, 16GB, 512GB, RTX 3050 4GB, Fulll HD 144Hz, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00A8VN (Core 3 304, 8GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>25990000</v>
+        <v>18990000</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>31990000</v>
+        <v>20890000</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-19%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 4 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35W - 80W | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 4 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle 350 nits Acer ComfyView | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C (hỗ trợ DisplayPort 1.4) LAN (RJ45) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn LED - 15 chế độ màu | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 359.5 mm - Rộng 238 mm - Dày 22.7 mm - 1.99 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core™ 3 - 304 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz (P-core), Turbo tối đa 4.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 2242 PCIe 4.0x4 NVMe | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 × USB-C (USB 5 Gbps), hỗ trợ USB PD 45–65W và DisplayPort 1.2 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Optimized with Dolby Audio 2W x 2 High Definition (HD) Audio Stereo speakers | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 240 mm - Rộng 343 mm - Dày 17 - 18 - 1.59 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-aspire-7-a715-59g-59rd-core-5-210h-nh-dxusv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-3-304-83rr00a8vn</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:14:55</t>
+          <t>2026-08-01 14:54:17</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel AN16S-61-R9CN - NH.QXGSV.001 (Ryzen AI 7 350, 16GB, 512GB, RTX 5070 8GB, 2K+ 180Hz, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00AAVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>55990000</v>
+        <v>23990000</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>59990000</v>
+        <v>26490000</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.0 GHz (Lên đến 5.2 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe mở rộng (nâng cấp tối đa 2 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits 3ms | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: NVIDIA Optimus | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 19.9 mm - 2.18 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-an16s-61-r9cn-ryzen-ai-7-350-nh-qxgsv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00aavn</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:15:09</t>
+          <t>2026-08-01 14:54:31</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-73Z8 - NH.QUASV.001 (Core 7 240H, 16GB, 512GB, RTX 4050 6GB, Full HD  180Hz, Win11)</t>
+          <t>Laptop Lenovo Ideapad Slim 3 15IWC11 - 83RR00CVVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>37290000</v>
+        <v>19990000</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>37990000</v>
+        <v>22990000</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số luồng:: 16 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: IPS | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1x Ethernet 3 x USB 3.2 Gen 1 Type-A 1 x USB Type-C (65W) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: 720p at 30 fps HD camera Camera with Dual Microphone | Đèn bàn phím:: Đơn sắc - Màu cam | Công nghệ âm thanh:: Windows Spatial Sound High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-73z8-core-7-240h-nh-quasv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00cvvn</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:15:24</t>
+          <t>2026-08-01 14:54:46</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV16-72-71T9 - NH.QUNSV.001 (Core 7 240H, 16GB, 512GB, RTX 5060 8GB, WUXGA 180Hz, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US002TVN (Ultra 5 322, 24GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>43990000</v>
+        <v>29990000</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>45990000</v>
+        <v>31990000</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 95 W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD WVA NVIDIA Advanced Optimus | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 2 x USB 3.2 gen 2 Type-A LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (2 x 2) Wi-Fi Dual Band | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu cam | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio High SNR DAC with 2.1 Vrms out capability Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 360 mm - Rộng 274.5 mm - Dày 24.5 mm - 2.4 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 24 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16-72-71t9-core-7-240h-nh-qunsv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-5-322-83us002tvn</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:15:37</t>
+          <t>2026-08-01 14:54:59</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-61-R0B8 - NH.QXQSV.001 (Ryzen AI 5 340, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US002WVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>43990000</v>
+        <v>29990000</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>47990000</v>
+        <v>32990000</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.40 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-61-r0b8-ryzen-ai-5-340-nh-qxqsv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-7-355-83us002wvn</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:15:51</t>
+          <t>2026-08-01 14:55:13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-71-58WQ - NH.QXBSV.001 (Core 5 210H, 16GB, 512GB, RTX 5050 8GB, 2K+ 180Hz, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US003YVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>42990000</v>
+        <v>31590000</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46990000</v>
+        <v>32990000</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-71-58wq-core-5-210h-nh-qxbsv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-7-355-83us003yvn</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:16:04</t>
+          <t>2026-08-01 14:55:26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Predator Helios Neo 16 PHN16-I31-50H7 - NH.U4SSV.001 (i5 14450HX, 32GB, 512GB, RTX 5050 8GB, Full HD+ 180Hz, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 - 83S1006RVN (R7 AI 445, 16GB, 512GB, WUXGA OLED, Win11)</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>49990000</v>
+        <v>30990000</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>61990000</v>
+        <v>32990000</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-19%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe mở rộng (nâng cấp tối đa 2 TB) 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 2 x Thunderbolt 4 with USB Type - C (hỗ trợ DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Hi-Res Audio Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Quạt kim loại 3D AeroBlade 2 quạt | Tính năng khác:: NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 26.75 mm - 2.5 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.0 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 2 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 2-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16-phn16-i31-50h7-i5-14450hx-nh-u4ssv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-14agp11-r7-ai-445-83s1006rvn</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:16:19</t>
+          <t>2026-08-01 14:55:41</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Predator Helios Neo 16 PHN16-I31-72XE - NH.U4RSV.001 (i7 14650HX, 32GB, 512GB, RTX5060 8GB, 2K+ 180Hz, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14IPH11 - 83S5004FVN (Ultra 7 355, 16GB, 512GB, WUXGA OLED, Win11)</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>59990000</v>
+        <v>34990000</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>71990000</v>
+        <v>37990000</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 14650HX | Số nhân:: 16 | Số luồng:: 24 | Tốc độ CPU:: 2.20 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe mở rộng (nâng cấp tối đa 2 TB) 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 2 x Thunderbolt 4 with USB Type - C (hỗ trợ DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Hi-Res Audio Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Quạt kim loại 3D AeroBlade 2 quạt | Tính năng khác:: NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 26.75 mm - 2.5 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16-phn16-i31-72xe-i7-14650hx-nh-u4rsv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-14iph11-ultra-7-355-83s5004fvn</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:16:33</t>
+          <t>2026-08-01 14:55:56</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Predator Helios Neo 16 PHN16-I31-74MN - NH.U4SSV.002 (i7 14650HX, 32GB, 512GB, RTX 5050 8GB, Full HD+ 180Hz, Win11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP - NX.DMCSV.003 (R7 7730U, 8GB, 512GB, Full HD+, Win11)</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>54990000</v>
+        <v>20990000</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>66990000</v>
+        <v>22990000</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 14650HX | Số nhân:: 16 | Số luồng:: 24 | Tốc độ CPU:: 2.20 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView NVIDIA Advanced Optimus | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1x Ethernet 2 x Thunderbolt 4 with USB Type - C (hỗ trợ DisplayPort 2.1) 2 x USB 3.2 gen 2 Type-A HDMI 2.1 | Kết nối không dây:: Bluetooth 5.4 + LE Wi-Fi 6E (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Hi-Res certification Windows Spatial Sound High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Quạt kim loại 3D AeroBlade 2 quạt | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 26.75 mm - 2.5 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 680M Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14.5" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB Type - C 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 324 mm - Rộng 227.6 mm - Dày 17.9 mm - 1.3 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16-phn16-i31-74mn-i7-14650hx-nh-u4ssv-002</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-14-al14-44p-r0sp-r7-7730u-nx-dmcsv-003</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:16:47</t>
+          <t>2026-08-01 13:23:25</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Predator Helios Neo 16S PHN16S-I51-97T9 - NH.U3SSV.006 (Ultra 9 386H, 16GB, 512GB, RTX 5070 8GB, 2K+ 165Hz, Win11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-45P-R7Z3 - NX.DPESV.002 (R3 5400U, 8GB, 512GB, Full HD+, Win11)</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>73990000</v>
+        <v>15990000</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>77990000</v>
+        <v>17990000</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 9 Panther Lake - 386H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 50 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: LED-backlit TFT LCD 500 nits Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 18.9 mm - 2.2 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 3 - 5400U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.60 GHz (Lên đến 4.0 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.8 mm - Rộng 219.7 mm - Dày 19.1 mm - 1.3 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16s-phn16s-i51-97t9-ultra-9-386h</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-14-al14-45p-r7z3-r3-5400u-nx-dpesv-002</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:17:01</t>
+          <t>2026-08-01 13:23:40</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Nitro ProPanel ANV15-52-50RB - NH.QUASV.002 (Core 5 210H, 16GB, 512GB, RTX 4050 6GB, Full HD 180Hz, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN - NX.DDASV.001 (Core 3 N350, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>35990000</v>
+        <v>16990000</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>37990000</v>
+        <v>18990000</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 60W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 300 nits Acer ComfyView 3ms | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2 microphones Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Tính năng khác:: Copilot Key | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Twin Lake - N350 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 3.90 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB 3.2 HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.0 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357.8 mm - Rộng 235.6 mm - Dày 19.7 mm - 1.53 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv15-52-50rb-core-5-210h-nh-quasv-002</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-36p-30tn-core-3-n350-nx-ddasv-001</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:17:16</t>
+          <t>2026-08-01 13:23:54</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP - NX.JZHSV.003 (Ultra 7 358H, 32GB, 1TB, 2.8K 120Hz, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-44P-R4UH - NX.DJVSV.002 (R7 7730U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>47590000</v>
+        <v>21990000</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>50990000</v>
+        <v>23990000</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra X7 - 358H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 9600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: 2.8K (2880 x 1800) - OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 ACER CineCrystal WVA | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A HDMI 2.1 2 x USB-C (hỗ trợ Thunderbolt 4/USB 4, USB Power Delivery và DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res certification High SNR DAC with 2.1 Vrms out capability Công nghệ Smart AMP Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-ion, 71 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.5 mm - Rộng 218.9 mm - Dày 15.6 mm - 1.12 kg | Chất liệu:: Vỏ hợp kim Nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB Type - C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 230.2 mm - Dày 18.6 mm - 1.49 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-swift-go-14-ai-sfg14-i71-70rp-ultra-7-358h-nx-jzhsv-003</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-44p-r4uh-r7-7730u-nx-djvsv-002</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:17:29</t>
+          <t>2026-08-01 13:24:07</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming ROG Strix G16 G614PM - TS147W (R9 8940HX, 16GB, 512GB, RTX 5060 8GB, WQXGA 300Hz, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-48P-R86Q - NX.DS1SV.002 (R7 5825U, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>49990000</v>
+        <v>18990000</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>52990000</v>
+        <v>21990000</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115W - 140W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.288 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 5825U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) 1 x USB 3.2 Gen 2 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360.66 mm - Rộng 234.8 mm - Dày 16.95 mm - 1.45 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pm-r9-8940hx-ts147w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-48p-r86q-r7-5825u-nx-ds1sv-002</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:17:43</t>
+          <t>2026-08-01 13:24:20</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming ROG Strix G16 G614PR - TS103W (R9 8940HX, 16GB, 512GB, RTX 5070Ti 12GB, WQXGA 300Hz, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-49P-R6XX - NX.DRZSV.002 (R5 7430U, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>70590000</v>
+        <v>17690000</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>71990000</v>
+        <v>20990000</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070Ti, 12 GB | Số nhân GPU:: 5888 CUDA Cores | Công suất đồ hoạ - TGP:: 140 W | Hiệu năng xử lý AI (TOPS):: Lên đến 992 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.34 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 7430U | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) 1 x USB 3.2 Gen 2 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360.66 mm - Rộng 234.8 mm - Dày 16.95 mm - 1.45 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pr-r9-8940hx-ts103w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-49p-r6xx-r5-7430u-nx-drzsv-002</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:17:56</t>
+          <t>2026-08-01 13:24:34</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming ROG Zephyrus GA403GM - SY004W (R9 AI 465, 32GB, 1TB, RTX 5060 8GB, 3K OLED 120Hz, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC - NX.DG3SV.002.16G (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>64590000</v>
+        <v>21990000</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>65990000</v>
+        <v>24990000</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 9 - 465 | Số nhân:: 10 | Số luồng:: 20 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 623 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Anti-Reflective G-Sync ROG Nebula HDR Display 1000 nits Dolby Vision | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, G-SYNC) 1 x USB4 Type-C (hỗ trợ DisplayPort, Power Delivery) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 73 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311 mm - Rộng 220 mm - Dày 16.3 mm - 1.5 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 357.6 mm - Rộng 228.5 mm - Dày 18.7 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-zephyrus-ga403gm-r9-ai-465-sy004w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-53p-56ec-core-5-120u-nx-dg3sv-002-16g</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:18:10</t>
+          <t>2026-08-01 13:24:48</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus TUF Gaming F16 FX608JHI - TU210W (i5 14450HX, 16GB, 512GB,RTX 5050 8GB, WUXGA 144Hz, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH - NX.DG3SV.001 (Core 5 120U, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>40990000</v>
+        <v>20990000</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>47990000</v>
+        <v>24990000</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 2TB) 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 72% NTSC | Công nghệ màn hình:: G-Sync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 3 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: FHD 1080p | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Dolby Atmos | Tản nhiệt:: 2 quạt | Tính năng khác:: MUX Switch NVIDIA Optimus Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 269 mm - Dày 27.3 mm - 2.2 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD WVA | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3x Type-A USB 3.2 Gen 1 1 x USB Type-C 3.2 gen 1 (hỗ trợ truyền dữ liệu và Power Delivery) HDMI 1.4 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) Wi-Fi Dual Band | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357.6 mm - Rộng 228.5 mm - Dày 18.7 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-tuf-gaming-f16-fx608jhi-i5-14450hx-tu210w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-53p-56qh-core-5-120u-nx-dg3sv-001</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:18:25</t>
+          <t>2026-08-01 13:25:02</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus TUF Gaming FA401EA - RG034W (RYZEN AI MAX+ 392, 64GB, 1TB, WQXGA 165Hz, Win11)</t>
+          <t>Laptop Acer Aspire Lite 16 AL16-71P-582Q - NX.DRSSV.001 (Ultra 5 125H, 16GB, 512GB, Full HD+ 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>62990000</v>
+        <v>24990000</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>64990000</v>
+        <v>26990000</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI Max+ - 392 | Số nhân:: 12 | Số luồng:: 24 | Tốc độ CPU:: 3.2 GHz (Lên đến 5.0 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 8060S Graphics | RAM:: 64 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8000 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 2 x USB 3.2 gen 2 Type-A 1 x USB Type-C USB 4 (hỗ trợ DisplayPort và Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hi-Res certification AI noise-canceling technology Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 73 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311 mm - Rộng 227 mm - Dày 19.9 mm - 1.48 kg | Chất liệu:: Nắp lưng và chiếu nghỉ tay bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 125H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357 mm - Rộng 245.5 mm - Dày 18.9 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-tuf-gaming-fa401ea-ryzen-ai-max-392-rg034w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-16-al16-71p-582q-ultra-5-125h-nx-drssv-001</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:18:38</t>
+          <t>2026-08-01 13:25:17</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US002WVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Acer Gaming Aspire 7 A715-59G-59RD - NH.DXUSV.001 (Core 5 210H, 16GB, 512GB, RTX 3050 4GB, Fulll HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>30090000</v>
+        <v>25990000</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>32990000</v>
+        <v>31990000</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-19%</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 4 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35W - 80W | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 4 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle 350 nits Acer ComfyView | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C (hỗ trợ DisplayPort 1.4) LAN (RJ45) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn LED - 15 chế độ màu | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 359.5 mm - Rộng 238 mm - Dày 22.7 mm - 1.99 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-7-355-83us002wvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-aspire-7-a715-59g-59rd-core-5-210h-nh-dxusv-001</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:24:33</t>
+          <t>2026-08-01 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US003YVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel AN16S-61-R9CN - NH.QXGSV.001 (Ryzen AI 7 350, 16GB, 512GB, RTX 5070 8GB, 2K+ 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>29490000</v>
+        <v>53990000</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>32990000</v>
+        <v>59990000</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.0 GHz (Lên đến 5.2 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe mở rộng (nâng cấp tối đa 2 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits 3ms | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: NVIDIA Optimus | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 19.9 mm - 2.18 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-7-355-83us003yvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-an16s-61-r9cn-ryzen-ai-7-350-nh-qxgsv-001</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:24:47</t>
+          <t>2026-08-01 13:25:43</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 - 83S1006RVN (R7 AI 445, 16GB, 512GB, WUXGA OLED, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-73Z8 - NH.QUASV.001 (Core 7 240H, 16GB, 512GB, RTX 4050 6GB, Full HD  180Hz, Win11)</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>30590000</v>
+        <v>35990000</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>32990000</v>
+        <v>39990000</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.0 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 2 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 2-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số luồng:: 16 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: IPS | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1x Ethernet 3 x USB 3.2 Gen 1 Type-A 1 x USB Type-C (65W) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: 720p at 30 fps HD camera Camera with Dual Microphone | Đèn bàn phím:: Đơn sắc - Màu cam | Công nghệ âm thanh:: Windows Spatial Sound High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-14agp11-r7-ai-445-83s1006rvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-73z8-core-7-240h-nh-quasv-001</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:25:02</t>
+          <t>2026-08-01 13:25:58</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14IPH11 - 83S5004FVN (Ultra 7 355, 16GB, 512GB, WUXGA OLED, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-61-R0B8 - NH.QXQSV.001 (Ryzen AI 5 340, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>34490000</v>
+        <v>40990000</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>37990000</v>
+        <v>47990000</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.40 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-14iph11-ultra-7-355-83s5004fvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-61-r0b8-ryzen-ai-5-340-nh-qxqsv-001</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:25:16</t>
+          <t>2026-08-01 13:26:12</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 OLED 14IPH11 - 83S5000DVN (Ultra 5 322, 16GB, 512GB, WUXGA OLED, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-71-58WQ - NH.QXBSV.001 (Core 5 210H, 16GB, 512GB, RTX 5050 8GB, 2K+ 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>29490000</v>
+        <v>40990000</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>32990000</v>
+        <v>46990000</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD NVMe M.2 PCIe Gen 4.0 mở rộng (2280) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 2 x USB Type-C 3.2 (hỗ trợ truyền dữ liệu, Power Delivery 3.0, and DisplayPort 1.2) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Nắp lưng và mặt đáy bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-oled-14iph11-ultra-5-322-83s5000dvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-71-58wq-core-5-210h-nh-qxbsv-001</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:25:30</t>
+          <t>2026-08-01 13:26:25</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkBook 14 G9 - 21V0005PVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Acer Gaming Predator Helios Neo 16S PHN16S-I51-97T9 - NH.U3SSV.006 (Ultra 9 386H, 16GB, 512GB, RTX 5070 8GB, 2K+ 165Hz, Win11)</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>28290000</v>
+        <v>75990000</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>31190000</v>
+        <v>77990000</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 9 Panther Lake - 386H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 50 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: LED-backlit TFT LCD 500 nits Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 18.9 mm - 2.2 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-g9-r7-250-21v0005pvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16s-phn16s-i51-97t9-ultra-9-386h</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:25:45</t>
+          <t>2026-08-01 13:26:39</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkBook 14 Gen 9 IRL - 21UY008TVN (i5 13420H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Acer Nitro ProPanel ANV15-52-50RB - NH.QUASV.002 (Core 5 210H, 16GB, 512GB, RTX 4050 6GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>27290000</v>
+        <v>33490000</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>28890000</v>
+        <v>37990000</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 60W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 300 nits Acer ComfyView 3ms | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2 microphones Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Tính năng khác:: Copilot Key | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-gen-9-irl-i5-13420h-21uy008tvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv15-52-50rb-core-5-210h-nh-quasv-002</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:25:58</t>
+          <t>2026-08-01 13:26:52</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkBook 16 G9 - 21UT005MVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP - NX.JZHSV.003 (Ultra 7 358H, 32GB, 1TB, 2.8K 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>29690000</v>
+        <v>49590000</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>31590000</v>
+        <v>50990000</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356 mm - Rộng 253.5 mm - Dày 17.5 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra X7 - 358H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 9600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: 2.8K (2880 x 1800) - OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 ACER CineCrystal WVA | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A HDMI 2.1 2 x USB-C (hỗ trợ Thunderbolt 4/USB 4, USB Power Delivery và DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res certification High SNR DAC with 2.1 Vrms out capability Công nghệ Smart AMP Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-ion, 71 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.5 mm - Rộng 218.9 mm - Dày 15.6 mm - 1.12 kg | Chất liệu:: Vỏ hợp kim Nhôm</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-16-g9-r7-250-21ut005mvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-swift-go-14-ai-sfg14-i71-70rp-ultra-7-358h-nx-jzhsv-003</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:26:11</t>
+          <t>2026-08-01 13:27:07</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad E14 Gen 7 - 21SX00BNVN (Ultra 5 135H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Gaming ROG Strix G16 G614PM - TS147W (R9 8940HX, 16GB, 512GB, RTX 5060 8GB, WQXGA 300Hz, Win11)</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>29690000</v>
+        <v>50590000</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>31590000</v>
+        <v>52990000</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 135H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.60 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x USB-A (USB 10Gbps/USB 3.2 Gen 2), Always On 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Audio by HARMAN Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 19.7 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115W - 140W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.288 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-5-135h-21sx00bnvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pm-r9-8940hx-ts147w</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:26:24</t>
+          <t>2026-08-01 13:27:20</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad E14 Gen 7 - 21SX005NVN (Ultra 5 225U, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Gaming ROG Strix G16 G614PR - TS103W (R9 8940HX, 16GB, 512GB, RTX 5070Ti 12GB, WQXGA 300Hz, Win11)</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>31490000</v>
+        <v>70590000</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>33890000</v>
+        <v>71990000</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4 với USB Power Delivery và DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Audio by HARMAN Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 19.7 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070Ti, 12 GB | Số nhân GPU:: 5888 CUDA Cores | Công suất đồ hoạ - TGP:: 140 W | Hiệu năng xử lý AI (TOPS):: Lên đến 992 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.34 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-5-225u-21sx005nvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pr-r9-8940hx-ts103w</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:26:38</t>
+          <t>2026-08-01 13:27:36</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad X9 14 Gen 1 - 21QA006JVN (Ultra 7 258V, 32GB, 512GB, WUXGA OLED, Win11Pro)</t>
+          <t>Laptop Asus Gaming V16 V3607VJ Core 5 - TK189W (Core 5 210H, 16GB, 512GB, RTX 3050 6GB, WUXGA 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>53290000</v>
+        <v>28990000</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>55190000</v>
+        <v>36990000</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.80 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Chống chói Anti Glare Dolby Vision 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm HDMI 2.1 2 x USB-C (hỗ trợ Thunderbolt 4/USB 4, USB Power Delivery và DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.8 mm - Rộng 212.3 mm - Dày 17.18 mm - 1.21 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% Adobe | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x 3.5mm combo audio jack HDMI 2.1 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: 1080p with Privacy Shutter | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 63 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 251 mm - Dày 22 mm - 1.95 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-x9-14-gen-1-ultra-7-258v-21qa006jvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-v16-v3607vj-core-5-core-5-210h-tk189w</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:26:53</t>
+          <t>2026-08-01 13:27:50</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo V14 G5 - 83HD0035VN (Core7 240H, 16G, 512GB, Full HD, Win11)</t>
+          <t>Laptop Asus ProArt P1 H7606WP - SR335W (R9 AI HX 370, 64GB, 2TB, RTX 5070 8GB, 3K 120Hz, Cảm ứng, Win11)</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>26990000</v>
+        <v>122890000</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>28590000</v>
+        <v>124990000</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) LAN (RJ45) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Ion, 47 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324.2 mm - Rộng 215.2 mm - Dày 17.9 mm - 1.37 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 9 - Hãng không công bố | Số nhân:: 12 | Số luồng:: 24 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 64 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 2 TB SSD M.2 NVMe PCIe Gen 4 | Kích thước màn hình:: 16" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 500 nits (Khi bật HDR) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354.9 mm - Rộng 246.9 mm - Dày 17.3 mm - 1.85 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-v14-g5-core7-240h-83hd0035vn</t>
+          <t>https://www.thegioididong.com/laptop/asus-proart-p1-h7606wp-r9-ai-hx-370-sr335w</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:27:07</t>
+          <t>2026-08-01 14:15:41</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002LVN (Ultra 5 322, 16GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Asus TUF Gaming F16 FX608JHI - TU210W (i5 14450HX, 16GB, 512GB,RTX 5050 8GB, WUXGA 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>37490000</v>
+        <v>45090000</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>39990000</v>
+        <v>47990000</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
@@ -2271,1694 +2271,1662 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.45 mm - 1.38 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 2TB) 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 72% NTSC | Công nghệ màn hình:: G-Sync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 3 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: FHD 1080p | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Dolby Atmos | Tản nhiệt:: 2 quạt | Tính năng khác:: MUX Switch NVIDIA Optimus Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 269 mm - Dày 27.3 mm - 2.2 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-5-322-83tc002lvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-tuf-gaming-f16-fx608jhi-i5-14450hx-tu210w</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:27:21</t>
+          <t>2026-08-01 14:15:55</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002MVN (Ultra 7 355, 32GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Asus Vivobook 14 X1404MA - EB028W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>54490000</v>
+        <v>24990000</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>57990000</v>
+        <v>31990000</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.95 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Core i5 - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 SO-DIMM | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Hãng không công bố | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 21.39 mm - Rộng 32.49 mm - Dày 1.79 mm - 1.4 kg | Chất liệu:: Khung nhôm - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-7-355-83tc002mvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1404ma-core-5-320-eb028w</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:27:34</t>
+          <t>2026-08-01 14:16:09</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga 7 2in1 OLED 14IPH11 - 83TC002JVN (Ultra 7 355, 32GB, 1TB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Asus Vivobook 14 X1404MA - EB219W (Core 5 320, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>53490000</v>
+        <v>20990000</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>57990000</v>
+        <v>26990000</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Tiêu chuẩn Nền Intel Evo | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.45 mm - 1.38 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 8 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 324.9 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.409 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-oled-14iph11-ultra-7-355-83tc002jvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1404ma-core-5-320-eb219w</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:27:47</t>
+          <t>2026-08-01 14:16:21</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 OLED 14AGP11 - 83QS001DVN (R7 AI 445, 16GB, 512GB, WUXGA OLED, OfficeH24+365, Win11)</t>
+          <t>Laptop Asus Vivobook 14 X1407CA - LY203W (Ultra 5 225H, 16GB, 512GB, WUXGA OLED, Win11)</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>37490000</v>
+        <v>23990000</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>39990000</v>
+        <v>33490000</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-28%</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 8000 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Glossy Display Chuẩn DisplayHDR True Black 500 Eyesafe Dolby Vision 400 nits X-Rite Flicker Free | Cổng giao tiếp:: 1 x USB Type-C (hỗ trợ DisplayPort 1.4) 2 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 221 mm - Dày 13.9 mm - 1.15 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 19.9 mm - 1.46 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-oled-14agp11-r7-ai-445-83qs001dvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1407ca-ultra-5-225h-ly203w</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:28:01</t>
+          <t>2026-08-01 14:16:34</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 OLED 14IPH11 - 83QM002FVN (Ultra 7 355, 32GB, 1TB, WUXGA OLED, OfficeH24+365, Win11)</t>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ385W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>52490000</v>
+        <v>25090000</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>55990000</v>
+        <v>31990000</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe 600nits (peak) Dolby Vision 400 nits X-Rite Flicker Free | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 2-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 221 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-oled-14iph11-ultra-7-355</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-5-320-bq385w</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:28:14</t>
+          <t>2026-08-01 14:16:48</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Laptop MacBook Pro 14 inch M5 Pro 48GB/1TB</t>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ632W (Core 5 320, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>84990000</v>
+        <v>21090000</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>85490000</v>
+        <v>26990000</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm giá 500,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Phiếu mua hàng Chuột, Bàn phím (Apple) trị giá 500,000đ | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng 50.000đ mua Chuột Logitech M240 | Tặng Phiếu mua hàng Balo, Túi chống sốc (giá trị trên 1,000,000đ) trị giá 300,000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Apple M5 Pro | Số nhân:: 15 | Số luồng:: Hãng không công bố | Tốc độ CPU:: 307 GB/s memory bandwidth | Card màn hình:: Card tích hợp - 16 nhân GPU | RAM:: 48 GB | Loại RAM:: Hãng không công bố | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 1 TB SSD | Kích thước màn hình:: 14.2" | Độ phân giải:: Liquid Retina XDR display (3024 x 1964) | Tần số quét:: up to 120 Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: ProMotion Độ sáng XDR: toàn màn hình 1000 nits, cao nhất 1600 nits (chỉ nội dung HDR) Độ sáng SDR: lên đến 1000 nits Wide color (P3) True Tone Technology 1 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm MagSafe 3 3 x Thunderbolt 5 (hỗ trợ DisplayPort, Thunderbolt 5 (up to 120Gb/s), USB 4 (up to 120Gb/s)) HDMI | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Khe đọc thẻ nhớ:: SDXC | Webcam:: Camera 12MP Center Stage | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Hệ thống âm thanh 6 loa Spatial Audio 3 microphones Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-Po, 72.4 Wh | Hệ điều hành:: macOS Tahoe | Thời điểm ra mắt:: 03/2026 | Kích thước:: Dài 312.6 mm - Rộng 221.2 mm - Dày 15.5 mm - 1.6 kg | Chất liệu:: Vỏ nhôm tái chế 100% | Hãng:: MacBook. Xem thông tin hãng</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 8 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/macbook-pro-14-inch-m5-pro-48gb-1tb</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-5-320-bq632w</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:28:27</t>
+          <t>2026-08-01 14:17:01</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Laptop MacBook Pro 14 inch M5 Pro 48GB/2TB</t>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ395W (Core 7 350, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>98690000</v>
+        <v>28490000</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>99190000</v>
+        <v>35490000</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm giá 500,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Phiếu mua hàng Chuột, Bàn phím (Apple) trị giá 500,000đ | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng 50.000đ mua Chuột Logitech M240 | Tặng Phiếu mua hàng Balo, Túi chống sốc (giá trị trên 1,000,000đ) trị giá 300,000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Apple M5 Pro | Số nhân:: 15 | Số luồng:: Hãng không công bố | Tốc độ CPU:: 307 GB/s memory bandwidth | Card màn hình:: Card tích hợp - 16 nhân GPU | RAM:: 48 GB | Loại RAM:: Hãng không công bố | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 2 TB SSD | Kích thước màn hình:: 14.2" | Độ phân giải:: Liquid Retina XDR display (3024 x 1964) | Tần số quét:: up to 120 Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: ProMotion Độ sáng XDR: toàn màn hình 1000 nits, cao nhất 1600 nits (chỉ nội dung HDR) Độ sáng SDR: lên đến 1000 nits Wide color (P3) True Tone Technology 1 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm MagSafe 3 3 x Thunderbolt 5 (hỗ trợ DisplayPort, Thunderbolt 5 (up to 120Gb/s), USB 4 (up to 120Gb/s)) HDMI | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Khe đọc thẻ nhớ:: SDXC | Webcam:: Camera 12MP Center Stage | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Hệ thống âm thanh 6 loa Spatial Audio 3 microphones Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-Po, 72.4 Wh | Hệ điều hành:: macOS Tahoe | Thời điểm ra mắt:: 03/2026 | Kích thước:: Dài 312.6 mm - Rộng 221.2 mm - Dày 15.5 mm - 1.6 kg | Chất liệu:: Vỏ nhôm tái chế 100% | Hãng:: MacBook. Xem thông tin hãng</t>
+          <t>Công nghệ CPU:: Intel Core 7 Wildcat Lake - 350 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 17 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/macbook-pro-14-inch-m5-pro-48gb-2tb</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-7-350-bq395w</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:28:41</t>
+          <t>2026-08-01 14:17:16</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Gaming Cyborg 15 Black Edition A13VE - A13VE-2410VN (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ633W (Core 7 350, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>27990000</v>
+        <v>25090000</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>31990000</v>
+        <v>30490000</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.60 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Công nghệ âm thanh:: Hi-Res Audio DTS Audio | Tản nhiệt:: Cooler Boost 1 x Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 53.5 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.36 mm - Rộng 250.34 mm - Dày 22.9 mm - 1.98 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 7 Wildcat Lake - 350 | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 8 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Hãng không công bố | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-black-edition-a13ve-i5-13420h-a13ve-2410vn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-7-350-bq633w</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:28:54</t>
+          <t>2026-08-01 14:17:30</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Gaming Cyborg 15 C13WEO-417VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Asus Vivobook 16 X1607CA - MB387W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>35590000</v>
+        <v>25090000</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>36990000</v>
+        <v>33490000</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card rời - Intel UHD Graphics (tích hợp) + NVIDIA GeForce RTX 5050 GPU, 8GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB Type-A 1 x Headphone/ Microphone combo audio jack 1 x USB Type C (chỉ hỗ trợ Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: DTS Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.98 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.7 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 SO-DIMM | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 25.06 mm - Rộng 35.7 mm - Dày 1.79 ~ 1.99 - 1.88 kg | Chất liệu:: Khung nhôm - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-c13weo-417vn-i7-13620h</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-16-x1607ca-ultra-5-225h-mb387w</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:29:07</t>
+          <t>2026-08-01 14:17:44</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Gaming Raider 16 MAX HX B2WI - 095VN (Ultra 9 290HX Plus, 64GB, 2TB, RTX 5080 16GB, QHD+ OLED 240Hz, Win11)</t>
+          <t>Laptop Asus Vivobook Go 14 E1404FA - EB012W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>1350000</v>
+        <v>17990000</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>1590000</v>
+        <v>22990000</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 9 Arrow Lake - 290HX Plus | Số nhân:: 24 | Số luồng:: 24 | Tốc độ CPU:: 2.70 GHz (Lên đến 5.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 1334 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5080, 16 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 175 W | RAM:: 64 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe 32 GB) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: 128 GB | Ổ cứng:: 2 TB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 4 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: QHD+ (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 240Hz | Độ phủ màu:: 100% DCI-P3 | Cổng giao tiếp:: 2 x Thunderbolt 4 (hỗ trợ Power Delivery 3.1 và DisplayPort) 3 x USB Type-A 3.2 Gen 2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Cooler Boost 3 Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-Po, 91.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 363 mm - Rộng 269.7 mm - Dày 28.85 mm - 2.6 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-gaming-raider-16-max-hx-b2wi-ultra-9-290hx-plus-095vn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb012w</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:29:22</t>
+          <t>2026-08-01 14:17:56</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 F1MG-1264VN (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Asus Vivobook Go 14 E1404FA - EB1832W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>19990000</v>
+        <v>17990000</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>22390000</v>
+        <v>22990000</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core thế hệ 12 - 120U | Số nhân:: Hãng không công bố | Số luồng:: 12 | Tốc độ CPU:: 1.45 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (2280) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: Hãng không công bố | Cổng giao tiếp:: 3 x USB 3.2 Gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell, 46.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.7 kg | Chất liệu:: Plastic (nhựa dẻo)</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-modern-15-f1mg-1264vn-core-5-120u</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb1832w</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:29:35</t>
+          <t>2026-08-01 14:18:09</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Laptop SingPC M16-i382 (i3 1215U, 8GB, 256GB, WUXGA, Win11 Pro)</t>
+          <t>Laptop Asus Vivobook S 16 S3607VA - RP155W (Core 5 210H, 16GB, 512GB, Full HD+ 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>13890000</v>
+        <v>30190000</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>15190000</v>
+        <v>34990000</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i3 Alder Lake - 1215U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.2GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 256 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Hãng không công bố | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare LED Backlit | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 259.6 mm - Dày 15.9 mm - 1.7 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/singpc-m16-i382-i3-1215u</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-s-16-s3607va-core-5-210h-rp155w</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:29:49</t>
+          <t>2026-08-01 14:18:23</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Laptop SingPC M16-i595 (i5 1235U, 16GB, 512GB, WUXGA, Win11 Pro)</t>
+          <t>Laptop Asus Vivobook S14 S3407VA - LY256W (Core 7 240H, 16GB, 512GB, WUXGA OLED, Win11)</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>18390000</v>
+        <v>27090000</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>19990000</v>
+        <v>29990000</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Alder Lake - 1235U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.30 GHz (Lên đến 4.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 72% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 17.9 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/singpc-m16-i595-i5-1235u</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-s14-s3407va-core-7-240h-ly256w</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:30:02</t>
+          <t>2026-08-01 14:18:37</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP OmniBook X Flip 14 fk0082AU - BZ7N8PA (R7 AI 350, 32GB, 1TB, 2K, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Asus Zenbook 14 UM3406GA - QD075W (R7 AI 445, 16GB, 512GB, WUXGA OLED, Win11)</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>39890000</v>
+        <v>34590000</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>40890000</v>
+        <v>39990000</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: 2K (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Corning Gorilla Glass 3 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB Type-C (hỗ trợ truyền dữ liệu, DisplayPort 2.1, Power delivery 3.1, HP Sleep and Charge) Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E MT7922 Bluetooth 5.3 | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ | Thông tin Pin:: 3-cell Li-Po, 59 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 218.5 mm - Dày 14.6 mm - 1.39 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.0 GHz | NPU:: AMD XDNA | Card màn hình:: Card tích hợp | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 70% Less harmful blue light 400 nits 600 nits (Khi bật HDR) | Cổng giao tiếp:: 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 75 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.01 mm - Rộng 31.24 mm - Dày 1.49 mm - 1.2 kg | Chất liệu:: Nhôm nguyên khối</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-x-flip-14-fk0082au-r7-ai-350-bz7n8pa</t>
+          <t>https://www.thegioididong.com/laptop/asus-zenbook-14-um3406ga-r7-ai-445-qd075w</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:30:56</t>
+          <t>2026-08-01 14:18:51</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP Probook 4 G1ah 16 - C40JPAT (R5 220, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Zenbook A14 UX3407NA - QD132WS (X2E 88 100, 16GB, 512GB, WUXGA OLED, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>25490000</v>
+        <v>44590000</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>29890000</v>
+        <v>48990000</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 220 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 48 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x USB Type-C 3.2 Gen 2 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: FHD 1080p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 359.4 mm - Rộng 251 mm - Dày 17 mm - 1.785 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Snapdragon X2 Elite - X2E88100 | Số nhân:: 18 | Số luồng:: 18 | Tốc độ CPU:: Lên đến 4.0 GHz khi tải nặng | NPU:: Qualcomm Hexagon | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | Card màn hình:: Card tích hợp - Qualcomm Adreno GPU | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 9523 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: VESA DisplayHDR Thời gian phản hồi 0.2 ms Màn hình bảo vệ mắt - EYE CARE Low Blue Light Chống chói Anti Glare 400 nits 600 nits (Khi bật HDR) 1.07 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Công nghệ Smart AMP | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.7 mm - Rộng 213.9 mm - Dày 15.9 mm - 0.986 kg | Chất liệu:: Vỏ gốm nhôm Ceraluminum</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-probook-4-g1ah-16-r5-220-c40jpat</t>
+          <t>https://www.thegioididong.com/laptop/asus-zenbook-a14-ux3407na-x2e-88-100-qd132ws</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:31:10</t>
+          <t>2026-08-01 14:19:05</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP ProBook 4 G1iR 14 - C40JKAT (Core 5 120U, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Zenbook A14 UX3407NA - QD254W (X2E 88 100, 32GB, 1TB, WUXGA OLED, Win11)</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>26990000</v>
+        <v>58290000</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>34590000</v>
+        <v>63990000</v>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>-22%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB Type-A 2 x USB Type-C (hỗ trợ DisplayPort 1.4, Power delivery 3.0, HP Sleep and Charge) 1 x Headphone/microphone combo LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 56 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Snapdragon X2 Elite - X2E88100 | Số nhân:: 18 | Số luồng:: 18 | Tốc độ CPU:: Lên đến 4.0 GHz khi tải nặng | NPU:: Qualcomm Hexagon | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | Card màn hình:: Card tích hợp - Qualcomm Adreno GPU | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 9523 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: VESA DisplayHDR Thời gian phản hồi 0.2 ms Màn hình bảo vệ mắt - EYE CARE Low Blue Light Chống chói Anti Glare 400 nits 600 nits (Khi bật HDR) 1.07 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Công nghệ Smart AMP | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.7 mm - Rộng 213.9 mm - Dày 15.9 mm - 0.986 kg | Chất liệu:: Vỏ gốm nhôm Ceraluminum</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-probook-4-g1ir-14-core-5-120u-c40jkat</t>
+          <t>https://www.thegioididong.com/laptop/asus-zenbook-a14-ux3407na-x2e-88-100-qd254w</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:31:23</t>
+          <t>2026-08-01 14:19:19</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming Legion 5 15AHP11 - 83Q7001HVN (R7 250, 16GB, 512GB, RTX 5050 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
+          <t>Laptop Asus Zenbook S 16 UM5606GA - SS441W (R9 AI 465, 16GB, 512GB, 3K OLED 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>55290000</v>
+        <v>45090000</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>55990000</v>
+        <v>49490000</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: Boost Clock 2662MHz, TGP 115W, 440 AI TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: 2.5K | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: DisplayHDR True Black 1000 | Cổng giao tiếp:: 1x Ethernet 2 x USB Type-C (USB4 40Gbps) hỗ trợ USB PD 65 - 100W và DisplayPort 1.4 1 x Headphone/ Microphone combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) 2×2 Bluetooth 6.0 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 244.5 mm - Rộng 344 mm - Dày 19~20 - 1.87 kg | Chất liệu:: Mặt trên: nhôm + Mặt dưới: nhựa PC-ABS</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 9 - 465 | Số nhân:: 10 | Số luồng:: 20 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Màn hình bảo vệ mắt - EYE CARE Low Blue Light DisplayHDR True Black 1000 500 nits Chống chói Anti Glare 1100 nits (peak) | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Công nghệ Smart AMP | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 83 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 353.6 mm - Rộng 243 mm - Dày 12.9 mm - 1.5 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15ahp11-r7-250-83q7001hvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-zenbook-s-16-um5606ga-r9-ai-465-ss441w</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:31:37</t>
+          <t>2026-08-01 14:19:33</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming Legion 5 15AHP11 - 83Q7001JVN (R7 250, 16GB, 512GB, RTX 5060 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
+          <t>Laptop Dell 14 DC14250 - DC14250-C3U085W11SLU-27 (Core 3 100U, 8GB, 512GB, Full HD+, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>55490000</v>
+        <v>18990000</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>58990000</v>
+        <v>19390000</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 2TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WQXGA (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light 1000 nits (peak) G-Sync 500 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB4 Type-C (DisplayPort 1.4, Power Delivery) LAN (RJ45) HDMI 2.1 3 x USB A | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio Audio by HARMAN Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Legion ColdFont Hyper | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-ion, 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344 mm - Rộng 244.5 mm - Dày 19.95 mm - 1.87 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits ComfortView Plus | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15ahp11-r7-250-83q7001jvn</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-3-100u-dc14250-c3u085w11slu-27</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:31:51</t>
+          <t>2026-08-01 14:19:47</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming Legion 5 15IPH11 - 83RW0023VN (Ultra 7 356H, 16GB, 512GB, RTX 5060 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
+          <t>Laptop Dell 14 DC14250 - DC4C5375W1-2Y (Core 5 120U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>59490000</v>
+        <v>30990000</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>64990000</v>
+        <v>32090000</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 365H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 15.3" | Độ phân giải:: WQXGA (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light 1000 nits (peak) 500 nits typical G-Sync DisplayHDR True Black 1000 High Gaming Performance Flicker Free | Cổng giao tiếp:: 3 x USB Jack tai nghe 3.5 mm 1 x USB Type-C (USB Power Delivery, DisplayPort 2.1) LAN (RJ45) HDMI 2.1 1 x Thunderbolt 4 (hỗ trợ DisplayPort 2.1, Power Delivery) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đèn chuyển màu RGB - 24 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Realtek Audio Audio by HARMAN Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Legion ColdFont Hyper | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344 mm - Rộng 244.5 mm - Dày 19.95 mm - 1.87 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226 mm - Dày 18 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15iph11-ultra-7-356h-83rw0023vn</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-5-120u-dc4c5375w1-2y</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:32:04</t>
+          <t>2026-08-01 14:20:01</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming LOQ 15AHP11 - 83TN0040VN (R7 250, 16GB, 512GB, RTX 5050 8GB, WUXGA 165Hz, Win11)</t>
+          <t>Laptop Dell 14 DC14250 - 71100515 (Core 7 150U, 16GB, 512GB, Full HD+ 120Hz, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>43490000</v>
+        <v>34790000</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>46990000</v>
+        <v>35490000</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 2TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Low Blue Light G-Sync AMD Freesync 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm LAN (RJ45) HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) 3 x USB A | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344.9 mm - Rộng 254.83 mm - Dày 23.25 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 320 mm - Rộng 215.97 mm - Dày 18.02 mm - 1.83 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15ahp11-r7-250-83tn0040vn</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-71100515</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:32:17</t>
+          <t>2026-08-01 12:27:36</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming LOQ 15ARP10E - 83S0004FVN (R7 7735HS, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Dell 14 DC14250 - DC14250-C7U161W11SLU-2Y (Core 7 150U, 16GB, 1TB, Full HD+ ,OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>34490000</v>
+        <v>36990000</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>40990000</v>
+        <v>37990000</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7735HS | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 65 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: AMD Freesync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A 1x Ethernet 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery 3.0) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3 - cell Li-ion, 57.5 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 359.2 mm - Rộng 236 mm - Dày 22.95 mm - 1.8 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: E-core: 0.9 GHz - 3.3 GHz, P-core: 1.2 GHz - 4.7 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MT/s | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 PCIe Gen 4 x 4 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (M.2 2230)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Display with ComfortView Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.615 mm - Rộng 31.4 mm - Dày 1.669 ~ 1.807 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15arp10e-r7-7735hs-83s0004fvn</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-dc14250-c7u161w11slu-2y</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:32:30</t>
+          <t>2026-08-01 12:27:51</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming LOQ 15IPH11 - 83SL000LVN (Ultra 7 356H, 16GB, 512GB, RTX 5060 8GB, WUXGA 165Hz, Win11)</t>
+          <t>Laptop Dell 15 DC15250 - 71100520 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>51490000</v>
+        <v>21990000</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>55990000</v>
+        <v>22590000</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 365H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 1TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Low Blue Light G-Sync AMD Freesync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 3 x USB Jack tai nghe 3.5 mm LAN (RJ45) HDMI 2.1 1 x Thunderbolt 4 (hỗ trợ DisplayPort 2.1, Power Delivery) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 344.9 mm - Rộng 254.83 mm - Dày 23.25 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort 1.4, Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Bluetooth 5.0 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.5 mm - Dày 18.9 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15iph11-ultra-7-356h-83sl000lvn</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-71100520</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:32:43</t>
+          <t>2026-08-01 12:28:05</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming LOQ 15IRX9 - 83DV01H2VN (i7 13645HX, 16GB, 1TB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Dell 15 DC15250 - CPH993 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>34590000</v>
+        <v>21990000</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>36990000</v>
+        <v>22590000</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13645HX | Số nhân:: 14 | Số luồng:: 20 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 150 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD NVMe M.2 PCIe Gen 4.0x4 (2242) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1x Ethernet 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort 1.4) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.86 mm - Rộng 258.7 mm - Dày 23.9 mm - 2.38 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: Đang cập nhật | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 70% Less harmful blue light 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 16.96 mm đến 18.99 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15irx9-i7-13645hx-83dv01h2vn</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-cph993</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:32:56</t>
+          <t>2026-08-01 12:28:19</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming LOQ 15IRX9 - 83DV01H3VN (i7 13645HX, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Dell 15 DC15250 - DC5C3259W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>34590000</v>
+        <v>21990000</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>36490000</v>
+        <v>22590000</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13645HX | Số nhân:: 14 | Số luồng:: 20 | Tốc độ CPU:: 2.60 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 105 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1x Ethernet 3 x USB 3.2 Gen 1 HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.86 mm - Rộng 258.7 mm - Dày 23.9 mm - 2.38 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-15irx9-i7-13645hx-83dv01h3vn</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3259w1-2y</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:33:09</t>
+          <t>2026-08-01 12:28:34</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming LOQ Essential 15ARP10E - 83S0000DVN (R5 7535HS, 16GB, 512GB, RTX 3050 6GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Dell 15 DC15250 - DC5C3851W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>24190000</v>
-      </c>
-      <c r="C67" s="2" t="n">
-        <v>35990000</v>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>-33%</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
+        <v>22590000</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 7535HS | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.30 GHz (Lên đến 4.55 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 6 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 65 W | Hiệu năng xử lý AI (TOPS):: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB onboard + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: AMD Freesync Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery 3.0) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek ALC3287 Nahimic Audio High Definition (HD) Audio | Tản nhiệt:: Hyper Champer Cooling | Thông tin Pin:: 4-cell Li-ion, 57.5 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 359.2 mm - Rộng 236 mm - Dày 22.95 mm - 1.8 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x Headphone/ Microphone combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 2 x USB 2.0 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 235 mm - Rộng 358.5 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-loq-essential-15arp10e-r5-7535hs-83s0000dvn</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3851w1-2y</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:33:22</t>
+          <t>2026-08-01 12:28:47</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad 5 2in1 14IPH11 - 83UG0026VN (Ultra 5 322, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
+          <t>Laptop Dell 15 DC15255 - DC5R5973W1-2Y (R5 7530U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>30590000</v>
+        <v>24990000</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>32990000</v>
+        <v>25690000</v>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.6 mm - Rộng 224.9 mm - Dày 17.4 mm - 1.54 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 7530U | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/microphone combo 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-5-2in1-14iph11-ultra-5-322-83ug0026vn</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r5-7530u-dc5r5973w1-2y</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:33:36</t>
+          <t>2026-08-01 12:29:01</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad 5 2in1 14IPH11 - 83UG0027VN (Ultra 7 355, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="n">
-        <v>35590000</v>
-      </c>
-      <c r="C69" s="2" t="n">
-        <v>37990000</v>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
+          <t>Laptop Dell 16 DC16250 - 71100513 (Core 5 120U, 16GB, 1TB, Full HD+, OfficeH24+365B, Win11)</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr"/>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.6 mm - Rộng 224.9 mm - Dày 17.4 mm - 1.54 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits eDP Wide View Angle | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2W x 2 Realtek ALC3254 Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 05/2025 | Kích thước:: Dài 357.3 mm - Rộng 250.6 mm - Dày 18.23 mm - 2 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-5-2in1-14iph11-ultra-7-355-83ug0027vn</t>
+          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-5-120u-71100513</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:33:49</t>
+          <t>2026-08-01 12:29:14</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14ARP10 - 83K600E6VN (R5 7535HS, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Dell Pro 14 PC14250 - PC14250-235U-16512WP-2Y (Ultra 5 235U, 16GB, 512GB, Full HD+, Win11Pro)</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>19690000</v>
+        <v>38990000</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>24990000</v>
+        <v>39990000</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 7533HS | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.30 GHz (Lên đến 4.55 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 660M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 NVMe PCIe Gen 4 mở rộng (nâng cấp tối đa 1TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.39 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 235U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 2.0 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1x Global headset jack 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4, USB Power Delivery 3.1 and DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14arp10-r5-7535hs-83k600e6vn</t>
+          <t>https://www.thegioididong.com/laptop/dell-pro-14-pc14250-ultra-5-235u-pc14250-235u-16512wp-2y</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:34:02</t>
+          <t>2026-08-01 12:29:28</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14ARP10 - 83K6005WVN (R7 7735HS, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Dell Pro 14 PC14250 - PC14250-255U-32512WH-2Y (Ultra 7 255U, 32GB, 512GB, Full HD+, Win11)</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>19690000</v>
+        <v>55990000</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>26990000</v>
+        <v>56690000</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>-27%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7735HS | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 680M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.39 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 2.0 GHz (Lên đến 5.2 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe trống) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1x Global headset jack 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4, USB Power Delivery 3.1 and DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14arp10-r7-7735hs-83k6005wvn</t>
+          <t>https://www.thegioididong.com/laptop/dell-pro-14-pc14250-ultra-7-255u-pc14250-255u-32512wh-2y</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:34:15</t>
+          <t>2026-08-01 12:29:42</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IPH11 - 83UQ003NVN (Ultra 5 322, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Dell Pro 15 Essential PV15250 - PV15250-100U-8512W-2Y (Core 3 100U, 8GB, 512GB, Full HD, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>25390000</v>
-      </c>
-      <c r="C72" s="2" t="n">
-        <v>27990000</v>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>-9%</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
+        <v>23990000</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.43 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Rộng 358.5 mm - Dày 17.5 mm | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iph11-ultra-5-322-83uq003nvn</t>
+          <t>https://www.thegioididong.com/laptop/dell-pro-15-essential-pv15250-core-3-100u-pv15250-100u-8512w-2y</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:34:29</t>
+          <t>2026-08-01 12:29:56</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IPH11 - 83UQ003PVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop GIGABYTE Gaming A16 - 3THK3VN893SH (R7 260, 16GB, 512GB, RTX 5050 8GB, Full HD+ 165Hz, Win11)</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>30090000</v>
+        <v>33890000</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>32990000</v>
+        <v>38990000</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 17.9 mm - 1.43 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 260 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.80 GHz (Lên đến 5.10 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 85 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB Type-C (hỗ trợ USB 4, DisplayPort 1.4 và Power Delivery 3.0) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6E (802.11ax) | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Smart Cooling Công nghệ làm mát WINDFORCE 2 quạt | Tính năng khác:: MUX Switch Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-Po, 76.1 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.3 mm - Rộng 262.5 mm - Dày 22.99 mm - 2.191 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iph11-ultra-7-355-83uq003pvn</t>
+          <t>https://www.thegioididong.com/laptop/gigabyte-gaming-a16-r7-260-a16-3thk3vn893sh</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:34:42</t>
+          <t>2026-08-01 12:30:08</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002NVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop GIGABYTE Gaming A16 - 3VHK3VN893SH (R7 260, 16GB, 512GB, RTX 5060 8GB, Full HD+ 165Hz, Win11)</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>24190000</v>
+        <v>37790000</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>26490000</v>
+        <v>40990000</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 260 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.80 GHz (Lên đến 5.10 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 85 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB onboard + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB Type-C (hỗ trợ USB 4, DisplayPort 1.4 và Power Delivery 3.0) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6E (802.11ax) | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Smart Cooling Công nghệ làm mát WINDFORCE 2 quạt | Tính năng khác:: MUX Switch Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-Po, 76.1 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.3 mm - Rộng 262.5 mm - Dày 22.99 mm - 2.191 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002nvn</t>
+          <t>https://www.thegioididong.com/laptop/gigabyte-gaming-a16-r7-260-a16-3vhk3vn893sh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:34:55</t>
+          <t>2026-08-01 12:30:22</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002PVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop GIGABYTE Gaming AERO X16 - 1VH93VNC94AH (R7 AI 350, 16GB, 1TB, RTX 5060 8GB, WQXGA 165Hz, Win11)</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>20790000</v>
+        <v>42290000</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>22990000</v>
+        <v>44990000</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 85 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 1 TB SSD M.2 PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: MUX Switch Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB Type-C (hỗ trợ USB 4, DisplayPort 1.4 và Power Delivery 3.0) 1 x USB-A (hỗ trợ USB 2.0) 2 x USB 3.2 gen 1 Type-A LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6E (802.11ax) | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: 4 x Ống dẫn nhiệt 2 quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-Po, 76.1 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 355 mm - Rộng 250.7 mm - Dày 19.99 mm - 1.972 kg | Chất liệu:: Nắp lưng và mặt đáy bằng nhôm</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002pvn</t>
+          <t>https://www.thegioididong.com/laptop/gigabyte-gaming-aero-x16-r7-ai-350-aero-x16-1vh93vnc94ah</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:35:08</t>
+          <t>2026-08-01 12:30:36</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15ARP10 - 83K700YUVN (R5 7535HS, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop HP 15 fd2126TU - D72CBPA (Ultra 5 225U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>18690000</v>
+        <v>22990000</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>24990000</v>
+        <v>26990000</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 7535HS | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.30 GHz (Lên đến 4.55 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 660M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe RAM) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB Type-C 3.2 Gen 1 (hỗ trợ DisplayPort 1.2 và Power delivery 3.0) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Nắp lưng và chiếu nghỉ tay bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: Hãng không công bố | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB Type-A 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack HDMI | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.8 mm - Rộng 236 mm - Dày 18.6 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15arp10-r5-7535hs-83k700yuvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-15-fd2126tu-ultra-5-225u-d72cbpa</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:35:21</t>
+          <t>2026-08-01 12:30:51</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15ARP10 - 83K700YVVN (R7 7735HS, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop HP 15 fd2127TU - D72CCPA (Ultra 5 225U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>19890000</v>
+        <v>22990000</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>26990000</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>-26%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7735HS | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.20 GHz (Lên đến 4.75 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon 660M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.40 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 2800 MHz | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB Type-A HDMI 1.4b 1 x USB Type - C (hỗ trợ Power Delivery 3.1, DisplayPort 1.4b, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.8 mm - Rộng 236 mm - Dày 18.6 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15arp10-r7-7735hs-83k700yvvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-15-fd2127tu-ultra-5-225u-d72ccpa</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:35:35</t>
+          <t>2026-08-01 12:31:05</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IPH11 - 83UR00A4VN (Ultra 5 322, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop HP Gaming HyperX Omen 15 ga0092TX - D72D8PA (i5 14450HX, 16GB, 512GB, RTX 5050 8GB, WUXGA 165Hz, Win11)</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>24990000</v>
+        <v>45590000</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>27990000</v>
+        <v>46990000</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 2.50 GHz (Lên đến 4.40 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.63 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 421 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.37 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iph11-ultra-5-322-83ur00a4vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-gaming-hyperx-omen-15-ga0092tx-i5-14450hx-d72d8pa</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:35:48</t>
+          <t>2026-08-01 12:31:19</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IPH11 - 83UR0075VN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop HP Gaming VICTUS 15 fa2451TX - D17WPPA (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>28990000</v>
+        <v>27490000</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>32990000</v>
+        <v>31990000</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4.0 mở rộng (nâng cấp tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4 1 x USB Type-C (hỗ trợ USB, Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.63 kg | Chất liệu:: Mặt lưng nhôm - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35W - 115W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x USB 3.2 1 x USB 3.2 (hỗ trợ HP Sleep and Charge) 1 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358 mm - Rộng 255 mm - Dày 23.5 mm - 2.29 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iph11-ultra-7-355-83ur0075vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-gaming-victus-15-fa2451tx-i5-13420h-d17wppa</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:36:01</t>
+          <t>2026-08-01 12:31:34</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IPH11 - 83UR00A5VN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop HP HyperX Omen 15 ga0091TX - D72D7PA (i5 14450HX, 16GB, 512GB, RTX 5060 8GB, WUXGA 165Hz, Win11)</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>29490000</v>
+        <v>48590000</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>32990000</v>
+        <v>49990000</v>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.63 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3840 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 614 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.363 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iph11-ultra-7-355-83ur00a5vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-hyperx-omen-15-ga0091tx-i5-14450h-d72d7pa</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:36:14</t>
+          <t>2026-08-01 12:31:48</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00A8VN (Core 3 304, 8GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop HP OmniBook X Flip 14 fk0082AU - BZ7N8PA (R7 AI 350, 32GB, 1TB, 2K, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>18990000</v>
+        <v>39890000</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>20890000</v>
+        <v>40890000</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core™ 3 - 304 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz (P-core), Turbo tối đa 4.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 2242 PCIe 4.0x4 NVMe | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 × USB-C (USB 5 Gbps), hỗ trợ USB PD 45–65W và DisplayPort 1.2 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Optimized with Dolby Audio 2W x 2 High Definition (HD) Audio Stereo speakers | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 240 mm - Rộng 343 mm - Dày 17 - 18 - 1.59 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: 2K (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Corning Gorilla Glass 3 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB Type-C (hỗ trợ truyền dữ liệu, DisplayPort 2.1, Power delivery 3.1, HP Sleep and Charge) Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E MT7922 Bluetooth 5.3 | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ | Thông tin Pin:: 3-cell Li-Po, 59 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 218.5 mm - Dày 14.6 mm - 1.39 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-3-304-83rr00a8vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-x-flip-14-fk0082au-r7-ai-350-bz7n8pa</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:36:27</t>
+          <t>2026-08-01 12:32:01</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00AAVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Lenovo ThinkBook 14 G9 - 21V0005PVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>23590000</v>
+        <v>28790000</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>26490000</v>
+        <v>31190000</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00aavn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-g9-r7-250-21v0005pvn</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -3968,40 +3936,40 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:36:40</t>
+          <t>2026-08-01 14:46:40</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Ideapad Slim 3 15IWC11 - 83RR00CVVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Lenovo ThinkBook 14 Gen 9 IRL - 21UY008TVN (i5 13420H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>20190000</v>
+        <v>27790000</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>22990000</v>
+        <v>28890000</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00cvvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-gen-9-irl-i5-13420h-21uy008tvn</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4011,2512 +3979,695 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:36:54</t>
+          <t>2026-08-01 14:46:54</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US002TVN (Ultra 5 322, 24GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Lenovo ThinkBook 16 G9 - 21UT005MVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>30090000</v>
+        <v>30190000</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>31990000</v>
+        <v>31590000</v>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 24 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356 mm - Rộng 253.5 mm - Dày 17.5 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-5-322-83us002tvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-16-g9-r7-250-21ut005mvn</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:37:07</t>
+          <t>2026-08-01 14:47:08</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - DC5C3851W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo ThinkPad E14 Gen 7 - 21SX005NVN (Ultra 5 225U, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>22590000</v>
-      </c>
-      <c r="C85" s="2" t="inlineStr"/>
-      <c r="D85" s="2" t="inlineStr"/>
-      <c r="E85" s="2" t="inlineStr"/>
+        <v>31990000</v>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>33890000</v>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x Headphone/ Microphone combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 2 x USB 2.0 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 235 mm - Rộng 358.5 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4 với USB Power Delivery và DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Audio by HARMAN Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 19.7 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3851w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-5-225u-21sx005nvn</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:37:36</t>
+          <t>2026-08-01 14:47:22</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - CPH992 (i5 1334U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365B, Win11)</t>
+          <t>Laptop Lenovo ThinkPad X9 14 Gen 1 - 21QA006JVN (Ultra 7 258V, 32GB, 512GB, WUXGA OLED, Win11Pro)</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>21990000</v>
+        <v>53790000</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>23490000</v>
+        <v>55190000</v>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 1334U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 2666 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Bluetooth 5.0 Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235.6 mm - Dày 19 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.80 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Chống chói Anti Glare Dolby Vision 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm HDMI 2.1 2 x USB-C (hỗ trợ Thunderbolt 4/USB 4, USB Power Delivery và DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.8 mm - Rộng 212.3 mm - Dày 17.18 mm - 1.21 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-i5-1334u-cph992</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-x9-14-gen-1-ultra-7-258v-21qa006jvn</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:37:50</t>
+          <t>2026-08-01 14:47:36</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - DC15250-i5U165W11SLU-27 (i5 1334U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+          <t>Laptop Lenovo V14 G5 - 83HD0035VN (Core7 240H, 16G, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>21990000</v>
+        <v>27490000</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>23490000</v>
+        <v>28590000</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 1334U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.30 GHz (Lên đến 4.60 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm HDD SATA (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 18.99 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) LAN (RJ45) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Ion, 47 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324.2 mm - Rộng 215.2 mm - Dày 17.9 mm - 1.37 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-i5-1334u-dc15250-i5u165w11slu-27</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-v14-g5-core7-240h-83hd0035vn</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:38:03</t>
+          <t>2026-08-01 14:47:50</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - DC15250-i7U161W11SLU-27 (i7 1355U, 16GB, 1TB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002LVN (Ultra 5 322, 16GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>26990000</v>
+        <v>36990000</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>27490000</v>
+        <v>39990000</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 1355U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.70 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-Po, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 18.99 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.45 mm - 1.38 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-i7-1355u-dc15250-i7u161w11slu-27</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-5-322-83tc002lvn</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:38:16</t>
+          <t>2026-08-01 14:48:05</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15255 - DC5R5973W1-2Y (R5 7530U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002MVN (Ultra 7 355, 32GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>24990000</v>
+        <v>54990000</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>25690000</v>
+        <v>57990000</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 7530U | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/microphone combo 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.95 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r5-7530u-dc5r5973w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-7-355-83tc002mvn</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:38:30</t>
+          <t>2026-08-01 14:48:19</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 16 DC16250 - 71092481 (Core 5 120U, 16GB, 1TB, Full HD+, OfficeHS24+365, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 OLED 14IPH11 - 83QM002FVN (Ultra 7 355, 32GB, 1TB, WUXGA OLED, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>27990000</v>
+        <v>52990000</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>28490000</v>
+        <v>55990000</v>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Display with ComfortView Wide viewing angle Chống chói Anti Glare | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1x Global headset jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD RGB | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Bảo mật vân tay | Công nghệ âm thanh:: Realtek ALC32xx | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 249.52 mm - Dày 17.37 mm - 1.98 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe 600nits (peak) Dolby Vision 400 nits X-Rite Flicker Free | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 2-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 221 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-5-120u-71092481</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-oled-14iph11-ultra-7-355</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:38:43</t>
+          <t>2026-08-01 14:48:33</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 16 DC16250 - 71100513 (Core 5 120U, 16GB, 1TB, Full HD+, OfficeH24+365B, Win11)</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr"/>
-      <c r="C91" s="2" t="inlineStr"/>
-      <c r="D91" s="2" t="inlineStr"/>
-      <c r="E91" s="2" t="inlineStr"/>
+          <t>Laptop MacBook Pro 14 inch M5 Pro 48GB/1TB</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>84990000</v>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>85490000</v>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>-1%</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm giá 500,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Phiếu mua hàng AirPods Pro, AirPods Max trị giá 800,000đ | Phiếu mua hàng Chuột, Bàn phím (Apple) trị giá 300,000đ | Phiếu mua hàng 50.000đ mua Chuột Logitech M240 | Tặng Phiếu mua hàng Balo, Túi chống sốc (giá trị trên 1,000,000đ) trị giá 300,000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+        </is>
+      </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits eDP Wide View Angle | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2W x 2 Realtek ALC3254 Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 05/2025 | Kích thước:: Dài 357.3 mm - Rộng 250.6 mm - Dày 18.23 mm - 2 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Apple M5 Pro | Số nhân:: 15 | Số luồng:: Hãng không công bố | Tốc độ CPU:: 307 GB/s memory bandwidth | Card màn hình:: Card tích hợp - 16 nhân GPU | RAM:: 48 GB | Loại RAM:: Hãng không công bố | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 1 TB SSD | Kích thước màn hình:: 14.2" | Độ phân giải:: Liquid Retina XDR display (3024 x 1964) | Tần số quét:: up to 120 Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: ProMotion Độ sáng XDR: toàn màn hình 1000 nits, cao nhất 1600 nits (chỉ nội dung HDR) Độ sáng SDR: lên đến 1000 nits Wide color (P3) True Tone Technology 1 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm MagSafe 3 3 x Thunderbolt 5 (hỗ trợ DisplayPort, Thunderbolt 5 (up to 120Gb/s), USB 4 (up to 120Gb/s)) HDMI | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Khe đọc thẻ nhớ:: SDXC | Webcam:: Camera 12MP Center Stage | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Hệ thống âm thanh 6 loa Spatial Audio 3 microphones Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-Po, 72.4 Wh | Hệ điều hành:: macOS Tahoe | Thời điểm ra mắt:: 03/2026 | Kích thước:: Dài 312.6 mm - Rộng 221.2 mm - Dày 15.5 mm - 1.6 kg | Chất liệu:: Vỏ nhôm tái chế 100% | Hãng:: MacBook. Xem thông tin hãng</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-5-120u-71100513</t>
+          <t>https://www.thegioididong.com/laptop/macbook-pro-14-inch-m5-pro-48gb-1tb</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:38:57</t>
+          <t>2026-08-01 14:48:47</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 16 DC16250 - DC16250-C7U161W11BLU-27 (Core 7 150U, 16GB, 1TB, Full HD+, OfficeHS24+365, Win11)</t>
+          <t>Laptop MacBook Pro 14 inch M5 Pro 48GB/2TB</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>35290000</v>
+        <v>98690000</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>35990000</v>
+        <v>99190000</v>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm giá 500,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Phiếu mua hàng AirPods Pro, AirPods Max trị giá 800,000đ | Phiếu mua hàng Chuột, Bàn phím (Apple) trị giá 300,000đ | Phiếu mua hàng 50.000đ mua Chuột Logitech M240 | Tặng Phiếu mua hàng Balo, Túi chống sốc (giá trị trên 1,000,000đ) trị giá 300,000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits ComfortView Plus | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.3 mm - Rộng 250.6 mm - Dày 18.23 mm - 2 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Apple M5 Pro | Số nhân:: 15 | Số luồng:: Hãng không công bố | Tốc độ CPU:: 307 GB/s memory bandwidth | Card màn hình:: Card tích hợp - 16 nhân GPU | RAM:: 48 GB | Loại RAM:: Hãng không công bố | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 2 TB SSD | Kích thước màn hình:: 14.2" | Độ phân giải:: Liquid Retina XDR display (3024 x 1964) | Tần số quét:: up to 120 Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: ProMotion Độ sáng XDR: toàn màn hình 1000 nits, cao nhất 1600 nits (chỉ nội dung HDR) Độ sáng SDR: lên đến 1000 nits Wide color (P3) True Tone Technology 1 tỷ màu | Cổng giao tiếp:: Jack tai nghe 3.5 mm MagSafe 3 3 x Thunderbolt 5 (hỗ trợ DisplayPort, Thunderbolt 5 (up to 120Gb/s), USB 4 (up to 120Gb/s)) HDMI | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Khe đọc thẻ nhớ:: SDXC | Webcam:: Camera 12MP Center Stage | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Hệ thống âm thanh 6 loa Spatial Audio 3 microphones Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Li-Po, 72.4 Wh | Hệ điều hành:: macOS Tahoe | Thời điểm ra mắt:: 03/2026 | Kích thước:: Dài 312.6 mm - Rộng 221.2 mm - Dày 15.5 mm - 1.6 kg | Chất liệu:: Vỏ nhôm tái chế 100% | Hãng:: MacBook. Xem thông tin hãng</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-7-150u-dc16250-c7u161w11blu-27</t>
+          <t>https://www.thegioididong.com/laptop/macbook-pro-14-inch-m5-pro-48gb-2tb</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:39:11</t>
+          <t>2026-08-01 14:49:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell Pro 14 PC14250 - PC14250-235U-16512WP-2Y (Ultra 5 235U, 16GB, 512GB, Full HD+, Win11Pro)</t>
+          <t>Laptop MSI Gaming Cyborg 15 Black Edition A13VE - A13VE-2410VN (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>38290000</v>
+        <v>29990000</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>39990000</v>
+        <v>31990000</v>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 235U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 2.0 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1x Global headset jack 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4, USB Power Delivery 3.1 and DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.60 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Công nghệ âm thanh:: Hi-Res Audio DTS Audio | Tản nhiệt:: Cooler Boost 1 x Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 53.5 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.36 mm - Rộng 250.34 mm - Dày 22.9 mm - 1.98 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-pro-14-pc14250-ultra-5-235u-pc14250-235u-16512wp-2y</t>
+          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-black-edition-a13ve-i5-13420h-a13ve-2410vn</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:39:24</t>
+          <t>2026-08-01 14:49:13</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell Pro 14 PC14250 - PC14250-255U-32512WH-2Y (Ultra 7 255U, 32GB, 512GB, Full HD+, Win11)</t>
+          <t>Laptop MSI Gaming Cyborg 15 C13WEO-417VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>55290000</v>
+        <v>35590000</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>56690000</v>
+        <v>36990000</v>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 2.0 GHz (Lên đến 5.2 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe trống) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1x Global headset jack 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4, USB Power Delivery 3.1 and DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226.15 mm - Dày 18.07 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card rời - Intel UHD Graphics (tích hợp) + NVIDIA GeForce RTX 5050 GPU, 8GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB Type-A 1 x Headphone/ Microphone combo audio jack 1 x USB Type C (chỉ hỗ trợ Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: DTS Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.98 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-pro-14-pc14250-ultra-7-255u-pc14250-255u-32512wh-2y</t>
+          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-c13weo-417vn-i7-13620h</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:39:39</t>
+          <t>2026-08-01 14:49:27</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell Pro 15 Essential PV15250 - PV15250-100U-8512W-2Y (Core 3 100U, 8GB, 512GB, Full HD, OfficeH24+365, Win11)</t>
+          <t>Laptop MSI Gaming Raider 16 MAX HX B2WI - 095VN (Ultra 9 290HX Plus, 64GB, 2TB, RTX 5080 16GB, QHD+ OLED 240Hz, Win11)</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>23990000</v>
-      </c>
-      <c r="C95" s="2" t="inlineStr"/>
-      <c r="D95" s="2" t="inlineStr"/>
-      <c r="E95" s="2" t="inlineStr"/>
+        <v>129590000</v>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>130990000</v>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>-1%</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Rộng 358.5 mm - Dày 17.5 mm | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 9 Arrow Lake - 290HX Plus | Số nhân:: 24 | Số luồng:: 24 | Tốc độ CPU:: 2.70 GHz (Lên đến 5.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 1334 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5080, 16 GB | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: 175 W | RAM:: 64 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe 32 GB) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: 128 GB | Ổ cứng:: 2 TB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 4 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: QHD+ (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 240Hz | Độ phủ màu:: 100% DCI-P3 | Cổng giao tiếp:: 2 x Thunderbolt 4 (hỗ trợ Power Delivery 3.1 và DisplayPort) 3 x USB Type-A 3.2 Gen 2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Cooler Boost 3 Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 4-cell Li-Po, 91.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 363 mm - Rộng 269.7 mm - Dày 28.85 mm - 2.6 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-pro-15-essential-pv15250-core-3-100u-pv15250-100u-8512w-2y</t>
+          <t>https://www.thegioididong.com/laptop/msi-gaming-raider-16-max-hx-b2wi-ultra-9-290hx-plus-095vn</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:39:53</t>
+          <t>2026-08-01 14:49:41</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 15 fd1487TU - D0BH4PA (Ultra 5 125H, 24GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop MSI Modern 14S G3MG-003VN (Core 5 320, 16GB, 1TB, Full HD+ 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>22490000</v>
+        <v>30090000</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>24390000</v>
+        <v>31490000</v>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 125H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 24 GB | Loại RAM:: DDR5 (1 khe RAM) | Tốc độ Bus RAM:: Hãng không công bố | Hỗ trợ RAM tối đa:: 24 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB Type-A HDMI 1.4b 1 x USB Type - C (hỗ trợ Power Delivery, DisplayPort 1.4b, HP Sleep and Charge) 1 x Headphone/microphone combo | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.8 mm - Rộng 236 mm - Dày 18.6 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: SSD 1TB, chuẩn M.2 2280 NVMe PCIe Gen4, tối đa hỗ trợ 2TB | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 50% NTSC | Công nghệ màn hình:: Chống chói Anti Glare | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 2 x USB 3.2 gen 1 Type-A LAN (RJ45) HDMI 2.1 2 x USB Type-C 3.2 Gen 2 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD card reader | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: DTS | Tản nhiệt:: 2 ống đồng 1 x Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.39 mm - Rộng 31.59 mm - Dày 1.11 ~ 1.79 - 1.45 kg | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-15-fd1487tu-ultra-5-125h-d0bh4pa</t>
+          <t>https://www.thegioididong.com/laptop/msi-modern-14s-g3mg-003vn-core-5-320</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:40:05</t>
+          <t>2026-08-01 14:49:55</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 15 fd2126TU - D72CBPA (Ultra 5 225U, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop MSI Modern 15 F1MG-1264VN (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>22990000</v>
+        <v>19990000</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>26990000</v>
+        <v>22390000</v>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: Hãng không công bố | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB Type-A 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack HDMI | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.8 mm - Rộng 236 mm - Dày 18.6 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core thế hệ 12 - 120U | Số nhân:: Hãng không công bố | Số luồng:: 12 | Tốc độ CPU:: 1.45 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (2280) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: Hãng không công bố | Cổng giao tiếp:: 3 x USB 3.2 Gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell, 46.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.7 kg | Chất liệu:: Plastic (nhựa dẻo)</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-15-fd2126tu-ultra-5-225u-d72cbpa</t>
+          <t>https://www.thegioididong.com/laptop/msi-modern-15-f1mg-1264vn-core-5-120u</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:40:18</t>
+          <t>2026-08-01 14:50:08</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 15 fd2127TU - D72CCPA (Ultra 5 225U, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop SingPC M16-i382 (i3 1215U, 8GB, 256GB, WUXGA, Win11 Pro)</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>22990000</v>
+        <v>13890000</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>26990000</v>
+        <v>15190000</v>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.40 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 2800 MHz | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB Type-A HDMI 1.4b 1 x USB Type - C (hỗ trợ Power Delivery 3.1, DisplayPort 1.4b, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.8 mm - Rộng 236 mm - Dày 18.6 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i3 Alder Lake - 1215U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.2GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 256 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-15-fd2127tu-ultra-5-225u-d72ccpa</t>
+          <t>https://www.thegioididong.com/laptop/singpc-m16-i382-i3-1215u</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:40:32</t>
+          <t>2026-08-01 14:50:22</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 240R G10 - C3SG9AT (Core 5 120U, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop SingPC M16-i595 (i5 1235U, 16GB, 512GB, WUXGA, Win11 Pro)</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>20490000</v>
+        <v>18390000</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>23590000</v>
+        <v>19990000</v>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack HDMI | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HP TrueVision Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 323.7 mm - Rộng 215 mm - Dày 13.2 mm - 1.404 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Alder Lake - 1235U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.30 GHz (Lên đến 4.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 72% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-240r-g10-core-5-120u-c3sg9at</t>
+          <t>https://www.thegioididong.com/laptop/singpc-m16-i595-i5-1235u</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:40:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>Laptop HP 240R G10 - CC9B9PT (Core 7 150U, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="n">
-        <v>23990000</v>
-      </c>
-      <c r="C100" s="2" t="n">
-        <v>29590000</v>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>-19%</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x USB Type-C (Power Delivery, DisplayPort 1.4, HP Sleep and Charge) 2 x USB Type-A HDMI 1.4b 1 x Headphone/ Microphone combo audio jack | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 323.7 mm - Rộng 215 mm - Dày 13.2 mm - 1.406 kg | Chất liệu:: Vỏ nhựa</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thegioididong.com/laptop/hp-240r-g10-core-7-150u-cc9b9pt</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31 14:40:58</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>Laptop HP 240R G9 - C40LGAT (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="n">
-        <v>24490000</v>
-      </c>
-      <c r="C101" s="2" t="n">
-        <v>26590000</v>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>-8%</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HP TrueVision Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324 mm - Rộng 225.9 mm - Dày 9.4 mm - 1.406 kg | Chất liệu:: Vỏ nhựa</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thegioididong.com/laptop/hp-240r-g9-core-5-120u-c40lgat</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31 14:41:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Laptop HP 240R G9 - C40M2AT (Core 5 120U, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="n">
-        <v>18990000</v>
-      </c>
-      <c r="C102" s="2" t="n">
-        <v>23590000</v>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>-19%</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HP TrueVision Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324 mm - Rộng 225.9 mm - Dày 9.4 mm - 1.406 kg | Chất liệu:: Vỏ nhựa</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thegioididong.com/laptop/hp-240r-g9-core-5-120u-c40m2at</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31 14:41:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Laptop HP 240R G9 - AX3C6AT (i3 1315U, 8GB, 512GB, Full HD, Win11)</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="n">
-        <v>14490000</v>
-      </c>
-      <c r="C103" s="2" t="n">
-        <v>16390000</v>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>-12%</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ CPU:: Intel Core i3 Raptor Lake - 1315U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.50 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324 mm - Rộng 225.9 mm - Dày 9.4 mm - 1.397 kg | Chất liệu:: Vỏ nhựa</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thegioididong.com/laptop/hp-240r-g9-i3-1315u-ax3c6at</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31 14:41:40</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>Laptop HP EliteBook 6 G1a 14 - C0CE1PT (R5 AI 340, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="n">
-        <v>30190000</v>
-      </c>
-      <c r="C104" s="2" t="n">
-        <v>31590000</v>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.528 kg | Chất liệu:: Vỏ kim loại</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r5-ai-340-c0ce1pt</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31 14:41:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>Laptop HP EliteBook 6 G1a 14 - C0CF2PT (R5 AI 340, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="n">
-        <v>31190000</v>
-      </c>
-      <c r="C105" s="2" t="n">
-        <v>32590000</v>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.528 kg | Chất liệu:: Vỏ kim loại</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r5-ai-340-c0cf2pt</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31 14:42:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Laptop HP EliteBook 6 G1a 14 - C0CE2PT (R7 AI 350, 16GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="n">
-        <v>34290000</v>
-      </c>
-      <c r="C106" s="2" t="n">
-        <v>35690000</v>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.549 kg | Chất liệu:: Nắp lưng và chiếu nghỉ tay bằng kim loại</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r7-ai-350-c0ce2pt</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31 14:42:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>Laptop HP EliteBook 6 G1a 14 - C0CG2PT (R7 AI 350, 16GB, 512GB, WUXGA, Win11)</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="n">
-        <v>33290000</v>
-      </c>
-      <c r="C107" s="2" t="n">
-        <v>34690000</v>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng 100.000đ mua Bàn Phím Logitech MK250 | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E (802.11ax) | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 318.6 mm - Rộng 224.3 mm - Dày 17 mm - 1.531 kg | Chất liệu:: Vỏ kim loại</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-6-g1a-14-r7-ai-350-c0cg2pt</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31 14:42:35</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>Laptop HP EliteBook 8 G1a 14 - C0CE5PT (R7 AI PRO 350, 32GB, 512GB, WUXGA, Cảm ứng, Win11)</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="n">
-        <v>37790000</v>
-      </c>
-      <c r="C108" s="2" t="n">
-        <v>39190000</v>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x USB 3.2. 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1 x Headphone/microphone combo 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 62 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 315.6 mm - Rộng 222 mm - Dày 15.5 mm - 1.564 kg | Chất liệu:: Vỏ kim loại</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-8-g1a-14-ai-350-c0ce5pt</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31 14:42:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Laptop HP EliteBook 8 G1a 14 - C0CE3PT (R5 AI PRO 340, 32GB, 512GB, WUXGA, Cảm ứng, Win11 Pro)</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="n">
-        <v>40790000</v>
-      </c>
-      <c r="C109" s="2" t="n">
-        <v>42190000</v>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 Pro - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 32 GB | Loại RAM:: DDR5 (1 khe 32 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x USB A 2 x Thunderbolt 4 (Hỗ trợ Power Delivery, DisplayPort 2.1, HP Sleep and Charge) 1 x Headphone/microphone combo HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Smart Card | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 62 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 315.6 mm - Rộng 222 mm - Dày 15.5 mm - 1.39 kg | Chất liệu:: Vỏ kim loại</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thegioididong.com/laptop/hp-elitebook-8-g1a-14-r5-ai-pro-340-c0ce3pt</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31 14:43:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Laptop HP Gaming HyperX Omen 15 ga0092TX - D72D8PA (i5 14450HX, 16GB, 512GB, RTX 5050 8GB, WUXGA 165Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="n">
-        <v>45590000</v>
-      </c>
-      <c r="C110" s="2" t="n">
-        <v>46990000</v>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 421 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.37 kg | Chất liệu:: Vỏ nhựa</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thegioididong.com/laptop/hp-gaming-hyperx-omen-15-ga0092tx-i5-14450hx-d72d8pa</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31 14:43:17</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>Laptop HP Gaming VICTUS 15 fa2451TX - D17WPPA (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="n">
-        <v>27490000</v>
-      </c>
-      <c r="C111" s="2" t="n">
-        <v>31990000</v>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>-14%</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35W - 115W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2280)) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x USB 3.2 1 x USB 3.2 (hỗ trợ HP Sleep and Charge) 1 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358 mm - Rộng 255 mm - Dày 23.5 mm - 2.29 kg | Chất liệu:: Vỏ nhựa</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thegioididong.com/laptop/hp-gaming-victus-15-fa2451tx-i5-13420h-d17wppa</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31 14:43:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Laptop HP HyperX Omen 15 ga0091TX - D72D7PA (i5 14450HX, 16GB, 512GB, RTX 5060 8GB, WUXGA 165Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="n">
-        <v>48590000</v>
-      </c>
-      <c r="C112" s="2" t="n">
-        <v>49990000</v>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3840 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 614 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.363 kg | Chất liệu:: Vỏ nhựa</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thegioididong.com/laptop/hp-hyperx-omen-15-ga0091tx-i5-14450h-d72d7pa</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31 14:43:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>Laptop HP OmniBook 7 Aero 13 bg1087AU - BZ7S1PA (R5 AI 340, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="n">
-        <v>27990000</v>
-      </c>
-      <c r="C113" s="2" t="n">
-        <v>29790000</v>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Phiếu mua hàng giảm 10% tối đa 300,000đ mua đèn năng lượng mặt trời | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN NGAY ĐẾN 1,2 TRIỆU khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 840M Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCie Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4TB) | Kích thước màn hình:: 13.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 400 nits | Cổng giao tiếp:: 2 x USB Type-A 2 x USB Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) 1 x Headphone/microphone combo HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E MT7922 Bluetooth 5.3 | Webcam:: HP 5MP Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Poly Studio HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 43 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 297.3 mm - Rộng 211.2 mm - Dày 17.4 mm - 0.99 kg | Chất liệu:: Vỏ kim loại</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-7-aero-13-bg1087au-r5-ai-340-bz7s1pa</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31 14:43:58</t>
-        </is>
-      </c>
-    </row>
